--- a/eduservices/tagetik/RESTITUTIONS_EDUSERVICES.xlsx
+++ b/eduservices/tagetik/RESTITUTIONS_EDUSERVICES.xlsx
@@ -1270,7 +1270,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="B59" s="60" t="inlineStr">
         <is>
-          <t>V_CAMPAGNES (calibration : élasticité acquisition, conversion, réfs)  +  socle AW_002_000002_000001 (CA/inscrit réel)</t>
+          <t>V_MOTEUR_CAL  (source unique : séries annuelles par campus × exercice)</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="B60" s="60" t="inlineStr">
         <is>
-          <t>ENTITY (campus) ▸ groupé par MARQUE   —   l'élasticité vit au campus, la marque = sous-total</t>
+          <t>ENTITY (campus) ▸ groupé par MARQUE   en lignes   ·   EXERCICE (2024·2025·2026) en colonnes</t>
         </is>
       </c>
     </row>
@@ -3726,75 +3726,87 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="59" t="inlineStr">
+      <c r="A64" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   EXERCICE</t>
+        </is>
+      </c>
+      <c r="B64" s="63" t="inlineStr">
+        <is>
+          <t>2024 · 2025 · 2026   (réel ; le budget = 2027)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="59" t="inlineStr">
         <is>
           <t>Champs de la vue</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Leads payants (L.pay 24/25/26)</t>
-        </is>
-      </c>
-      <c r="B65" s="63" t="inlineStr">
-        <is>
-          <t>PAID_REF / LEAD_REF  (V_CAMPAGNES)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="64" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Budget acquisition (Bud.24/25/26)</t>
+          <t xml:space="preserve">   Leads payants (L.pay 24/25/26)</t>
         </is>
       </c>
       <c r="B66" s="63" t="inlineStr">
         <is>
-          <t>SPEND_ACQ_REF  (compte 6231, V_CAMPAGNES)</t>
+          <t>LEAD_PAY  (par EXERCICE)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="64" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Élasticité</t>
+          <t xml:space="preserve">   Budget acquisition (Bud.24/25/26)</t>
         </is>
       </c>
       <c r="B67" s="63" t="inlineStr">
         <is>
-          <t>REND_ACQ = régression 3 ans  =SLOPE(LN(leads);LN(budget))</t>
+          <t>SPEND_ACQ  (compte 6231, par EXERCICE)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="64" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Conversion</t>
+          <t xml:space="preserve">   Élasticité</t>
         </is>
       </c>
       <c r="B68" s="63" t="inlineStr">
         <is>
-          <t>CONVERSION = inscrits ÷ leads  (V_CAMPAGNES)</t>
+          <t>MEMBRE CALCULÉ = LN(LEAD_PAY[2026]/LEAD_PAY[2024]) ÷ LN(SPEND_ACQ[2026]/SPEND_ACQ[2024])</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="64" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Conversion</t>
+        </is>
+      </c>
+      <c r="B69" s="63" t="inlineStr">
+        <is>
+          <t>CONVERSION = INSCRITS ÷ LEAD_TOT  (par EXERCICE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="64" t="inlineStr">
+        <is>
           <t xml:space="preserve">   CA / inscrit</t>
         </is>
       </c>
-      <c r="B69" s="63" t="inlineStr">
-        <is>
-          <t>(VOL_NEW·REV_STUD + VOL_NEW·REV_FRAIS_INS) ÷ VOL_NEW  par campus (socle 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="65" t="n"/>
-      <c r="B70" s="65" t="n"/>
+      <c r="B70" s="63" t="inlineStr">
+        <is>
+          <t>CA_PAR_INSCRIT  (par campus × EXERCICE, vrai chiffre)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="65" t="n"/>
+      <c r="B71" s="65" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3807,7 +3819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5011,7 +5023,7 @@
       </c>
       <c r="B49" s="60" t="inlineStr">
         <is>
-          <t>V_CAMPAGNES (élasticité marque, réfs organiques)  +  socle AW_002_000002_000001</t>
+          <t>V_MOTEUR_CAL  (source unique : séries annuelles par campus × exercice)</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5035,7 @@
       </c>
       <c r="B50" s="60" t="inlineStr">
         <is>
-          <t>ENTITY (campus) ▸ groupé par MARQUE</t>
+          <t>ENTITY (campus) ▸ groupé par MARQUE   en lignes   ·   EXERCICE (2024·2025·2026) en colonnes</t>
         </is>
       </c>
     </row>
@@ -5059,51 +5071,63 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="59" t="inlineStr">
+      <c r="A54" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   EXERCICE</t>
+        </is>
+      </c>
+      <c r="B54" s="63" t="inlineStr">
+        <is>
+          <t>2024 · 2025 · 2026   (réel ; le budget = 2027)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="59" t="inlineStr">
         <is>
           <t>Champs de la vue</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Budget de marque (Bud.mq 24/25/26)</t>
-        </is>
-      </c>
-      <c r="B55" s="63" t="inlineStr">
-        <is>
-          <t>SPEND_BRAND_REF  (compte 6236, V_CAMPAGNES)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="64" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Leads organiques (Org.24/25/26)</t>
+          <t xml:space="preserve">   Budget de marque (Bud.mq 24/25/26)</t>
         </is>
       </c>
       <c r="B56" s="63" t="inlineStr">
         <is>
-          <t>ORG_REF  (V_CAMPAGNES)</t>
+          <t>SPEND_BRAND  (compte 6236, par EXERCICE)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="64" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Leads organiques (Org.24/25/26)</t>
+        </is>
+      </c>
+      <c r="B57" s="63" t="inlineStr">
+        <is>
+          <t>LEAD_ORG  (par EXERCICE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="64" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Élasticité marque</t>
         </is>
       </c>
-      <c r="B57" s="63" t="inlineStr">
-        <is>
-          <t>REND_BRAND = régression 3 ans  =SLOPE(LN(organiques);LN(budget marque))</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="65" t="n"/>
-      <c r="B58" s="65" t="n"/>
+      <c r="B58" s="63" t="inlineStr">
+        <is>
+          <t>MEMBRE CALCULÉ = LN(LEAD_ORG[2026]/LEAD_ORG[2024]) ÷ LN(SPEND_BRAND[2026]/SPEND_BRAND[2024])</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="65" t="n"/>
+      <c r="B59" s="65" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/eduservices/tagetik/RESTITUTIONS_EDUSERVICES.xlsx
+++ b/eduservices/tagetik/RESTITUTIONS_EDUSERVICES.xlsx
@@ -5140,7 +5140,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5392,13 +5392,13 @@
         <v>3176674</v>
       </c>
       <c r="E19" s="70" t="n">
-        <v>1467998</v>
+        <v>1431227</v>
       </c>
       <c r="F19" s="71" t="n">
-        <v>1708676</v>
+        <v>1745447</v>
       </c>
       <c r="G19" s="72" t="n">
-        <v>0.1785925824284567</v>
+        <v>0.1824358877166731</v>
       </c>
     </row>
     <row r="20" outlineLevel="1">
@@ -5417,13 +5417,13 @@
         <v>655576</v>
       </c>
       <c r="E20" s="75" t="n">
-        <v>272137</v>
+        <v>265320</v>
       </c>
       <c r="F20" s="76" t="n">
-        <v>383439</v>
+        <v>390256</v>
       </c>
       <c r="G20" s="77" t="n">
-        <v>0.2161914740917732</v>
+        <v>0.2200347793799896</v>
       </c>
     </row>
     <row r="21" hidden="1" outlineLevel="2">
@@ -5442,13 +5442,13 @@
         <v>350802</v>
       </c>
       <c r="E21" s="80" t="n">
-        <v>161752</v>
+        <v>157700</v>
       </c>
       <c r="F21" s="81" t="n">
-        <v>189050</v>
+        <v>193102</v>
       </c>
       <c r="G21" s="82" t="n">
-        <v>0.1827904309835726</v>
+        <v>0.1867078673489377</v>
       </c>
     </row>
     <row r="22" hidden="1" outlineLevel="3">
@@ -5467,13 +5467,13 @@
         <v>121994</v>
       </c>
       <c r="E22" s="80" t="n">
-        <v>55739</v>
+        <v>54343</v>
       </c>
       <c r="F22" s="81" t="n">
-        <v>66255</v>
+        <v>67651</v>
       </c>
       <c r="G22" s="82" t="n">
-        <v>0.1763900977877877</v>
+        <v>0.1801070836905206</v>
       </c>
     </row>
     <row r="23" hidden="1" outlineLevel="4">
@@ -5492,13 +5492,13 @@
         <v>121994</v>
       </c>
       <c r="E23" s="80" t="n">
-        <v>55739</v>
+        <v>54343</v>
       </c>
       <c r="F23" s="81" t="n">
-        <v>66255</v>
+        <v>67651</v>
       </c>
       <c r="G23" s="82" t="n">
-        <v>0.1763900977877877</v>
+        <v>0.1801070836905206</v>
       </c>
     </row>
     <row r="24" hidden="1" outlineLevel="3">
@@ -5517,13 +5517,13 @@
         <v>116372</v>
       </c>
       <c r="E24" s="80" t="n">
-        <v>53553</v>
+        <v>52212</v>
       </c>
       <c r="F24" s="81" t="n">
-        <v>62819</v>
+        <v>64160</v>
       </c>
       <c r="G24" s="82" t="n">
-        <v>0.1888093005949026</v>
+        <v>0.1928410533450688</v>
       </c>
     </row>
     <row r="25" hidden="1" outlineLevel="4">
@@ -5542,13 +5542,13 @@
         <v>116372</v>
       </c>
       <c r="E25" s="80" t="n">
-        <v>53553</v>
+        <v>52212</v>
       </c>
       <c r="F25" s="81" t="n">
-        <v>62819</v>
+        <v>64160</v>
       </c>
       <c r="G25" s="82" t="n">
-        <v>0.1888093005949026</v>
+        <v>0.1928410533450688</v>
       </c>
     </row>
     <row r="26" hidden="1" outlineLevel="3">
@@ -5567,13 +5567,13 @@
         <v>112437</v>
       </c>
       <c r="E26" s="80" t="n">
-        <v>52460</v>
+        <v>51146</v>
       </c>
       <c r="F26" s="81" t="n">
-        <v>59977</v>
+        <v>61291</v>
       </c>
       <c r="G26" s="82" t="n">
-        <v>0.1840223990890867</v>
+        <v>0.1880541518392529</v>
       </c>
     </row>
     <row r="27" hidden="1" outlineLevel="4">
@@ -5592,13 +5592,13 @@
         <v>112437</v>
       </c>
       <c r="E27" s="80" t="n">
-        <v>52460</v>
+        <v>51146</v>
       </c>
       <c r="F27" s="81" t="n">
-        <v>59977</v>
+        <v>61291</v>
       </c>
       <c r="G27" s="82" t="n">
-        <v>0.1840223990890867</v>
+        <v>0.1880541518392529</v>
       </c>
     </row>
     <row r="28" hidden="1" outlineLevel="2">
@@ -5617,13 +5617,13 @@
         <v>304774</v>
       </c>
       <c r="E28" s="80" t="n">
-        <v>110385</v>
+        <v>107620</v>
       </c>
       <c r="F28" s="81" t="n">
-        <v>194389</v>
+        <v>197154</v>
       </c>
       <c r="G28" s="82" t="n">
-        <v>0.2629138126247588</v>
+        <v>0.2666534212328704</v>
       </c>
     </row>
     <row r="29" hidden="1" outlineLevel="3">
@@ -5642,13 +5642,13 @@
         <v>150661</v>
       </c>
       <c r="E29" s="80" t="n">
-        <v>55739</v>
+        <v>54343</v>
       </c>
       <c r="F29" s="81" t="n">
-        <v>94922</v>
+        <v>96319</v>
       </c>
       <c r="G29" s="82" t="n">
-        <v>0.2527121296555245</v>
+        <v>0.2564291155582575</v>
       </c>
     </row>
     <row r="30" hidden="1" outlineLevel="4">
@@ -5667,13 +5667,13 @@
         <v>150661</v>
       </c>
       <c r="E30" s="80" t="n">
-        <v>55739</v>
+        <v>54343</v>
       </c>
       <c r="F30" s="81" t="n">
-        <v>94922</v>
+        <v>96319</v>
       </c>
       <c r="G30" s="82" t="n">
-        <v>0.2527121296555245</v>
+        <v>0.2564291155582575</v>
       </c>
     </row>
     <row r="31" hidden="1" outlineLevel="3">
@@ -5692,13 +5692,13 @@
         <v>154113</v>
       </c>
       <c r="E31" s="80" t="n">
-        <v>54646</v>
+        <v>53277</v>
       </c>
       <c r="F31" s="81" t="n">
-        <v>99467</v>
+        <v>100836</v>
       </c>
       <c r="G31" s="82" t="n">
-        <v>0.2734482597683709</v>
+        <v>0.2772112290018594</v>
       </c>
     </row>
     <row r="32" hidden="1" outlineLevel="4">
@@ -5717,13 +5717,13 @@
         <v>154113</v>
       </c>
       <c r="E32" s="80" t="n">
-        <v>54646</v>
+        <v>53277</v>
       </c>
       <c r="F32" s="81" t="n">
-        <v>99467</v>
+        <v>100836</v>
       </c>
       <c r="G32" s="82" t="n">
-        <v>0.2734482597683709</v>
+        <v>0.2772112290018594</v>
       </c>
     </row>
     <row r="33" outlineLevel="1">
@@ -5742,13 +5742,13 @@
         <v>956986</v>
       </c>
       <c r="E33" s="75" t="n">
-        <v>383086</v>
+        <v>373490</v>
       </c>
       <c r="F33" s="76" t="n">
-        <v>573900</v>
+        <v>583496</v>
       </c>
       <c r="G33" s="77" t="n">
-        <v>0.2298630161977837</v>
+        <v>0.233706321486</v>
       </c>
     </row>
     <row r="34" hidden="1" outlineLevel="2">
@@ -5767,13 +5767,13 @@
         <v>545713</v>
       </c>
       <c r="E34" s="80" t="n">
-        <v>228196</v>
+        <v>222480</v>
       </c>
       <c r="F34" s="81" t="n">
-        <v>317517</v>
+        <v>323232</v>
       </c>
       <c r="G34" s="82" t="n">
-        <v>0.2176052657480825</v>
+        <v>0.2215225713189437</v>
       </c>
     </row>
     <row r="35" hidden="1" outlineLevel="3">
@@ -5792,13 +5792,13 @@
         <v>155626</v>
       </c>
       <c r="E35" s="80" t="n">
-        <v>78036</v>
+        <v>76081</v>
       </c>
       <c r="F35" s="81" t="n">
-        <v>77590</v>
+        <v>79544</v>
       </c>
       <c r="G35" s="82" t="n">
-        <v>0.1475958602703101</v>
+        <v>0.1513141337079641</v>
       </c>
     </row>
     <row r="36" hidden="1" outlineLevel="4">
@@ -5817,13 +5817,13 @@
         <v>155626</v>
       </c>
       <c r="E36" s="80" t="n">
-        <v>78036</v>
+        <v>76081</v>
       </c>
       <c r="F36" s="81" t="n">
-        <v>77590</v>
+        <v>79544</v>
       </c>
       <c r="G36" s="82" t="n">
-        <v>0.1475958602703101</v>
+        <v>0.1513141337079641</v>
       </c>
     </row>
     <row r="37" hidden="1" outlineLevel="3">
@@ -5842,13 +5842,13 @@
         <v>197209</v>
       </c>
       <c r="E37" s="80" t="n">
-        <v>75671</v>
+        <v>73776</v>
       </c>
       <c r="F37" s="81" t="n">
-        <v>121537</v>
+        <v>123433</v>
       </c>
       <c r="G37" s="82" t="n">
-        <v>0.2583703984446492</v>
+        <v>0.262399792720964</v>
       </c>
     </row>
     <row r="38" hidden="1" outlineLevel="4">
@@ -5867,13 +5867,13 @@
         <v>197209</v>
       </c>
       <c r="E38" s="80" t="n">
-        <v>75671</v>
+        <v>73776</v>
       </c>
       <c r="F38" s="81" t="n">
-        <v>121537</v>
+        <v>123433</v>
       </c>
       <c r="G38" s="82" t="n">
-        <v>0.2583703984446492</v>
+        <v>0.262399792720964</v>
       </c>
     </row>
     <row r="39" hidden="1" outlineLevel="3">
@@ -5892,13 +5892,13 @@
         <v>192878</v>
       </c>
       <c r="E39" s="80" t="n">
-        <v>74489</v>
+        <v>72623</v>
       </c>
       <c r="F39" s="81" t="n">
-        <v>118389</v>
+        <v>120255</v>
       </c>
       <c r="G39" s="82" t="n">
-        <v>0.2556731330305471</v>
+        <v>0.2597025273068619</v>
       </c>
     </row>
     <row r="40" hidden="1" outlineLevel="4">
@@ -5917,13 +5917,13 @@
         <v>192878</v>
       </c>
       <c r="E40" s="80" t="n">
-        <v>74489</v>
+        <v>72623</v>
       </c>
       <c r="F40" s="81" t="n">
-        <v>118389</v>
+        <v>120255</v>
       </c>
       <c r="G40" s="82" t="n">
-        <v>0.2556731330305471</v>
+        <v>0.2597025273068619</v>
       </c>
     </row>
     <row r="41" hidden="1" outlineLevel="2">
@@ -5942,13 +5942,13 @@
         <v>411273</v>
       </c>
       <c r="E41" s="80" t="n">
-        <v>154890</v>
+        <v>151010</v>
       </c>
       <c r="F41" s="81" t="n">
-        <v>256384</v>
+        <v>260263</v>
       </c>
       <c r="G41" s="82" t="n">
-        <v>0.2471012364453605</v>
+        <v>0.2508404742559553</v>
       </c>
     </row>
     <row r="42" hidden="1" outlineLevel="3">
@@ -5967,13 +5967,13 @@
         <v>200589</v>
       </c>
       <c r="E42" s="80" t="n">
-        <v>78036</v>
+        <v>76081</v>
       </c>
       <c r="F42" s="81" t="n">
-        <v>122553</v>
+        <v>124507</v>
       </c>
       <c r="G42" s="82" t="n">
-        <v>0.2331270193184183</v>
+        <v>0.2368452927560723</v>
       </c>
     </row>
     <row r="43" hidden="1" outlineLevel="4">
@@ -5992,13 +5992,13 @@
         <v>200589</v>
       </c>
       <c r="E43" s="80" t="n">
-        <v>78036</v>
+        <v>76081</v>
       </c>
       <c r="F43" s="81" t="n">
-        <v>122553</v>
+        <v>124507</v>
       </c>
       <c r="G43" s="82" t="n">
-        <v>0.2331270193184183</v>
+        <v>0.2368452927560723</v>
       </c>
     </row>
     <row r="44" hidden="1" outlineLevel="3">
@@ -6017,13 +6017,13 @@
         <v>210685</v>
       </c>
       <c r="E44" s="80" t="n">
-        <v>76854</v>
+        <v>74929</v>
       </c>
       <c r="F44" s="81" t="n">
-        <v>133831</v>
+        <v>135756</v>
       </c>
       <c r="G44" s="82" t="n">
-        <v>0.2614526038719046</v>
+        <v>0.2652133718631318</v>
       </c>
     </row>
     <row r="45" hidden="1" outlineLevel="4">
@@ -6042,13 +6042,13 @@
         <v>210685</v>
       </c>
       <c r="E45" s="80" t="n">
-        <v>76854</v>
+        <v>74929</v>
       </c>
       <c r="F45" s="81" t="n">
-        <v>133831</v>
+        <v>135756</v>
       </c>
       <c r="G45" s="82" t="n">
-        <v>0.2614526038719046</v>
+        <v>0.2652133718631318</v>
       </c>
     </row>
     <row r="46" outlineLevel="1">
@@ -6067,13 +6067,13 @@
         <v>874770</v>
       </c>
       <c r="E46" s="75" t="n">
-        <v>331162</v>
+        <v>322867</v>
       </c>
       <c r="F46" s="76" t="n">
-        <v>543608</v>
+        <v>551903</v>
       </c>
       <c r="G46" s="77" t="n">
-        <v>0.2518685285767535</v>
+        <v>0.2557118338649698</v>
       </c>
     </row>
     <row r="47" hidden="1" outlineLevel="2">
@@ -6092,13 +6092,13 @@
         <v>518055</v>
       </c>
       <c r="E47" s="80" t="n">
-        <v>197120</v>
+        <v>192183</v>
       </c>
       <c r="F47" s="81" t="n">
-        <v>320935</v>
+        <v>325872</v>
       </c>
       <c r="G47" s="82" t="n">
-        <v>0.254629182121454</v>
+        <v>0.2585465920345755</v>
       </c>
     </row>
     <row r="48" hidden="1" outlineLevel="3">
@@ -6117,13 +6117,13 @@
         <v>180270</v>
       </c>
       <c r="E48" s="80" t="n">
-        <v>67584</v>
+        <v>65891</v>
       </c>
       <c r="F48" s="81" t="n">
-        <v>112686</v>
+        <v>114379</v>
       </c>
       <c r="G48" s="82" t="n">
-        <v>0.2474444722449507</v>
+        <v>0.2511617720412981</v>
       </c>
     </row>
     <row r="49" hidden="1" outlineLevel="4">
@@ -6142,13 +6142,13 @@
         <v>180270</v>
       </c>
       <c r="E49" s="80" t="n">
-        <v>67584</v>
+        <v>65891</v>
       </c>
       <c r="F49" s="81" t="n">
-        <v>112686</v>
+        <v>114379</v>
       </c>
       <c r="G49" s="82" t="n">
-        <v>0.2474444722449507</v>
+        <v>0.2511617720412981</v>
       </c>
     </row>
     <row r="50" hidden="1" outlineLevel="3">
@@ -6167,13 +6167,13 @@
         <v>171018</v>
       </c>
       <c r="E50" s="80" t="n">
-        <v>65331</v>
+        <v>63695</v>
       </c>
       <c r="F50" s="81" t="n">
-        <v>105686</v>
+        <v>107323</v>
       </c>
       <c r="G50" s="82" t="n">
-        <v>0.2603113708487192</v>
+        <v>0.2643419859136159</v>
       </c>
     </row>
     <row r="51" hidden="1" outlineLevel="4">
@@ -6192,13 +6192,13 @@
         <v>171018</v>
       </c>
       <c r="E51" s="80" t="n">
-        <v>65331</v>
+        <v>63695</v>
       </c>
       <c r="F51" s="81" t="n">
-        <v>105686</v>
+        <v>107323</v>
       </c>
       <c r="G51" s="82" t="n">
-        <v>0.2603113708487192</v>
+        <v>0.2643419859136159</v>
       </c>
     </row>
     <row r="52" hidden="1" outlineLevel="3">
@@ -6217,13 +6217,13 @@
         <v>166767</v>
       </c>
       <c r="E52" s="80" t="n">
-        <v>64205</v>
+        <v>62597</v>
       </c>
       <c r="F52" s="81" t="n">
-        <v>102562</v>
+        <v>104170</v>
       </c>
       <c r="G52" s="82" t="n">
-        <v>0.2570475987993735</v>
+        <v>0.2610782138642702</v>
       </c>
     </row>
     <row r="53" hidden="1" outlineLevel="4">
@@ -6242,13 +6242,13 @@
         <v>166767</v>
       </c>
       <c r="E53" s="80" t="n">
-        <v>64205</v>
+        <v>62597</v>
       </c>
       <c r="F53" s="81" t="n">
-        <v>102562</v>
+        <v>104170</v>
       </c>
       <c r="G53" s="82" t="n">
-        <v>0.2570475987993735</v>
+        <v>0.2610782138642702</v>
       </c>
     </row>
     <row r="54" hidden="1" outlineLevel="2">
@@ -6267,13 +6267,13 @@
         <v>356715</v>
       </c>
       <c r="E54" s="80" t="n">
-        <v>134042</v>
+        <v>130684</v>
       </c>
       <c r="F54" s="81" t="n">
-        <v>222673</v>
+        <v>226031</v>
       </c>
       <c r="G54" s="82" t="n">
-        <v>0.247993344561005</v>
+        <v>0.2517326277206653</v>
       </c>
     </row>
     <row r="55" hidden="1" outlineLevel="3">
@@ -6292,13 +6292,13 @@
         <v>175550</v>
       </c>
       <c r="E55" s="80" t="n">
-        <v>67584</v>
+        <v>65891</v>
       </c>
       <c r="F55" s="81" t="n">
-        <v>107966</v>
+        <v>109658</v>
       </c>
       <c r="G55" s="82" t="n">
-        <v>0.2370785559123368</v>
+        <v>0.2407958557086842</v>
       </c>
     </row>
     <row r="56" hidden="1" outlineLevel="4">
@@ -6317,13 +6317,13 @@
         <v>175550</v>
       </c>
       <c r="E56" s="80" t="n">
-        <v>67584</v>
+        <v>65891</v>
       </c>
       <c r="F56" s="81" t="n">
-        <v>107966</v>
+        <v>109658</v>
       </c>
       <c r="G56" s="82" t="n">
-        <v>0.2370785559123368</v>
+        <v>0.2407958557086842</v>
       </c>
     </row>
     <row r="57" hidden="1" outlineLevel="3">
@@ -6342,13 +6342,13 @@
         <v>181165</v>
       </c>
       <c r="E57" s="80" t="n">
-        <v>66458</v>
+        <v>64793</v>
       </c>
       <c r="F57" s="81" t="n">
-        <v>114708</v>
+        <v>116372</v>
       </c>
       <c r="G57" s="82" t="n">
-        <v>0.2592263270482446</v>
+        <v>0.2629882344421482</v>
       </c>
     </row>
     <row r="58" hidden="1" outlineLevel="4">
@@ -6367,13 +6367,13 @@
         <v>181165</v>
       </c>
       <c r="E58" s="80" t="n">
-        <v>66458</v>
+        <v>64793</v>
       </c>
       <c r="F58" s="81" t="n">
-        <v>114708</v>
+        <v>116372</v>
       </c>
       <c r="G58" s="82" t="n">
-        <v>0.2592263270482446</v>
+        <v>0.2629882344421482</v>
       </c>
     </row>
     <row r="59" outlineLevel="1">
@@ -6392,13 +6392,13 @@
         <v>689342</v>
       </c>
       <c r="E59" s="75" t="n">
-        <v>481613</v>
+        <v>469549</v>
       </c>
       <c r="F59" s="76" t="n">
-        <v>207729</v>
+        <v>219793</v>
       </c>
       <c r="G59" s="77" t="n">
-        <v>0.06618022845090719</v>
+        <v>0.07002353373912357</v>
       </c>
     </row>
     <row r="60" hidden="1" outlineLevel="2">
@@ -6417,13 +6417,13 @@
         <v>341046</v>
       </c>
       <c r="E60" s="80" t="n">
-        <v>287455</v>
+        <v>280255</v>
       </c>
       <c r="F60" s="85" t="n">
-        <v>53591</v>
+        <v>60791</v>
       </c>
       <c r="G60" s="86" t="n">
-        <v>0.02915369245173039</v>
+        <v>0.03307064273352934</v>
       </c>
     </row>
     <row r="61" hidden="1" outlineLevel="3">
@@ -6442,13 +6442,13 @@
         <v>105838</v>
       </c>
       <c r="E61" s="80" t="n">
-        <v>98340</v>
+        <v>95877</v>
       </c>
       <c r="F61" s="85" t="n">
-        <v>7498</v>
+        <v>9961</v>
       </c>
       <c r="G61" s="86" t="n">
-        <v>0.01132289503893838</v>
+        <v>0.01504255301995241</v>
       </c>
     </row>
     <row r="62" hidden="1" outlineLevel="4">
@@ -6467,13 +6467,13 @@
         <v>105838</v>
       </c>
       <c r="E62" s="80" t="n">
-        <v>98340</v>
+        <v>95877</v>
       </c>
       <c r="F62" s="85" t="n">
-        <v>7498</v>
+        <v>9961</v>
       </c>
       <c r="G62" s="86" t="n">
-        <v>0.01132289503893838</v>
+        <v>0.01504255301995241</v>
       </c>
     </row>
     <row r="63" hidden="1" outlineLevel="3">
@@ -6492,13 +6492,13 @@
         <v>121269</v>
       </c>
       <c r="E63" s="80" t="n">
-        <v>95818</v>
+        <v>93418</v>
       </c>
       <c r="F63" s="85" t="n">
-        <v>25450</v>
+        <v>27850</v>
       </c>
       <c r="G63" s="86" t="n">
-        <v>0.04271348043021603</v>
+        <v>0.04674152842241108</v>
       </c>
     </row>
     <row r="64" hidden="1" outlineLevel="4">
@@ -6517,13 +6517,13 @@
         <v>121269</v>
       </c>
       <c r="E64" s="80" t="n">
-        <v>95818</v>
+        <v>93418</v>
       </c>
       <c r="F64" s="85" t="n">
-        <v>25450</v>
+        <v>27850</v>
       </c>
       <c r="G64" s="86" t="n">
-        <v>0.04271348043021603</v>
+        <v>0.04674152842241108</v>
       </c>
     </row>
     <row r="65" hidden="1" outlineLevel="3">
@@ -6542,13 +6542,13 @@
         <v>113939</v>
       </c>
       <c r="E65" s="80" t="n">
-        <v>93297</v>
+        <v>90960</v>
       </c>
       <c r="F65" s="85" t="n">
-        <v>20642</v>
+        <v>22979</v>
       </c>
       <c r="G65" s="86" t="n">
-        <v>0.03558027579701142</v>
+        <v>0.03960832378920643</v>
       </c>
     </row>
     <row r="66" hidden="1" outlineLevel="4">
@@ -6567,13 +6567,13 @@
         <v>113939</v>
       </c>
       <c r="E66" s="80" t="n">
-        <v>93297</v>
+        <v>90960</v>
       </c>
       <c r="F66" s="85" t="n">
-        <v>20642</v>
+        <v>22979</v>
       </c>
       <c r="G66" s="86" t="n">
-        <v>0.03558027579701142</v>
+        <v>0.03960832378920643</v>
       </c>
     </row>
     <row r="67" hidden="1" outlineLevel="2">
@@ -6592,13 +6592,13 @@
         <v>348296</v>
       </c>
       <c r="E67" s="80" t="n">
-        <v>194158</v>
+        <v>189295</v>
       </c>
       <c r="F67" s="81" t="n">
-        <v>154138</v>
+        <v>159002</v>
       </c>
       <c r="G67" s="82" t="n">
-        <v>0.1185113620674953</v>
+        <v>0.1222505818425691</v>
       </c>
     </row>
     <row r="68" hidden="1" outlineLevel="3">
@@ -6617,13 +6617,13 @@
         <v>164810</v>
       </c>
       <c r="E68" s="80" t="n">
-        <v>98340</v>
+        <v>95877</v>
       </c>
       <c r="F68" s="81" t="n">
-        <v>66470</v>
+        <v>68934</v>
       </c>
       <c r="G68" s="82" t="n">
-        <v>0.1003751737378601</v>
+        <v>0.1040948317188742</v>
       </c>
     </row>
     <row r="69" hidden="1" outlineLevel="4">
@@ -6642,13 +6642,13 @@
         <v>164810</v>
       </c>
       <c r="E69" s="80" t="n">
-        <v>98340</v>
+        <v>95877</v>
       </c>
       <c r="F69" s="81" t="n">
-        <v>66470</v>
+        <v>68934</v>
       </c>
       <c r="G69" s="82" t="n">
-        <v>0.1003751737378601</v>
+        <v>0.1040948317188742</v>
       </c>
     </row>
     <row r="70" hidden="1" outlineLevel="3">
@@ -6667,13 +6667,13 @@
         <v>183486</v>
       </c>
       <c r="E70" s="80" t="n">
-        <v>95818</v>
+        <v>93418</v>
       </c>
       <c r="F70" s="81" t="n">
-        <v>87668</v>
+        <v>90068</v>
       </c>
       <c r="G70" s="82" t="n">
-        <v>0.137324248401535</v>
+        <v>0.141083759860917</v>
       </c>
     </row>
     <row r="71" hidden="1" outlineLevel="4">
@@ -6692,13 +6692,13 @@
         <v>183486</v>
       </c>
       <c r="E71" s="80" t="n">
-        <v>95818</v>
+        <v>93418</v>
       </c>
       <c r="F71" s="81" t="n">
-        <v>87668</v>
+        <v>90068</v>
       </c>
       <c r="G71" s="82" t="n">
-        <v>0.137324248401535</v>
+        <v>0.141083759860917</v>
       </c>
     </row>
     <row r="72">
@@ -6717,13 +6717,13 @@
         <v>1976427</v>
       </c>
       <c r="E72" s="70" t="n">
-        <v>974355</v>
+        <v>949950</v>
       </c>
       <c r="F72" s="71" t="n">
-        <v>1002072</v>
+        <v>1026477</v>
       </c>
       <c r="G72" s="72" t="n">
-        <v>0.1592472957412916</v>
+        <v>0.1631258219347755</v>
       </c>
     </row>
     <row r="73" outlineLevel="1">
@@ -6742,13 +6742,13 @@
         <v>755658</v>
       </c>
       <c r="E73" s="75" t="n">
-        <v>271881</v>
+        <v>265070</v>
       </c>
       <c r="F73" s="76" t="n">
-        <v>483777</v>
+        <v>490588</v>
       </c>
       <c r="G73" s="77" t="n">
-        <v>0.2755232200694355</v>
+        <v>0.2794017462629194</v>
       </c>
     </row>
     <row r="74" hidden="1" outlineLevel="2">
@@ -6767,13 +6767,13 @@
         <v>412201</v>
       </c>
       <c r="E74" s="80" t="n">
-        <v>161568</v>
+        <v>157521</v>
       </c>
       <c r="F74" s="81" t="n">
-        <v>250632</v>
+        <v>254679</v>
       </c>
       <c r="G74" s="82" t="n">
-        <v>0.2448297371317927</v>
+        <v>0.2487830356833349</v>
       </c>
     </row>
     <row r="75" hidden="1" outlineLevel="3">
@@ -6792,13 +6792,13 @@
         <v>143828</v>
       </c>
       <c r="E75" s="80" t="n">
-        <v>55713</v>
+        <v>54318</v>
       </c>
       <c r="F75" s="81" t="n">
-        <v>88115</v>
+        <v>89511</v>
       </c>
       <c r="G75" s="82" t="n">
-        <v>0.2368685362456584</v>
+        <v>0.2406199190109659</v>
       </c>
     </row>
     <row r="76" hidden="1" outlineLevel="4">
@@ -6817,13 +6817,13 @@
         <v>143828</v>
       </c>
       <c r="E76" s="80" t="n">
-        <v>55713</v>
+        <v>54318</v>
       </c>
       <c r="F76" s="81" t="n">
-        <v>88115</v>
+        <v>89511</v>
       </c>
       <c r="G76" s="82" t="n">
-        <v>0.2368685362456584</v>
+        <v>0.2406199190109659</v>
       </c>
     </row>
     <row r="77" hidden="1" outlineLevel="3">
@@ -6842,13 +6842,13 @@
         <v>136335</v>
       </c>
       <c r="E77" s="80" t="n">
-        <v>53485</v>
+        <v>52145</v>
       </c>
       <c r="F77" s="81" t="n">
-        <v>82850</v>
+        <v>84190</v>
       </c>
       <c r="G77" s="82" t="n">
-        <v>0.2516109440720648</v>
+        <v>0.2556794991411447</v>
       </c>
     </row>
     <row r="78" hidden="1" outlineLevel="4">
@@ -6867,13 +6867,13 @@
         <v>136335</v>
       </c>
       <c r="E78" s="80" t="n">
-        <v>53485</v>
+        <v>52145</v>
       </c>
       <c r="F78" s="81" t="n">
-        <v>82850</v>
+        <v>84190</v>
       </c>
       <c r="G78" s="82" t="n">
-        <v>0.2516109440720648</v>
+        <v>0.2556794991411447</v>
       </c>
     </row>
     <row r="79" hidden="1" outlineLevel="3">
@@ -6892,13 +6892,13 @@
         <v>132037</v>
       </c>
       <c r="E79" s="80" t="n">
-        <v>52370</v>
+        <v>51059</v>
       </c>
       <c r="F79" s="81" t="n">
-        <v>79667</v>
+        <v>80978</v>
       </c>
       <c r="G79" s="82" t="n">
-        <v>0.2470896803994225</v>
+        <v>0.2511582354685024</v>
       </c>
     </row>
     <row r="80" hidden="1" outlineLevel="4">
@@ -6917,13 +6917,13 @@
         <v>132037</v>
       </c>
       <c r="E80" s="80" t="n">
-        <v>52370</v>
+        <v>51059</v>
       </c>
       <c r="F80" s="81" t="n">
-        <v>79667</v>
+        <v>80978</v>
       </c>
       <c r="G80" s="82" t="n">
-        <v>0.2470896803994225</v>
+        <v>0.2511582354685024</v>
       </c>
     </row>
     <row r="81" hidden="1" outlineLevel="2">
@@ -6942,13 +6942,13 @@
         <v>343457</v>
       </c>
       <c r="E81" s="80" t="n">
-        <v>110312</v>
+        <v>107549</v>
       </c>
       <c r="F81" s="81" t="n">
-        <v>233145</v>
+        <v>235908</v>
       </c>
       <c r="G81" s="82" t="n">
-        <v>0.3184391778421117</v>
+        <v>0.3222131565208181</v>
       </c>
     </row>
     <row r="82" hidden="1" outlineLevel="3">
@@ -6967,13 +6967,13 @@
         <v>170068</v>
       </c>
       <c r="E82" s="80" t="n">
-        <v>55713</v>
+        <v>54318</v>
       </c>
       <c r="F82" s="81" t="n">
-        <v>114355</v>
+        <v>115750</v>
       </c>
       <c r="G82" s="82" t="n">
-        <v>0.3074046249553358</v>
+        <v>0.3111560077206432</v>
       </c>
     </row>
     <row r="83" hidden="1" outlineLevel="4">
@@ -6992,13 +6992,13 @@
         <v>170068</v>
       </c>
       <c r="E83" s="80" t="n">
-        <v>55713</v>
+        <v>54318</v>
       </c>
       <c r="F83" s="81" t="n">
-        <v>114355</v>
+        <v>115750</v>
       </c>
       <c r="G83" s="82" t="n">
-        <v>0.3074046249553358</v>
+        <v>0.3111560077206432</v>
       </c>
     </row>
     <row r="84" hidden="1" outlineLevel="3">
@@ -7017,13 +7017,13 @@
         <v>173390</v>
       </c>
       <c r="E84" s="80" t="n">
-        <v>54599</v>
+        <v>53231</v>
       </c>
       <c r="F84" s="81" t="n">
-        <v>118791</v>
+        <v>120158</v>
       </c>
       <c r="G84" s="82" t="n">
-        <v>0.3298368001491523</v>
+        <v>0.3336341182136268</v>
       </c>
     </row>
     <row r="85" hidden="1" outlineLevel="4">
@@ -7042,13 +7042,13 @@
         <v>173390</v>
       </c>
       <c r="E85" s="80" t="n">
-        <v>54599</v>
+        <v>53231</v>
       </c>
       <c r="F85" s="81" t="n">
-        <v>118791</v>
+        <v>120158</v>
       </c>
       <c r="G85" s="82" t="n">
-        <v>0.3298368001491523</v>
+        <v>0.3336341182136268</v>
       </c>
     </row>
     <row r="86" outlineLevel="1">
@@ -7067,13 +7067,13 @@
         <v>549694</v>
       </c>
       <c r="E86" s="75" t="n">
-        <v>450394</v>
+        <v>439113</v>
       </c>
       <c r="F86" s="87" t="n">
-        <v>99300</v>
+        <v>110581</v>
       </c>
       <c r="G86" s="88" t="n">
-        <v>0.03413870805884781</v>
+        <v>0.03801723425233167</v>
       </c>
     </row>
     <row r="87" hidden="1" outlineLevel="2">
@@ -7092,13 +7092,13 @@
         <v>258369</v>
       </c>
       <c r="E87" s="80" t="n">
-        <v>268455</v>
+        <v>261731</v>
       </c>
       <c r="F87" s="85" t="n">
-        <v>-10086</v>
+        <v>-3362</v>
       </c>
       <c r="G87" s="86" t="n">
-        <v>-0.005929449420008155</v>
+        <v>-0.001976390268380654</v>
       </c>
     </row>
     <row r="88" hidden="1" outlineLevel="3">
@@ -7117,13 +7117,13 @@
         <v>76795</v>
       </c>
       <c r="E88" s="80" t="n">
-        <v>91606</v>
+        <v>89311</v>
       </c>
       <c r="F88" s="85" t="n">
-        <v>-14811</v>
+        <v>-12516</v>
       </c>
       <c r="G88" s="86" t="n">
-        <v>-0.02422908875681863</v>
+        <v>-0.0204754048916165</v>
       </c>
     </row>
     <row r="89" hidden="1" outlineLevel="4">
@@ -7142,13 +7142,13 @@
         <v>76795</v>
       </c>
       <c r="E89" s="80" t="n">
-        <v>91606</v>
+        <v>89311</v>
       </c>
       <c r="F89" s="85" t="n">
-        <v>-14811</v>
+        <v>-12516</v>
       </c>
       <c r="G89" s="86" t="n">
-        <v>-0.02422908875681863</v>
+        <v>-0.0204754048916165</v>
       </c>
     </row>
     <row r="90" hidden="1" outlineLevel="3">
@@ -7167,13 +7167,13 @@
         <v>92572</v>
       </c>
       <c r="E90" s="80" t="n">
-        <v>89061</v>
+        <v>86830</v>
       </c>
       <c r="F90" s="85" t="n">
-        <v>3511</v>
+        <v>5741</v>
       </c>
       <c r="G90" s="86" t="n">
-        <v>0.006396900908326091</v>
+        <v>0.01046179580827074</v>
       </c>
     </row>
     <row r="91" hidden="1" outlineLevel="4">
@@ -7192,13 +7192,13 @@
         <v>92572</v>
       </c>
       <c r="E91" s="80" t="n">
-        <v>89061</v>
+        <v>86830</v>
       </c>
       <c r="F91" s="85" t="n">
-        <v>3511</v>
+        <v>5741</v>
       </c>
       <c r="G91" s="86" t="n">
-        <v>0.006396900908326091</v>
+        <v>0.01046179580827074</v>
       </c>
     </row>
     <row r="92" hidden="1" outlineLevel="3">
@@ -7217,13 +7217,13 @@
         <v>89003</v>
       </c>
       <c r="E92" s="80" t="n">
-        <v>87789</v>
+        <v>85590</v>
       </c>
       <c r="F92" s="85" t="n">
-        <v>1214</v>
+        <v>3413</v>
       </c>
       <c r="G92" s="86" t="n">
-        <v>0.002243987569077308</v>
+        <v>0.00630888246902197</v>
       </c>
     </row>
     <row r="93" hidden="1" outlineLevel="4">
@@ -7242,13 +7242,13 @@
         <v>89003</v>
       </c>
       <c r="E93" s="80" t="n">
-        <v>87789</v>
+        <v>85590</v>
       </c>
       <c r="F93" s="85" t="n">
-        <v>1214</v>
+        <v>3413</v>
       </c>
       <c r="G93" s="86" t="n">
-        <v>0.002243987569077308</v>
+        <v>0.00630888246902197</v>
       </c>
     </row>
     <row r="94" hidden="1" outlineLevel="2">
@@ -7267,13 +7267,13 @@
         <v>291325</v>
       </c>
       <c r="E94" s="80" t="n">
-        <v>181939</v>
+        <v>177382</v>
       </c>
       <c r="F94" s="81" t="n">
-        <v>109386</v>
+        <v>113943</v>
       </c>
       <c r="G94" s="82" t="n">
-        <v>0.09057546166728148</v>
+        <v>0.09434900678703666</v>
       </c>
     </row>
     <row r="95" hidden="1" outlineLevel="3">
@@ -7292,13 +7292,13 @@
         <v>135767</v>
       </c>
       <c r="E95" s="80" t="n">
-        <v>91606</v>
+        <v>89311</v>
       </c>
       <c r="F95" s="81" t="n">
-        <v>44161</v>
+        <v>46456</v>
       </c>
       <c r="G95" s="82" t="n">
-        <v>0.07224421316701335</v>
+        <v>0.07599789703221548</v>
       </c>
     </row>
     <row r="96" hidden="1" outlineLevel="4">
@@ -7317,13 +7317,13 @@
         <v>135767</v>
       </c>
       <c r="E96" s="80" t="n">
-        <v>91606</v>
+        <v>89311</v>
       </c>
       <c r="F96" s="81" t="n">
-        <v>44161</v>
+        <v>46456</v>
       </c>
       <c r="G96" s="82" t="n">
-        <v>0.07224421316701335</v>
+        <v>0.07599789703221548</v>
       </c>
     </row>
     <row r="97" hidden="1" outlineLevel="3">
@@ -7342,13 +7342,13 @@
         <v>155558</v>
       </c>
       <c r="E97" s="80" t="n">
-        <v>90333</v>
+        <v>88071</v>
       </c>
       <c r="F97" s="81" t="n">
-        <v>65225</v>
+        <v>67487</v>
       </c>
       <c r="G97" s="82" t="n">
-        <v>0.1093640692850613</v>
+        <v>0.1131579711916763</v>
       </c>
     </row>
     <row r="98" hidden="1" outlineLevel="4">
@@ -7367,13 +7367,13 @@
         <v>155558</v>
       </c>
       <c r="E98" s="80" t="n">
-        <v>90333</v>
+        <v>88071</v>
       </c>
       <c r="F98" s="81" t="n">
-        <v>65225</v>
+        <v>67487</v>
       </c>
       <c r="G98" s="82" t="n">
-        <v>0.1093640692850613</v>
+        <v>0.1131579711916763</v>
       </c>
     </row>
     <row r="99" outlineLevel="1">
@@ -7392,13 +7392,13 @@
         <v>671075</v>
       </c>
       <c r="E99" s="75" t="n">
-        <v>252081</v>
+        <v>245767</v>
       </c>
       <c r="F99" s="76" t="n">
-        <v>418994</v>
+        <v>425308</v>
       </c>
       <c r="G99" s="77" t="n">
-        <v>0.2573705954329993</v>
+        <v>0.2612491216264831</v>
       </c>
     </row>
     <row r="100" hidden="1" outlineLevel="2">
@@ -7417,13 +7417,13 @@
         <v>366504</v>
       </c>
       <c r="E100" s="80" t="n">
-        <v>150594</v>
+        <v>146822</v>
       </c>
       <c r="F100" s="81" t="n">
-        <v>215910</v>
+        <v>219682</v>
       </c>
       <c r="G100" s="82" t="n">
-        <v>0.226285161265295</v>
+        <v>0.2302385201920003</v>
       </c>
     </row>
     <row r="101" hidden="1" outlineLevel="3">
@@ -7442,13 +7442,13 @@
         <v>125337</v>
       </c>
       <c r="E101" s="80" t="n">
-        <v>51289</v>
+        <v>50004</v>
       </c>
       <c r="F101" s="81" t="n">
-        <v>74048</v>
+        <v>75333</v>
       </c>
       <c r="G101" s="82" t="n">
-        <v>0.21611631533911</v>
+        <v>0.2198658406168538</v>
       </c>
     </row>
     <row r="102" hidden="1" outlineLevel="4">
@@ -7467,13 +7467,13 @@
         <v>125337</v>
       </c>
       <c r="E102" s="80" t="n">
-        <v>51289</v>
+        <v>50004</v>
       </c>
       <c r="F102" s="81" t="n">
-        <v>74048</v>
+        <v>75333</v>
       </c>
       <c r="G102" s="82" t="n">
-        <v>0.21611631533911</v>
+        <v>0.2198658406168538</v>
       </c>
     </row>
     <row r="103" hidden="1" outlineLevel="3">
@@ -7492,13 +7492,13 @@
         <v>122666</v>
       </c>
       <c r="E103" s="80" t="n">
-        <v>50198</v>
+        <v>48941</v>
       </c>
       <c r="F103" s="81" t="n">
-        <v>72468</v>
+        <v>73726</v>
       </c>
       <c r="G103" s="82" t="n">
-        <v>0.234434725048828</v>
+        <v>0.2385022904170948</v>
       </c>
     </row>
     <row r="104" hidden="1" outlineLevel="4">
@@ -7517,13 +7517,13 @@
         <v>122666</v>
       </c>
       <c r="E104" s="80" t="n">
-        <v>50198</v>
+        <v>48941</v>
       </c>
       <c r="F104" s="81" t="n">
-        <v>72468</v>
+        <v>73726</v>
       </c>
       <c r="G104" s="82" t="n">
-        <v>0.234434725048828</v>
+        <v>0.2385022904170948</v>
       </c>
     </row>
     <row r="105" hidden="1" outlineLevel="3">
@@ -7542,13 +7542,13 @@
         <v>118500</v>
       </c>
       <c r="E105" s="80" t="n">
-        <v>49107</v>
+        <v>47877</v>
       </c>
       <c r="F105" s="81" t="n">
-        <v>69394</v>
+        <v>70624</v>
       </c>
       <c r="G105" s="82" t="n">
-        <v>0.2294761616717864</v>
+        <v>0.2335437270400531</v>
       </c>
     </row>
     <row r="106" hidden="1" outlineLevel="4">
@@ -7567,13 +7567,13 @@
         <v>118500</v>
       </c>
       <c r="E106" s="80" t="n">
-        <v>49107</v>
+        <v>47877</v>
       </c>
       <c r="F106" s="81" t="n">
-        <v>69394</v>
+        <v>70624</v>
       </c>
       <c r="G106" s="82" t="n">
-        <v>0.2294761616717864</v>
+        <v>0.2335437270400531</v>
       </c>
     </row>
     <row r="107" hidden="1" outlineLevel="2">
@@ -7592,13 +7592,13 @@
         <v>304571</v>
       </c>
       <c r="E107" s="80" t="n">
-        <v>101487</v>
+        <v>98945</v>
       </c>
       <c r="F107" s="81" t="n">
-        <v>203084</v>
+        <v>205626</v>
       </c>
       <c r="G107" s="82" t="n">
-        <v>0.3013878802245863</v>
+        <v>0.3051604425215336</v>
       </c>
     </row>
     <row r="108" hidden="1" outlineLevel="3">
@@ -7617,13 +7617,13 @@
         <v>151203</v>
       </c>
       <c r="E108" s="80" t="n">
-        <v>51289</v>
+        <v>50004</v>
       </c>
       <c r="F108" s="81" t="n">
-        <v>99914</v>
+        <v>101198</v>
       </c>
       <c r="G108" s="82" t="n">
-        <v>0.2916083913394601</v>
+        <v>0.295357916617204</v>
       </c>
     </row>
     <row r="109" hidden="1" outlineLevel="4">
@@ -7642,13 +7642,13 @@
         <v>151203</v>
       </c>
       <c r="E109" s="80" t="n">
-        <v>51289</v>
+        <v>50004</v>
       </c>
       <c r="F109" s="81" t="n">
-        <v>99914</v>
+        <v>101198</v>
       </c>
       <c r="G109" s="82" t="n">
-        <v>0.2916083913394601</v>
+        <v>0.295357916617204</v>
       </c>
     </row>
     <row r="110" hidden="1" outlineLevel="3">
@@ -7667,13 +7667,13 @@
         <v>153368</v>
       </c>
       <c r="E110" s="80" t="n">
-        <v>50198</v>
+        <v>48941</v>
       </c>
       <c r="F110" s="81" t="n">
-        <v>103170</v>
+        <v>104428</v>
       </c>
       <c r="G110" s="82" t="n">
-        <v>0.3115048677750414</v>
+        <v>0.3153012621187571</v>
       </c>
     </row>
     <row r="111" hidden="1" outlineLevel="4">
@@ -7692,13 +7692,13 @@
         <v>153368</v>
       </c>
       <c r="E111" s="80" t="n">
-        <v>50198</v>
+        <v>48941</v>
       </c>
       <c r="F111" s="81" t="n">
-        <v>103170</v>
+        <v>104428</v>
       </c>
       <c r="G111" s="82" t="n">
-        <v>0.3115048677750414</v>
+        <v>0.3153012621187571</v>
       </c>
     </row>
     <row r="112">
@@ -7717,13 +7717,13 @@
         <v>883393</v>
       </c>
       <c r="E112" s="70" t="n">
-        <v>445453</v>
+        <v>434295</v>
       </c>
       <c r="F112" s="71" t="n">
-        <v>437940</v>
+        <v>449098</v>
       </c>
       <c r="G112" s="72" t="n">
-        <v>0.1695600875549878</v>
+        <v>0.1738801229545905</v>
       </c>
     </row>
     <row r="113" outlineLevel="1">
@@ -7742,13 +7742,13 @@
         <v>253732</v>
       </c>
       <c r="E113" s="75" t="n">
-        <v>134810</v>
+        <v>131434</v>
       </c>
       <c r="F113" s="76" t="n">
-        <v>118922</v>
+        <v>122298</v>
       </c>
       <c r="G113" s="77" t="n">
-        <v>0.152141653722489</v>
+        <v>0.1564616891220917</v>
       </c>
     </row>
     <row r="114" hidden="1" outlineLevel="2">
@@ -7767,13 +7767,13 @@
         <v>253732</v>
       </c>
       <c r="E114" s="80" t="n">
-        <v>134810</v>
+        <v>131434</v>
       </c>
       <c r="F114" s="81" t="n">
-        <v>118922</v>
+        <v>122298</v>
       </c>
       <c r="G114" s="82" t="n">
-        <v>0.152141653722489</v>
+        <v>0.1564616891220917</v>
       </c>
     </row>
     <row r="115" hidden="1" outlineLevel="3">
@@ -7792,13 +7792,13 @@
         <v>80869</v>
       </c>
       <c r="E115" s="80" t="n">
-        <v>46089</v>
+        <v>44935</v>
       </c>
       <c r="F115" s="81" t="n">
-        <v>34780</v>
+        <v>35935</v>
       </c>
       <c r="G115" s="82" t="n">
-        <v>0.1290070108704044</v>
+        <v>0.1332890820237426</v>
       </c>
     </row>
     <row r="116" hidden="1" outlineLevel="4">
@@ -7817,13 +7817,13 @@
         <v>80869</v>
       </c>
       <c r="E116" s="80" t="n">
-        <v>46089</v>
+        <v>44935</v>
       </c>
       <c r="F116" s="81" t="n">
-        <v>34780</v>
+        <v>35935</v>
       </c>
       <c r="G116" s="82" t="n">
-        <v>0.1290070108704044</v>
+        <v>0.1332890820237426</v>
       </c>
     </row>
     <row r="117" hidden="1" outlineLevel="3">
@@ -7842,13 +7842,13 @@
         <v>88437</v>
       </c>
       <c r="E117" s="80" t="n">
-        <v>44937</v>
+        <v>43811</v>
       </c>
       <c r="F117" s="81" t="n">
-        <v>43500</v>
+        <v>44625</v>
       </c>
       <c r="G117" s="82" t="n">
-        <v>0.1677263975736566</v>
+        <v>0.1720664215696717</v>
       </c>
     </row>
     <row r="118" hidden="1" outlineLevel="4">
@@ -7867,13 +7867,13 @@
         <v>88437</v>
       </c>
       <c r="E118" s="80" t="n">
-        <v>44937</v>
+        <v>43811</v>
       </c>
       <c r="F118" s="81" t="n">
-        <v>43500</v>
+        <v>44625</v>
       </c>
       <c r="G118" s="82" t="n">
-        <v>0.1677263975736566</v>
+        <v>0.1720664215696717</v>
       </c>
     </row>
     <row r="119" hidden="1" outlineLevel="3">
@@ -7892,13 +7892,13 @@
         <v>84426</v>
       </c>
       <c r="E119" s="80" t="n">
-        <v>43785</v>
+        <v>42688</v>
       </c>
       <c r="F119" s="81" t="n">
-        <v>40641</v>
+        <v>41738</v>
       </c>
       <c r="G119" s="82" t="n">
-        <v>0.1608286200664607</v>
+        <v>0.1651686440624757</v>
       </c>
     </row>
     <row r="120" hidden="1" outlineLevel="4">
@@ -7917,13 +7917,13 @@
         <v>84426</v>
       </c>
       <c r="E120" s="80" t="n">
-        <v>43785</v>
+        <v>42688</v>
       </c>
       <c r="F120" s="81" t="n">
-        <v>40641</v>
+        <v>41738</v>
       </c>
       <c r="G120" s="82" t="n">
-        <v>0.1608286200664607</v>
+        <v>0.1651686440624757</v>
       </c>
     </row>
     <row r="121" outlineLevel="1">
@@ -7942,13 +7942,13 @@
         <v>375684</v>
       </c>
       <c r="E121" s="75" t="n">
-        <v>175832</v>
+        <v>171428</v>
       </c>
       <c r="F121" s="76" t="n">
-        <v>199852</v>
+        <v>204256</v>
       </c>
       <c r="G121" s="77" t="n">
-        <v>0.1960291779035364</v>
+        <v>0.2003492133031391</v>
       </c>
     </row>
     <row r="122" hidden="1" outlineLevel="2">
@@ -7967,13 +7967,13 @@
         <v>375684</v>
       </c>
       <c r="E122" s="80" t="n">
-        <v>175832</v>
+        <v>171428</v>
       </c>
       <c r="F122" s="81" t="n">
-        <v>199852</v>
+        <v>204256</v>
       </c>
       <c r="G122" s="82" t="n">
-        <v>0.1960291779035364</v>
+        <v>0.2003492133031391</v>
       </c>
     </row>
     <row r="123" hidden="1" outlineLevel="3">
@@ -7992,13 +7992,13 @@
         <v>120788</v>
       </c>
       <c r="E123" s="80" t="n">
-        <v>60632</v>
+        <v>59113</v>
       </c>
       <c r="F123" s="81" t="n">
-        <v>60156</v>
+        <v>61675</v>
       </c>
       <c r="G123" s="82" t="n">
-        <v>0.1696935429917372</v>
+        <v>0.1739776498833231</v>
       </c>
     </row>
     <row r="124" hidden="1" outlineLevel="4">
@@ -8017,13 +8017,13 @@
         <v>120788</v>
       </c>
       <c r="E124" s="80" t="n">
-        <v>60632</v>
+        <v>59113</v>
       </c>
       <c r="F124" s="81" t="n">
-        <v>60156</v>
+        <v>61675</v>
       </c>
       <c r="G124" s="82" t="n">
-        <v>0.1696935429917372</v>
+        <v>0.1739776498833231</v>
       </c>
     </row>
     <row r="125" hidden="1" outlineLevel="3">
@@ -8042,13 +8042,13 @@
         <v>129568</v>
       </c>
       <c r="E125" s="80" t="n">
-        <v>58207</v>
+        <v>56749</v>
       </c>
       <c r="F125" s="81" t="n">
-        <v>71361</v>
+        <v>72819</v>
       </c>
       <c r="G125" s="82" t="n">
-        <v>0.2123851980682976</v>
+        <v>0.216724386334204</v>
       </c>
     </row>
     <row r="126" hidden="1" outlineLevel="4">
@@ -8067,13 +8067,13 @@
         <v>129568</v>
       </c>
       <c r="E126" s="80" t="n">
-        <v>58207</v>
+        <v>56749</v>
       </c>
       <c r="F126" s="81" t="n">
-        <v>71361</v>
+        <v>72819</v>
       </c>
       <c r="G126" s="82" t="n">
-        <v>0.2123851980682976</v>
+        <v>0.216724386334204</v>
       </c>
     </row>
     <row r="127" hidden="1" outlineLevel="3">
@@ -8092,13 +8092,13 @@
         <v>125328</v>
       </c>
       <c r="E127" s="80" t="n">
-        <v>56994</v>
+        <v>55566</v>
       </c>
       <c r="F127" s="81" t="n">
-        <v>68334</v>
+        <v>69762</v>
       </c>
       <c r="G127" s="82" t="n">
-        <v>0.2077020040460078</v>
+        <v>0.2120411923119142</v>
       </c>
     </row>
     <row r="128" hidden="1" outlineLevel="4">
@@ -8117,13 +8117,13 @@
         <v>125328</v>
       </c>
       <c r="E128" s="80" t="n">
-        <v>56994</v>
+        <v>55566</v>
       </c>
       <c r="F128" s="81" t="n">
-        <v>68334</v>
+        <v>69762</v>
       </c>
       <c r="G128" s="82" t="n">
-        <v>0.2077020040460078</v>
+        <v>0.2120411923119142</v>
       </c>
     </row>
     <row r="129" outlineLevel="1">
@@ -8142,13 +8142,13 @@
         <v>253977</v>
       </c>
       <c r="E129" s="75" t="n">
-        <v>134810</v>
+        <v>131434</v>
       </c>
       <c r="F129" s="76" t="n">
-        <v>119167</v>
+        <v>122543</v>
       </c>
       <c r="G129" s="77" t="n">
-        <v>0.1524550932414553</v>
+        <v>0.156775128641058</v>
       </c>
     </row>
     <row r="130" hidden="1" outlineLevel="2">
@@ -8167,13 +8167,13 @@
         <v>253977</v>
       </c>
       <c r="E130" s="80" t="n">
-        <v>134810</v>
+        <v>131434</v>
       </c>
       <c r="F130" s="81" t="n">
-        <v>119167</v>
+        <v>122543</v>
       </c>
       <c r="G130" s="82" t="n">
-        <v>0.1524550932414553</v>
+        <v>0.156775128641058</v>
       </c>
     </row>
     <row r="131" hidden="1" outlineLevel="3">
@@ -8192,13 +8192,13 @@
         <v>81114</v>
       </c>
       <c r="E131" s="80" t="n">
-        <v>46089</v>
+        <v>44935</v>
       </c>
       <c r="F131" s="81" t="n">
-        <v>35025</v>
+        <v>36180</v>
       </c>
       <c r="G131" s="82" t="n">
-        <v>0.1299157645796032</v>
+        <v>0.1341978357329414</v>
       </c>
     </row>
     <row r="132" hidden="1" outlineLevel="4">
@@ -8217,13 +8217,13 @@
         <v>81114</v>
       </c>
       <c r="E132" s="80" t="n">
-        <v>46089</v>
+        <v>44935</v>
       </c>
       <c r="F132" s="81" t="n">
-        <v>35025</v>
+        <v>36180</v>
       </c>
       <c r="G132" s="82" t="n">
-        <v>0.1299157645796032</v>
+        <v>0.1341978357329414</v>
       </c>
     </row>
     <row r="133" hidden="1" outlineLevel="3">
@@ -8242,13 +8242,13 @@
         <v>88437</v>
       </c>
       <c r="E133" s="80" t="n">
-        <v>44937</v>
+        <v>43811</v>
       </c>
       <c r="F133" s="81" t="n">
-        <v>43500</v>
+        <v>44625</v>
       </c>
       <c r="G133" s="82" t="n">
-        <v>0.1677263975736566</v>
+        <v>0.1720664215696717</v>
       </c>
     </row>
     <row r="134" hidden="1" outlineLevel="4">
@@ -8267,13 +8267,13 @@
         <v>88437</v>
       </c>
       <c r="E134" s="80" t="n">
-        <v>44937</v>
+        <v>43811</v>
       </c>
       <c r="F134" s="81" t="n">
-        <v>43500</v>
+        <v>44625</v>
       </c>
       <c r="G134" s="82" t="n">
-        <v>0.1677263975736566</v>
+        <v>0.1720664215696717</v>
       </c>
     </row>
     <row r="135" hidden="1" outlineLevel="3">
@@ -8292,13 +8292,13 @@
         <v>84426</v>
       </c>
       <c r="E135" s="80" t="n">
-        <v>43785</v>
+        <v>42688</v>
       </c>
       <c r="F135" s="81" t="n">
-        <v>40641</v>
+        <v>41738</v>
       </c>
       <c r="G135" s="82" t="n">
-        <v>0.1608286200664607</v>
+        <v>0.1651686440624757</v>
       </c>
     </row>
     <row r="136" hidden="1" outlineLevel="4">
@@ -8317,13 +8317,13 @@
         <v>84426</v>
       </c>
       <c r="E136" s="80" t="n">
-        <v>43785</v>
+        <v>42688</v>
       </c>
       <c r="F136" s="81" t="n">
-        <v>40641</v>
+        <v>41738</v>
       </c>
       <c r="G136" s="82" t="n">
-        <v>0.1608286200664607</v>
+        <v>0.1651686440624757</v>
       </c>
     </row>
     <row r="137">
@@ -8333,22 +8333,22 @@
         </is>
       </c>
       <c r="B137" s="69" t="n">
-        <v>324</v>
+        <v>402</v>
       </c>
       <c r="C137" s="70" t="n">
-        <v>2152220</v>
+        <v>2706480</v>
       </c>
       <c r="D137" s="70" t="n">
-        <v>452323</v>
+        <v>1006583</v>
       </c>
       <c r="E137" s="70" t="n">
-        <v>380810</v>
-      </c>
-      <c r="F137" s="89" t="n">
-        <v>71513</v>
-      </c>
-      <c r="G137" s="90" t="n">
-        <v>0.03322773657408915</v>
+        <v>460651</v>
+      </c>
+      <c r="F137" s="71" t="n">
+        <v>545932</v>
+      </c>
+      <c r="G137" s="72" t="n">
+        <v>0.2017128975380232</v>
       </c>
     </row>
     <row r="138" outlineLevel="1">
@@ -8358,22 +8358,22 @@
         </is>
       </c>
       <c r="B138" s="74" t="n">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="C138" s="75" t="n">
-        <v>901790</v>
+        <v>1132650</v>
       </c>
       <c r="D138" s="75" t="n">
-        <v>122697</v>
+        <v>353557</v>
       </c>
       <c r="E138" s="75" t="n">
-        <v>159561</v>
-      </c>
-      <c r="F138" s="87" t="n">
-        <v>-36864</v>
-      </c>
-      <c r="G138" s="88" t="n">
-        <v>-0.0408786527493479</v>
+        <v>192780</v>
+      </c>
+      <c r="F138" s="76" t="n">
+        <v>160777</v>
+      </c>
+      <c r="G138" s="77" t="n">
+        <v>0.141947244301042</v>
       </c>
     </row>
     <row r="139" hidden="1" outlineLevel="2">
@@ -8383,22 +8383,22 @@
         </is>
       </c>
       <c r="B139" s="79" t="n">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="C139" s="80" t="n">
-        <v>485330</v>
+        <v>716190</v>
       </c>
       <c r="D139" s="80" t="n">
-        <v>124289</v>
+        <v>280895</v>
       </c>
       <c r="E139" s="80" t="n">
-        <v>79780</v>
+        <v>115011</v>
       </c>
       <c r="F139" s="81" t="n">
-        <v>44509</v>
+        <v>165884</v>
       </c>
       <c r="G139" s="82" t="n">
-        <v>0.09170826881888799</v>
+        <v>0.2316201505737618</v>
       </c>
     </row>
     <row r="140" hidden="1" outlineLevel="3">
@@ -8414,16 +8414,16 @@
         <v>247680</v>
       </c>
       <c r="D140" s="80" t="n">
-        <v>60078</v>
+        <v>92695</v>
       </c>
       <c r="E140" s="80" t="n">
-        <v>40452</v>
+        <v>39432</v>
       </c>
       <c r="F140" s="81" t="n">
-        <v>19626</v>
+        <v>53262</v>
       </c>
       <c r="G140" s="82" t="n">
-        <v>0.079240719550255</v>
+        <v>0.2150446515735042</v>
       </c>
     </row>
     <row r="141" hidden="1" outlineLevel="4">
@@ -8439,22 +8439,22 @@
         <v>247680</v>
       </c>
       <c r="D141" s="80" t="n">
-        <v>60078</v>
+        <v>92695</v>
       </c>
       <c r="E141" s="80" t="n">
-        <v>40452</v>
+        <v>39432</v>
       </c>
       <c r="F141" s="81" t="n">
-        <v>19626</v>
+        <v>53262</v>
       </c>
       <c r="G141" s="82" t="n">
-        <v>0.079240719550255</v>
+        <v>0.2150446515735042</v>
       </c>
     </row>
     <row r="142" hidden="1" outlineLevel="3">
       <c r="A142" s="83" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="B142" s="79" t="n">
@@ -8464,16 +8464,16 @@
         <v>237650</v>
       </c>
       <c r="D142" s="80" t="n">
-        <v>64211</v>
+        <v>96213</v>
       </c>
       <c r="E142" s="80" t="n">
-        <v>39328</v>
+        <v>38337</v>
       </c>
       <c r="F142" s="81" t="n">
-        <v>24882</v>
+        <v>57876</v>
       </c>
       <c r="G142" s="82" t="n">
-        <v>0.1047020100469756</v>
+        <v>0.243534659708847</v>
       </c>
     </row>
     <row r="143" hidden="1" outlineLevel="4">
@@ -8489,116 +8489,116 @@
         <v>237650</v>
       </c>
       <c r="D143" s="80" t="n">
-        <v>64211</v>
+        <v>96213</v>
       </c>
       <c r="E143" s="80" t="n">
-        <v>39328</v>
+        <v>38337</v>
       </c>
       <c r="F143" s="81" t="n">
-        <v>24882</v>
+        <v>57876</v>
       </c>
       <c r="G143" s="82" t="n">
-        <v>0.1047020100469756</v>
-      </c>
-    </row>
-    <row r="144" hidden="1" outlineLevel="2">
-      <c r="A144" s="78" t="inlineStr">
+        <v>0.243534659708847</v>
+      </c>
+    </row>
+    <row r="144" hidden="1" outlineLevel="3">
+      <c r="A144" s="83" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B144" s="79" t="n">
+        <v>34</v>
+      </c>
+      <c r="C144" s="80" t="n">
+        <v>230860</v>
+      </c>
+      <c r="D144" s="80" t="n">
+        <v>91987</v>
+      </c>
+      <c r="E144" s="80" t="n">
+        <v>37242</v>
+      </c>
+      <c r="F144" s="81" t="n">
+        <v>54746</v>
+      </c>
+      <c r="G144" s="82" t="n">
+        <v>0.2371383715580415</v>
+      </c>
+    </row>
+    <row r="145" hidden="1" outlineLevel="4">
+      <c r="A145" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
+        </is>
+      </c>
+      <c r="B145" s="79" t="n">
+        <v>34</v>
+      </c>
+      <c r="C145" s="80" t="n">
+        <v>230860</v>
+      </c>
+      <c r="D145" s="80" t="n">
+        <v>91987</v>
+      </c>
+      <c r="E145" s="80" t="n">
+        <v>37242</v>
+      </c>
+      <c r="F145" s="81" t="n">
+        <v>54746</v>
+      </c>
+      <c r="G145" s="82" t="n">
+        <v>0.2371383715580415</v>
+      </c>
+    </row>
+    <row r="146" hidden="1" outlineLevel="2">
+      <c r="A146" s="78" t="inlineStr">
         <is>
           <t>BTS_GES</t>
         </is>
       </c>
-      <c r="B144" s="79" t="n">
+      <c r="B146" s="79" t="n">
         <v>71</v>
       </c>
-      <c r="C144" s="80" t="n">
+      <c r="C146" s="80" t="n">
         <v>416460</v>
       </c>
-      <c r="D144" s="80" t="n">
-        <v>-1592</v>
-      </c>
-      <c r="E144" s="80" t="n">
-        <v>79780</v>
-      </c>
-      <c r="F144" s="85" t="n">
-        <v>-81373</v>
-      </c>
-      <c r="G144" s="86" t="n">
-        <v>-0.1953914766573149</v>
-      </c>
-    </row>
-    <row r="145" hidden="1" outlineLevel="3">
-      <c r="A145" s="83" t="inlineStr">
-        <is>
-          <t>BTS1</t>
-        </is>
-      </c>
-      <c r="B145" s="79" t="n">
-        <v>36</v>
-      </c>
-      <c r="C145" s="80" t="n">
-        <v>212760</v>
-      </c>
-      <c r="D145" s="80" t="n">
-        <v>-3347</v>
-      </c>
-      <c r="E145" s="80" t="n">
-        <v>40452</v>
-      </c>
-      <c r="F145" s="85" t="n">
-        <v>-43799</v>
-      </c>
-      <c r="G145" s="86" t="n">
-        <v>-0.2058630044138041</v>
-      </c>
-    </row>
-    <row r="146" hidden="1" outlineLevel="4">
-      <c r="A146" s="84" t="inlineStr">
-        <is>
-          <t>Alternance</t>
-        </is>
-      </c>
-      <c r="B146" s="79" t="n">
-        <v>36</v>
-      </c>
-      <c r="C146" s="80" t="n">
-        <v>212760</v>
-      </c>
       <c r="D146" s="80" t="n">
-        <v>-3347</v>
+        <v>72662</v>
       </c>
       <c r="E146" s="80" t="n">
-        <v>40452</v>
+        <v>77769</v>
       </c>
       <c r="F146" s="85" t="n">
-        <v>-43799</v>
+        <v>-5107</v>
       </c>
       <c r="G146" s="86" t="n">
-        <v>-0.2058630044138041</v>
+        <v>-0.01226405748894793</v>
       </c>
     </row>
     <row r="147" hidden="1" outlineLevel="3">
       <c r="A147" s="83" t="inlineStr">
         <is>
-          <t>BTS2</t>
+          <t>BTS1</t>
         </is>
       </c>
       <c r="B147" s="79" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C147" s="80" t="n">
-        <v>203700</v>
+        <v>212760</v>
       </c>
       <c r="D147" s="80" t="n">
-        <v>1755</v>
+        <v>34087</v>
       </c>
       <c r="E147" s="80" t="n">
-        <v>39328</v>
+        <v>39432</v>
       </c>
       <c r="F147" s="85" t="n">
-        <v>-37573</v>
+        <v>-5346</v>
       </c>
       <c r="G147" s="86" t="n">
-        <v>-0.1844542049564281</v>
+        <v>-0.02512512210925279</v>
       </c>
     </row>
     <row r="148" hidden="1" outlineLevel="4">
@@ -8608,147 +8608,147 @@
         </is>
       </c>
       <c r="B148" s="79" t="n">
+        <v>36</v>
+      </c>
+      <c r="C148" s="80" t="n">
+        <v>212760</v>
+      </c>
+      <c r="D148" s="80" t="n">
+        <v>34087</v>
+      </c>
+      <c r="E148" s="80" t="n">
+        <v>39432</v>
+      </c>
+      <c r="F148" s="85" t="n">
+        <v>-5346</v>
+      </c>
+      <c r="G148" s="86" t="n">
+        <v>-0.02512512210925279</v>
+      </c>
+    </row>
+    <row r="149" hidden="1" outlineLevel="3">
+      <c r="A149" s="83" t="inlineStr">
+        <is>
+          <t>BTS2</t>
+        </is>
+      </c>
+      <c r="B149" s="79" t="n">
         <v>35</v>
       </c>
-      <c r="C148" s="80" t="n">
+      <c r="C149" s="80" t="n">
         <v>203700</v>
       </c>
-      <c r="D148" s="80" t="n">
-        <v>1755</v>
-      </c>
-      <c r="E148" s="80" t="n">
-        <v>39328</v>
-      </c>
-      <c r="F148" s="85" t="n">
-        <v>-37573</v>
-      </c>
-      <c r="G148" s="86" t="n">
-        <v>-0.1844542049564281</v>
-      </c>
-    </row>
-    <row r="149" outlineLevel="1">
-      <c r="A149" s="73" t="inlineStr">
+      <c r="D149" s="80" t="n">
+        <v>38575</v>
+      </c>
+      <c r="E149" s="80" t="n">
+        <v>38337</v>
+      </c>
+      <c r="F149" s="85" t="n">
+        <v>238</v>
+      </c>
+      <c r="G149" s="86" t="n">
+        <v>0.001169030918592874</v>
+      </c>
+    </row>
+    <row r="150" hidden="1" outlineLevel="4">
+      <c r="A150" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
+        </is>
+      </c>
+      <c r="B150" s="79" t="n">
+        <v>35</v>
+      </c>
+      <c r="C150" s="80" t="n">
+        <v>203700</v>
+      </c>
+      <c r="D150" s="80" t="n">
+        <v>38575</v>
+      </c>
+      <c r="E150" s="80" t="n">
+        <v>38337</v>
+      </c>
+      <c r="F150" s="85" t="n">
+        <v>238</v>
+      </c>
+      <c r="G150" s="86" t="n">
+        <v>0.001169030918592874</v>
+      </c>
+    </row>
+    <row r="151" outlineLevel="1">
+      <c r="A151" s="73" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="B149" s="74" t="n">
-        <v>182</v>
-      </c>
-      <c r="C149" s="75" t="n">
-        <v>1250430</v>
-      </c>
-      <c r="D149" s="75" t="n">
-        <v>329626</v>
-      </c>
-      <c r="E149" s="75" t="n">
-        <v>221249</v>
-      </c>
-      <c r="F149" s="76" t="n">
-        <v>108377</v>
-      </c>
-      <c r="G149" s="77" t="n">
-        <v>0.08667207238495606</v>
-      </c>
-    </row>
-    <row r="150" hidden="1" outlineLevel="2">
-      <c r="A150" s="78" t="inlineStr">
+      <c r="B151" s="74" t="n">
+        <v>226</v>
+      </c>
+      <c r="C151" s="75" t="n">
+        <v>1573830</v>
+      </c>
+      <c r="D151" s="75" t="n">
+        <v>653026</v>
+      </c>
+      <c r="E151" s="75" t="n">
+        <v>267871</v>
+      </c>
+      <c r="F151" s="76" t="n">
+        <v>385155</v>
+      </c>
+      <c r="G151" s="77" t="n">
+        <v>0.24472489193314</v>
+      </c>
+    </row>
+    <row r="152" hidden="1" outlineLevel="2">
+      <c r="A152" s="78" t="inlineStr">
         <is>
           <t>BAC_RH</t>
         </is>
       </c>
-      <c r="B150" s="79" t="n">
-        <v>91</v>
-      </c>
-      <c r="C150" s="80" t="n">
-        <v>672990</v>
-      </c>
-      <c r="D150" s="80" t="n">
-        <v>242394</v>
-      </c>
-      <c r="E150" s="80" t="n">
-        <v>110624</v>
-      </c>
-      <c r="F150" s="81" t="n">
-        <v>131770</v>
-      </c>
-      <c r="G150" s="82" t="n">
-        <v>0.195797230332167</v>
-      </c>
-    </row>
-    <row r="151" hidden="1" outlineLevel="3">
-      <c r="A151" s="83" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B151" s="79" t="n">
-        <v>46</v>
-      </c>
-      <c r="C151" s="80" t="n">
-        <v>342240</v>
-      </c>
-      <c r="D151" s="80" t="n">
-        <v>116238</v>
-      </c>
-      <c r="E151" s="80" t="n">
-        <v>55920</v>
-      </c>
-      <c r="F151" s="81" t="n">
-        <v>60318</v>
-      </c>
-      <c r="G151" s="82" t="n">
-        <v>0.1762454996154851</v>
-      </c>
-    </row>
-    <row r="152" hidden="1" outlineLevel="4">
-      <c r="A152" s="84" t="inlineStr">
-        <is>
-          <t>Alternance</t>
-        </is>
-      </c>
       <c r="B152" s="79" t="n">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="C152" s="80" t="n">
-        <v>342240</v>
+        <v>996390</v>
       </c>
       <c r="D152" s="80" t="n">
-        <v>116238</v>
+        <v>478789</v>
       </c>
       <c r="E152" s="80" t="n">
-        <v>55920</v>
+        <v>160011</v>
       </c>
       <c r="F152" s="81" t="n">
-        <v>60318</v>
+        <v>318778</v>
       </c>
       <c r="G152" s="82" t="n">
-        <v>0.1762454996154851</v>
+        <v>0.3199330390007451</v>
       </c>
     </row>
     <row r="153" hidden="1" outlineLevel="3">
       <c r="A153" s="83" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B153" s="79" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C153" s="80" t="n">
-        <v>330750</v>
+        <v>342240</v>
       </c>
       <c r="D153" s="80" t="n">
-        <v>126156</v>
+        <v>155005</v>
       </c>
       <c r="E153" s="80" t="n">
-        <v>54704</v>
+        <v>54522</v>
       </c>
       <c r="F153" s="81" t="n">
-        <v>71451</v>
+        <v>100482</v>
       </c>
       <c r="G153" s="82" t="n">
-        <v>0.2160281731000497</v>
+        <v>0.293602440036657</v>
       </c>
     </row>
     <row r="154" hidden="1" outlineLevel="4">
@@ -8758,347 +8758,347 @@
         </is>
       </c>
       <c r="B154" s="79" t="n">
+        <v>46</v>
+      </c>
+      <c r="C154" s="80" t="n">
+        <v>342240</v>
+      </c>
+      <c r="D154" s="80" t="n">
+        <v>155005</v>
+      </c>
+      <c r="E154" s="80" t="n">
+        <v>54522</v>
+      </c>
+      <c r="F154" s="81" t="n">
+        <v>100482</v>
+      </c>
+      <c r="G154" s="82" t="n">
+        <v>0.293602440036657</v>
+      </c>
+    </row>
+    <row r="155" hidden="1" outlineLevel="3">
+      <c r="A155" s="83" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B155" s="79" t="n">
         <v>45</v>
       </c>
-      <c r="C154" s="80" t="n">
+      <c r="C155" s="80" t="n">
         <v>330750</v>
       </c>
-      <c r="D154" s="80" t="n">
-        <v>126156</v>
-      </c>
-      <c r="E154" s="80" t="n">
-        <v>54704</v>
-      </c>
-      <c r="F154" s="81" t="n">
-        <v>71451</v>
-      </c>
-      <c r="G154" s="82" t="n">
-        <v>0.2160281731000497</v>
-      </c>
-    </row>
-    <row r="155" hidden="1" outlineLevel="2">
-      <c r="A155" s="78" t="inlineStr">
+      <c r="D155" s="80" t="n">
+        <v>164318</v>
+      </c>
+      <c r="E155" s="80" t="n">
+        <v>53337</v>
+      </c>
+      <c r="F155" s="81" t="n">
+        <v>110981</v>
+      </c>
+      <c r="G155" s="82" t="n">
+        <v>0.3355445510002041</v>
+      </c>
+    </row>
+    <row r="156" hidden="1" outlineLevel="4">
+      <c r="A156" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
+        </is>
+      </c>
+      <c r="B156" s="79" t="n">
+        <v>45</v>
+      </c>
+      <c r="C156" s="80" t="n">
+        <v>330750</v>
+      </c>
+      <c r="D156" s="80" t="n">
+        <v>164318</v>
+      </c>
+      <c r="E156" s="80" t="n">
+        <v>53337</v>
+      </c>
+      <c r="F156" s="81" t="n">
+        <v>110981</v>
+      </c>
+      <c r="G156" s="82" t="n">
+        <v>0.3355445510002041</v>
+      </c>
+    </row>
+    <row r="157" hidden="1" outlineLevel="3">
+      <c r="A157" s="83" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B157" s="79" t="n">
+        <v>44</v>
+      </c>
+      <c r="C157" s="80" t="n">
+        <v>323400</v>
+      </c>
+      <c r="D157" s="80" t="n">
+        <v>159466</v>
+      </c>
+      <c r="E157" s="80" t="n">
+        <v>52152</v>
+      </c>
+      <c r="F157" s="81" t="n">
+        <v>107314</v>
+      </c>
+      <c r="G157" s="82" t="n">
+        <v>0.3318312350293429</v>
+      </c>
+    </row>
+    <row r="158" hidden="1" outlineLevel="4">
+      <c r="A158" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
+        </is>
+      </c>
+      <c r="B158" s="79" t="n">
+        <v>44</v>
+      </c>
+      <c r="C158" s="80" t="n">
+        <v>323400</v>
+      </c>
+      <c r="D158" s="80" t="n">
+        <v>159466</v>
+      </c>
+      <c r="E158" s="80" t="n">
+        <v>52152</v>
+      </c>
+      <c r="F158" s="81" t="n">
+        <v>107314</v>
+      </c>
+      <c r="G158" s="82" t="n">
+        <v>0.3318312350293429</v>
+      </c>
+    </row>
+    <row r="159" hidden="1" outlineLevel="2">
+      <c r="A159" s="78" t="inlineStr">
         <is>
           <t>BTS_GES</t>
         </is>
       </c>
-      <c r="B155" s="79" t="n">
+      <c r="B159" s="79" t="n">
         <v>91</v>
       </c>
-      <c r="C155" s="80" t="n">
+      <c r="C159" s="80" t="n">
         <v>577440</v>
       </c>
-      <c r="D155" s="80" t="n">
-        <v>87232</v>
-      </c>
-      <c r="E155" s="80" t="n">
-        <v>110624</v>
-      </c>
-      <c r="F155" s="85" t="n">
-        <v>-23392</v>
-      </c>
-      <c r="G155" s="86" t="n">
-        <v>-0.04051021503346574</v>
-      </c>
-    </row>
-    <row r="156" hidden="1" outlineLevel="3">
-      <c r="A156" s="83" t="inlineStr">
+      <c r="D159" s="80" t="n">
+        <v>174237</v>
+      </c>
+      <c r="E159" s="80" t="n">
+        <v>107859</v>
+      </c>
+      <c r="F159" s="81" t="n">
+        <v>66377</v>
+      </c>
+      <c r="G159" s="82" t="n">
+        <v>0.11495098355012</v>
+      </c>
+    </row>
+    <row r="160" hidden="1" outlineLevel="3">
+      <c r="A160" s="83" t="inlineStr">
         <is>
           <t>BTS1</t>
         </is>
       </c>
-      <c r="B156" s="79" t="n">
+      <c r="B160" s="79" t="n">
         <v>46</v>
       </c>
-      <c r="C156" s="80" t="n">
+      <c r="C160" s="80" t="n">
         <v>293940</v>
       </c>
-      <c r="D156" s="80" t="n">
-        <v>38132</v>
-      </c>
-      <c r="E156" s="80" t="n">
-        <v>55920</v>
-      </c>
-      <c r="F156" s="85" t="n">
-        <v>-17788</v>
-      </c>
-      <c r="G156" s="86" t="n">
-        <v>-0.06051452172783946</v>
-      </c>
-    </row>
-    <row r="157" hidden="1" outlineLevel="4">
-      <c r="A157" s="84" t="inlineStr">
+      <c r="D160" s="80" t="n">
+        <v>81937</v>
+      </c>
+      <c r="E160" s="80" t="n">
+        <v>54522</v>
+      </c>
+      <c r="F160" s="81" t="n">
+        <v>27414</v>
+      </c>
+      <c r="G160" s="82" t="n">
+        <v>0.09326467098048802</v>
+      </c>
+    </row>
+    <row r="161" hidden="1" outlineLevel="4">
+      <c r="A161" s="84" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B157" s="79" t="n">
+      <c r="B161" s="79" t="n">
         <v>46</v>
       </c>
-      <c r="C157" s="80" t="n">
+      <c r="C161" s="80" t="n">
         <v>293940</v>
       </c>
-      <c r="D157" s="80" t="n">
-        <v>38132</v>
-      </c>
-      <c r="E157" s="80" t="n">
-        <v>55920</v>
-      </c>
-      <c r="F157" s="85" t="n">
-        <v>-17788</v>
-      </c>
-      <c r="G157" s="86" t="n">
-        <v>-0.06051452172783946</v>
-      </c>
-    </row>
-    <row r="158" hidden="1" outlineLevel="3">
-      <c r="A158" s="83" t="inlineStr">
+      <c r="D161" s="80" t="n">
+        <v>81937</v>
+      </c>
+      <c r="E161" s="80" t="n">
+        <v>54522</v>
+      </c>
+      <c r="F161" s="81" t="n">
+        <v>27414</v>
+      </c>
+      <c r="G161" s="82" t="n">
+        <v>0.09326467098048802</v>
+      </c>
+    </row>
+    <row r="162" hidden="1" outlineLevel="3">
+      <c r="A162" s="83" t="inlineStr">
         <is>
           <t>BTS2</t>
         </is>
       </c>
-      <c r="B158" s="79" t="n">
+      <c r="B162" s="79" t="n">
         <v>45</v>
       </c>
-      <c r="C158" s="80" t="n">
+      <c r="C162" s="80" t="n">
         <v>283500</v>
       </c>
-      <c r="D158" s="80" t="n">
-        <v>49100</v>
-      </c>
-      <c r="E158" s="80" t="n">
-        <v>54704</v>
-      </c>
-      <c r="F158" s="85" t="n">
-        <v>-5605</v>
-      </c>
-      <c r="G158" s="86" t="n">
-        <v>-0.01976924180685477</v>
-      </c>
-    </row>
-    <row r="159" hidden="1" outlineLevel="4">
-      <c r="A159" s="84" t="inlineStr">
+      <c r="D162" s="80" t="n">
+        <v>92300</v>
+      </c>
+      <c r="E162" s="80" t="n">
+        <v>53337</v>
+      </c>
+      <c r="F162" s="81" t="n">
+        <v>38963</v>
+      </c>
+      <c r="G162" s="82" t="n">
+        <v>0.1374359031858083</v>
+      </c>
+    </row>
+    <row r="163" hidden="1" outlineLevel="4">
+      <c r="A163" s="84" t="inlineStr">
         <is>
           <t>Alternance</t>
         </is>
       </c>
-      <c r="B159" s="79" t="n">
+      <c r="B163" s="79" t="n">
         <v>45</v>
       </c>
-      <c r="C159" s="80" t="n">
+      <c r="C163" s="80" t="n">
         <v>283500</v>
       </c>
-      <c r="D159" s="80" t="n">
-        <v>49100</v>
-      </c>
-      <c r="E159" s="80" t="n">
-        <v>54704</v>
-      </c>
-      <c r="F159" s="85" t="n">
-        <v>-5605</v>
-      </c>
-      <c r="G159" s="86" t="n">
-        <v>-0.01976924180685477</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="68" t="inlineStr">
+      <c r="D163" s="80" t="n">
+        <v>92300</v>
+      </c>
+      <c r="E163" s="80" t="n">
+        <v>53337</v>
+      </c>
+      <c r="F163" s="81" t="n">
+        <v>38963</v>
+      </c>
+      <c r="G163" s="82" t="n">
+        <v>0.1374359031858083</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="68" t="inlineStr">
         <is>
           <t>Tunon</t>
         </is>
       </c>
-      <c r="B160" s="69" t="n">
+      <c r="B164" s="69" t="n">
         <v>255</v>
       </c>
-      <c r="C160" s="70" t="n">
+      <c r="C164" s="70" t="n">
         <v>1949700</v>
       </c>
-      <c r="D160" s="70" t="n">
+      <c r="D164" s="70" t="n">
         <v>371040</v>
       </c>
-      <c r="E160" s="70" t="n">
-        <v>299711</v>
-      </c>
-      <c r="F160" s="89" t="n">
-        <v>71329</v>
-      </c>
-      <c r="G160" s="90" t="n">
-        <v>0.03658446946636765</v>
-      </c>
-    </row>
-    <row r="161" outlineLevel="1">
-      <c r="A161" s="73" t="inlineStr">
+      <c r="E164" s="70" t="n">
+        <v>292204</v>
+      </c>
+      <c r="F164" s="89" t="n">
+        <v>78836</v>
+      </c>
+      <c r="G164" s="90" t="n">
+        <v>0.04043491746124073</v>
+      </c>
+    </row>
+    <row r="165" outlineLevel="1">
+      <c r="A165" s="73" t="inlineStr">
         <is>
           <t>Lyon</t>
         </is>
       </c>
-      <c r="B161" s="74" t="n">
+      <c r="B165" s="74" t="n">
         <v>117</v>
       </c>
-      <c r="C161" s="75" t="n">
+      <c r="C165" s="75" t="n">
         <v>863550</v>
       </c>
-      <c r="D161" s="75" t="n">
+      <c r="D165" s="75" t="n">
         <v>223752</v>
       </c>
-      <c r="E161" s="75" t="n">
-        <v>132746</v>
-      </c>
-      <c r="F161" s="76" t="n">
-        <v>91006</v>
-      </c>
-      <c r="G161" s="77" t="n">
-        <v>0.105385442387657</v>
-      </c>
-    </row>
-    <row r="162" hidden="1" outlineLevel="2">
-      <c r="A162" s="78" t="inlineStr">
+      <c r="E165" s="75" t="n">
+        <v>129421</v>
+      </c>
+      <c r="F165" s="76" t="n">
+        <v>94331</v>
+      </c>
+      <c r="G165" s="77" t="n">
+        <v>0.1092358903825301</v>
+      </c>
+    </row>
+    <row r="166" hidden="1" outlineLevel="2">
+      <c r="A166" s="78" t="inlineStr">
         <is>
           <t>BAC_TOU</t>
         </is>
       </c>
-      <c r="B162" s="79" t="n">
+      <c r="B166" s="79" t="n">
         <v>117</v>
       </c>
-      <c r="C162" s="80" t="n">
+      <c r="C166" s="80" t="n">
         <v>863550</v>
       </c>
-      <c r="D162" s="80" t="n">
+      <c r="D166" s="80" t="n">
         <v>223752</v>
       </c>
-      <c r="E162" s="80" t="n">
-        <v>132746</v>
-      </c>
-      <c r="F162" s="81" t="n">
-        <v>91006</v>
-      </c>
-      <c r="G162" s="82" t="n">
-        <v>0.105385442387657</v>
-      </c>
-    </row>
-    <row r="163" hidden="1" outlineLevel="3">
-      <c r="A163" s="83" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B163" s="79" t="n">
-        <v>40</v>
-      </c>
-      <c r="C163" s="80" t="n">
-        <v>297600</v>
-      </c>
-      <c r="D163" s="80" t="n">
-        <v>68510</v>
-      </c>
-      <c r="E163" s="80" t="n">
-        <v>45383</v>
-      </c>
-      <c r="F163" s="81" t="n">
-        <v>23126</v>
-      </c>
-      <c r="G163" s="82" t="n">
-        <v>0.07770930839750617</v>
-      </c>
-    </row>
-    <row r="164" hidden="1" outlineLevel="4">
-      <c r="A164" s="84" t="inlineStr">
-        <is>
-          <t>Alternance</t>
-        </is>
-      </c>
-      <c r="B164" s="79" t="n">
-        <v>40</v>
-      </c>
-      <c r="C164" s="80" t="n">
-        <v>297600</v>
-      </c>
-      <c r="D164" s="80" t="n">
-        <v>68510</v>
-      </c>
-      <c r="E164" s="80" t="n">
-        <v>45383</v>
-      </c>
-      <c r="F164" s="81" t="n">
-        <v>23126</v>
-      </c>
-      <c r="G164" s="82" t="n">
-        <v>0.07770930839750617</v>
-      </c>
-    </row>
-    <row r="165" hidden="1" outlineLevel="3">
-      <c r="A165" s="83" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B165" s="79" t="n">
-        <v>39</v>
-      </c>
-      <c r="C165" s="80" t="n">
-        <v>286650</v>
-      </c>
-      <c r="D165" s="80" t="n">
-        <v>79667</v>
-      </c>
-      <c r="E165" s="80" t="n">
-        <v>44249</v>
-      </c>
-      <c r="F165" s="81" t="n">
-        <v>35419</v>
-      </c>
-      <c r="G165" s="82" t="n">
-        <v>0.1235602055629527</v>
-      </c>
-    </row>
-    <row r="166" hidden="1" outlineLevel="4">
-      <c r="A166" s="84" t="inlineStr">
-        <is>
-          <t>Alternance</t>
-        </is>
-      </c>
-      <c r="B166" s="79" t="n">
-        <v>39</v>
-      </c>
-      <c r="C166" s="80" t="n">
-        <v>286650</v>
-      </c>
-      <c r="D166" s="80" t="n">
-        <v>79667</v>
-      </c>
       <c r="E166" s="80" t="n">
-        <v>44249</v>
+        <v>129421</v>
       </c>
       <c r="F166" s="81" t="n">
-        <v>35419</v>
+        <v>94331</v>
       </c>
       <c r="G166" s="82" t="n">
-        <v>0.1235602055629527</v>
+        <v>0.1092358903825301</v>
       </c>
     </row>
     <row r="167" hidden="1" outlineLevel="3">
       <c r="A167" s="83" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B167" s="79" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C167" s="80" t="n">
-        <v>279300</v>
+        <v>297600</v>
       </c>
       <c r="D167" s="80" t="n">
-        <v>75575</v>
+        <v>68510</v>
       </c>
       <c r="E167" s="80" t="n">
-        <v>43114</v>
+        <v>44247</v>
       </c>
       <c r="F167" s="81" t="n">
-        <v>32461</v>
+        <v>24263</v>
       </c>
       <c r="G167" s="82" t="n">
-        <v>0.1162218964201323</v>
+        <v>0.08152910249498416</v>
       </c>
     </row>
     <row r="168" hidden="1" outlineLevel="4">
@@ -9108,97 +9108,97 @@
         </is>
       </c>
       <c r="B168" s="79" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C168" s="80" t="n">
-        <v>279300</v>
+        <v>297600</v>
       </c>
       <c r="D168" s="80" t="n">
-        <v>75575</v>
+        <v>68510</v>
       </c>
       <c r="E168" s="80" t="n">
-        <v>43114</v>
+        <v>44247</v>
       </c>
       <c r="F168" s="81" t="n">
-        <v>32461</v>
+        <v>24263</v>
       </c>
       <c r="G168" s="82" t="n">
-        <v>0.1162218964201323</v>
-      </c>
-    </row>
-    <row r="169" outlineLevel="1">
-      <c r="A169" s="73" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="B169" s="74" t="n">
-        <v>138</v>
-      </c>
-      <c r="C169" s="75" t="n">
-        <v>1086150</v>
-      </c>
-      <c r="D169" s="75" t="n">
-        <v>147288</v>
-      </c>
-      <c r="E169" s="75" t="n">
-        <v>166965</v>
-      </c>
-      <c r="F169" s="87" t="n">
-        <v>-19677</v>
-      </c>
-      <c r="G169" s="88" t="n">
-        <v>-0.01811615214775505</v>
-      </c>
-    </row>
-    <row r="170" hidden="1" outlineLevel="2">
-      <c r="A170" s="78" t="inlineStr">
-        <is>
-          <t>BAC_TOU</t>
+        <v>0.08152910249498416</v>
+      </c>
+    </row>
+    <row r="169" hidden="1" outlineLevel="3">
+      <c r="A169" s="83" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B169" s="79" t="n">
+        <v>39</v>
+      </c>
+      <c r="C169" s="80" t="n">
+        <v>286650</v>
+      </c>
+      <c r="D169" s="80" t="n">
+        <v>79667</v>
+      </c>
+      <c r="E169" s="80" t="n">
+        <v>43140</v>
+      </c>
+      <c r="F169" s="81" t="n">
+        <v>36527</v>
+      </c>
+      <c r="G169" s="82" t="n">
+        <v>0.1274267726493794</v>
+      </c>
+    </row>
+    <row r="170" hidden="1" outlineLevel="4">
+      <c r="A170" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
         </is>
       </c>
       <c r="B170" s="79" t="n">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="C170" s="80" t="n">
-        <v>1086150</v>
+        <v>286650</v>
       </c>
       <c r="D170" s="80" t="n">
-        <v>147288</v>
+        <v>79667</v>
       </c>
       <c r="E170" s="80" t="n">
-        <v>166965</v>
-      </c>
-      <c r="F170" s="85" t="n">
-        <v>-19677</v>
-      </c>
-      <c r="G170" s="86" t="n">
-        <v>-0.01811615214775505</v>
+        <v>43140</v>
+      </c>
+      <c r="F170" s="81" t="n">
+        <v>36527</v>
+      </c>
+      <c r="G170" s="82" t="n">
+        <v>0.1274267726493794</v>
       </c>
     </row>
     <row r="171" hidden="1" outlineLevel="3">
       <c r="A171" s="83" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="B171" s="79" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C171" s="80" t="n">
-        <v>372710</v>
+        <v>279300</v>
       </c>
       <c r="D171" s="80" t="n">
-        <v>35291</v>
+        <v>75575</v>
       </c>
       <c r="E171" s="80" t="n">
-        <v>56865</v>
-      </c>
-      <c r="F171" s="85" t="n">
-        <v>-21574</v>
-      </c>
-      <c r="G171" s="86" t="n">
-        <v>-0.05788397780607987</v>
+        <v>42034</v>
+      </c>
+      <c r="F171" s="81" t="n">
+        <v>33541</v>
+      </c>
+      <c r="G171" s="82" t="n">
+        <v>0.120088463506559</v>
       </c>
     </row>
     <row r="172" hidden="1" outlineLevel="4">
@@ -9208,97 +9208,97 @@
         </is>
       </c>
       <c r="B172" s="79" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C172" s="80" t="n">
-        <v>372710</v>
+        <v>279300</v>
       </c>
       <c r="D172" s="80" t="n">
-        <v>35291</v>
+        <v>75575</v>
       </c>
       <c r="E172" s="80" t="n">
-        <v>56865</v>
-      </c>
-      <c r="F172" s="85" t="n">
-        <v>-21574</v>
-      </c>
-      <c r="G172" s="86" t="n">
-        <v>-0.05788397780607987</v>
-      </c>
-    </row>
-    <row r="173" hidden="1" outlineLevel="3">
-      <c r="A173" s="83" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B173" s="79" t="n">
-        <v>46</v>
-      </c>
-      <c r="C173" s="80" t="n">
-        <v>360640</v>
-      </c>
-      <c r="D173" s="80" t="n">
-        <v>57766</v>
-      </c>
-      <c r="E173" s="80" t="n">
-        <v>55655</v>
-      </c>
-      <c r="F173" s="85" t="n">
-        <v>2111</v>
-      </c>
-      <c r="G173" s="86" t="n">
-        <v>0.005853613339910389</v>
-      </c>
-    </row>
-    <row r="174" hidden="1" outlineLevel="4">
-      <c r="A174" s="84" t="inlineStr">
-        <is>
-          <t>Alternance</t>
+        <v>42034</v>
+      </c>
+      <c r="F172" s="81" t="n">
+        <v>33541</v>
+      </c>
+      <c r="G172" s="82" t="n">
+        <v>0.120088463506559</v>
+      </c>
+    </row>
+    <row r="173" outlineLevel="1">
+      <c r="A173" s="73" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="B173" s="74" t="n">
+        <v>138</v>
+      </c>
+      <c r="C173" s="75" t="n">
+        <v>1086150</v>
+      </c>
+      <c r="D173" s="75" t="n">
+        <v>147288</v>
+      </c>
+      <c r="E173" s="75" t="n">
+        <v>162783</v>
+      </c>
+      <c r="F173" s="87" t="n">
+        <v>-15495</v>
+      </c>
+      <c r="G173" s="88" t="n">
+        <v>-0.01426570415288199</v>
+      </c>
+    </row>
+    <row r="174" hidden="1" outlineLevel="2">
+      <c r="A174" s="78" t="inlineStr">
+        <is>
+          <t>BAC_TOU</t>
         </is>
       </c>
       <c r="B174" s="79" t="n">
-        <v>46</v>
+        <v>138</v>
       </c>
       <c r="C174" s="80" t="n">
-        <v>360640</v>
+        <v>1086150</v>
       </c>
       <c r="D174" s="80" t="n">
-        <v>57766</v>
+        <v>147288</v>
       </c>
       <c r="E174" s="80" t="n">
-        <v>55655</v>
+        <v>162783</v>
       </c>
       <c r="F174" s="85" t="n">
-        <v>2111</v>
+        <v>-15495</v>
       </c>
       <c r="G174" s="86" t="n">
-        <v>0.005853613339910389</v>
+        <v>-0.01426570415288199</v>
       </c>
     </row>
     <row r="175" hidden="1" outlineLevel="3">
       <c r="A175" s="83" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B175" s="79" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C175" s="80" t="n">
-        <v>352800</v>
+        <v>372710</v>
       </c>
       <c r="D175" s="80" t="n">
-        <v>54231</v>
+        <v>35291</v>
       </c>
       <c r="E175" s="80" t="n">
-        <v>54445</v>
+        <v>55440</v>
       </c>
       <c r="F175" s="85" t="n">
-        <v>-214</v>
+        <v>-20150</v>
       </c>
       <c r="G175" s="86" t="n">
-        <v>-0.0006064864004688316</v>
+        <v>-0.05406234642128962</v>
       </c>
     </row>
     <row r="176" hidden="1" outlineLevel="4">
@@ -9308,47 +9308,147 @@
         </is>
       </c>
       <c r="B176" s="79" t="n">
+        <v>47</v>
+      </c>
+      <c r="C176" s="80" t="n">
+        <v>372710</v>
+      </c>
+      <c r="D176" s="80" t="n">
+        <v>35291</v>
+      </c>
+      <c r="E176" s="80" t="n">
+        <v>55440</v>
+      </c>
+      <c r="F176" s="85" t="n">
+        <v>-20150</v>
+      </c>
+      <c r="G176" s="86" t="n">
+        <v>-0.05406234642128962</v>
+      </c>
+    </row>
+    <row r="177" hidden="1" outlineLevel="3">
+      <c r="A177" s="83" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B177" s="79" t="n">
+        <v>46</v>
+      </c>
+      <c r="C177" s="80" t="n">
+        <v>360640</v>
+      </c>
+      <c r="D177" s="80" t="n">
+        <v>57766</v>
+      </c>
+      <c r="E177" s="80" t="n">
+        <v>54261</v>
+      </c>
+      <c r="F177" s="85" t="n">
+        <v>3505</v>
+      </c>
+      <c r="G177" s="86" t="n">
+        <v>0.009719115493148514</v>
+      </c>
+    </row>
+    <row r="178" hidden="1" outlineLevel="4">
+      <c r="A178" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
+        </is>
+      </c>
+      <c r="B178" s="79" t="n">
+        <v>46</v>
+      </c>
+      <c r="C178" s="80" t="n">
+        <v>360640</v>
+      </c>
+      <c r="D178" s="80" t="n">
+        <v>57766</v>
+      </c>
+      <c r="E178" s="80" t="n">
+        <v>54261</v>
+      </c>
+      <c r="F178" s="85" t="n">
+        <v>3505</v>
+      </c>
+      <c r="G178" s="86" t="n">
+        <v>0.009719115493148514</v>
+      </c>
+    </row>
+    <row r="179" hidden="1" outlineLevel="3">
+      <c r="A179" s="83" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B179" s="79" t="n">
         <v>45</v>
       </c>
-      <c r="C176" s="80" t="n">
+      <c r="C179" s="80" t="n">
         <v>352800</v>
       </c>
-      <c r="D176" s="80" t="n">
+      <c r="D179" s="80" t="n">
         <v>54231</v>
       </c>
-      <c r="E176" s="80" t="n">
-        <v>54445</v>
-      </c>
-      <c r="F176" s="85" t="n">
-        <v>-214</v>
-      </c>
-      <c r="G176" s="86" t="n">
-        <v>-0.0006064864004688316</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="91" t="inlineStr">
+      <c r="E179" s="80" t="n">
+        <v>53081</v>
+      </c>
+      <c r="F179" s="85" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G179" s="86" t="n">
+        <v>0.00325901575276927</v>
+      </c>
+    </row>
+    <row r="180" hidden="1" outlineLevel="4">
+      <c r="A180" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
+        </is>
+      </c>
+      <c r="B180" s="79" t="n">
+        <v>45</v>
+      </c>
+      <c r="C180" s="80" t="n">
+        <v>352800</v>
+      </c>
+      <c r="D180" s="80" t="n">
+        <v>54231</v>
+      </c>
+      <c r="E180" s="80" t="n">
+        <v>53081</v>
+      </c>
+      <c r="F180" s="85" t="n">
+        <v>1150</v>
+      </c>
+      <c r="G180" s="86" t="n">
+        <v>0.00325901575276927</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="91" t="inlineStr">
         <is>
           <t>GROUPE</t>
         </is>
       </c>
-      <c r="B177" s="92" t="n">
-        <v>3036</v>
-      </c>
-      <c r="C177" s="93" t="n">
-        <v>22544725</v>
-      </c>
-      <c r="D177" s="93" t="n">
-        <v>6859857</v>
-      </c>
-      <c r="E177" s="93" t="n">
+      <c r="B181" s="92" t="n">
+        <v>3114</v>
+      </c>
+      <c r="C181" s="93" t="n">
+        <v>23098985</v>
+      </c>
+      <c r="D181" s="93" t="n">
+        <v>7414117</v>
+      </c>
+      <c r="E181" s="93" t="n">
         <v>3568327</v>
       </c>
-      <c r="F177" s="93" t="n">
-        <v>3291530</v>
-      </c>
-      <c r="G177" s="94" t="n">
-        <v>0.1460000066534411</v>
+      <c r="F181" s="93" t="n">
+        <v>3845790</v>
+      </c>
+      <c r="G181" s="94" t="n">
+        <v>0.1664917311301774</v>
       </c>
     </row>
   </sheetData>
@@ -9362,7 +9462,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U178"/>
+  <dimension ref="A1:U182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9716,13 +9816,13 @@
         <v/>
       </c>
       <c r="G21" s="70" t="n">
-        <v>7109004</v>
+        <v>7076881</v>
       </c>
       <c r="H21" s="70" t="n">
-        <v>7469118</v>
+        <v>7434844</v>
       </c>
       <c r="I21" s="70" t="n">
-        <v>7858779</v>
+        <v>7822008</v>
       </c>
       <c r="J21" s="70">
         <f>I21-G21</f>
@@ -9758,13 +9858,13 @@
         </is>
       </c>
       <c r="S21" s="100" t="n">
-        <v>0.1653423945193762</v>
+        <v>0.169113931603426</v>
       </c>
       <c r="T21" s="100" t="n">
-        <v>0.1730749735683474</v>
+        <v>0.1768694665337301</v>
       </c>
       <c r="U21" s="100" t="n">
-        <v>0.1785925824284567</v>
+        <v>0.1824358877166731</v>
       </c>
     </row>
     <row r="22" outlineLevel="1">
@@ -9791,13 +9891,13 @@
         <v/>
       </c>
       <c r="G22" s="75" t="n">
-        <v>1256721</v>
+        <v>1250786</v>
       </c>
       <c r="H22" s="75" t="n">
-        <v>1320088</v>
+        <v>1313763</v>
       </c>
       <c r="I22" s="75" t="n">
-        <v>1390171</v>
+        <v>1383354</v>
       </c>
       <c r="J22" s="75">
         <f>I22-G22</f>
@@ -9833,13 +9933,13 @@
         </is>
       </c>
       <c r="S22" s="100" t="n">
-        <v>0.1444641917808717</v>
+        <v>0.1482705554393484</v>
       </c>
       <c r="T22" s="100" t="n">
-        <v>0.1505317276302517</v>
+        <v>0.1543603321039889</v>
       </c>
       <c r="U22" s="100" t="n">
-        <v>0.1592472957412916</v>
+        <v>0.1631258219347755</v>
       </c>
     </row>
     <row r="23" hidden="1" outlineLevel="2">
@@ -9866,13 +9966,13 @@
         <v/>
       </c>
       <c r="G23" s="80" t="n">
-        <v>767006</v>
+        <v>763461</v>
       </c>
       <c r="H23" s="80" t="n">
-        <v>802449</v>
+        <v>798691</v>
       </c>
       <c r="I23" s="80" t="n">
-        <v>845195</v>
+        <v>841143</v>
       </c>
       <c r="J23" s="80">
         <f>I23-G23</f>
@@ -9908,13 +10008,13 @@
         </is>
       </c>
       <c r="S23" s="100" t="n">
-        <v>0.1601473616620489</v>
+        <v>0.1643868457409177</v>
       </c>
       <c r="T23" s="100" t="n">
-        <v>0.1646343683659466</v>
+        <v>0.1689006395444635</v>
       </c>
       <c r="U23" s="100" t="n">
-        <v>0.1695600875549878</v>
+        <v>0.1738801229545905</v>
       </c>
     </row>
     <row r="24" hidden="1" outlineLevel="3">
@@ -9941,13 +10041,13 @@
         <v/>
       </c>
       <c r="G24" s="80" t="n">
-        <v>278177</v>
+        <v>276969</v>
       </c>
       <c r="H24" s="80" t="n">
-        <v>293838</v>
+        <v>292541</v>
       </c>
       <c r="I24" s="80" t="n">
-        <v>309360</v>
+        <v>307964</v>
       </c>
       <c r="J24" s="80">
         <f>I24-G24</f>
@@ -9983,13 +10083,13 @@
         </is>
       </c>
       <c r="S24" s="100" t="n">
-        <v>0.01701342245969789</v>
+        <v>0.1885144052633296</v>
       </c>
       <c r="T24" s="100" t="n">
-        <v>0.02185341597747861</v>
+        <v>0.1924838800099822</v>
       </c>
       <c r="U24" s="100" t="n">
-        <v>0.03322773657408915</v>
+        <v>0.2017128975380232</v>
       </c>
     </row>
     <row r="25" hidden="1" outlineLevel="4">
@@ -10016,13 +10116,13 @@
         <v/>
       </c>
       <c r="G25" s="80" t="n">
-        <v>278177</v>
+        <v>276969</v>
       </c>
       <c r="H25" s="80" t="n">
-        <v>293838</v>
+        <v>292541</v>
       </c>
       <c r="I25" s="80" t="n">
-        <v>309360</v>
+        <v>307964</v>
       </c>
       <c r="J25" s="80">
         <f>I25-G25</f>
@@ -10058,13 +10158,13 @@
         </is>
       </c>
       <c r="S25" s="100" t="n">
-        <v>0.02403813013691491</v>
+        <v>0.02781671382510736</v>
       </c>
       <c r="T25" s="100" t="n">
-        <v>0.02712584130666647</v>
+        <v>0.03092874501352017</v>
       </c>
       <c r="U25" s="100" t="n">
-        <v>0.03658446946636766</v>
+        <v>0.04043491746124073</v>
       </c>
     </row>
     <row r="26" hidden="1" outlineLevel="3">
@@ -10091,13 +10191,13 @@
         <v/>
       </c>
       <c r="G26" s="80" t="n">
-        <v>246422</v>
+        <v>245240</v>
       </c>
       <c r="H26" s="80" t="n">
-        <v>256298</v>
+        <v>255054</v>
       </c>
       <c r="I26" s="80" t="n">
-        <v>269891</v>
+        <v>268550</v>
       </c>
       <c r="J26" s="80">
         <f>I26-G26</f>
@@ -10152,13 +10252,13 @@
         <v/>
       </c>
       <c r="G27" s="80" t="n">
-        <v>246422</v>
+        <v>245240</v>
       </c>
       <c r="H27" s="80" t="n">
-        <v>256298</v>
+        <v>255054</v>
       </c>
       <c r="I27" s="80" t="n">
-        <v>269891</v>
+        <v>268550</v>
       </c>
       <c r="J27" s="80">
         <f>I27-G27</f>
@@ -10213,13 +10313,13 @@
         <v/>
       </c>
       <c r="G28" s="80" t="n">
-        <v>242407</v>
+        <v>241252</v>
       </c>
       <c r="H28" s="80" t="n">
-        <v>252312</v>
+        <v>251096</v>
       </c>
       <c r="I28" s="80" t="n">
-        <v>265943</v>
+        <v>264629</v>
       </c>
       <c r="J28" s="80">
         <f>I28-G28</f>
@@ -10274,13 +10374,13 @@
         <v/>
       </c>
       <c r="G29" s="80" t="n">
-        <v>242407</v>
+        <v>241252</v>
       </c>
       <c r="H29" s="80" t="n">
-        <v>252312</v>
+        <v>251096</v>
       </c>
       <c r="I29" s="80" t="n">
-        <v>265943</v>
+        <v>264629</v>
       </c>
       <c r="J29" s="80">
         <f>I29-G29</f>
@@ -10335,13 +10435,13 @@
         <v/>
       </c>
       <c r="G30" s="80" t="n">
-        <v>489715</v>
+        <v>487325</v>
       </c>
       <c r="H30" s="80" t="n">
-        <v>517640</v>
+        <v>515072</v>
       </c>
       <c r="I30" s="80" t="n">
-        <v>544976</v>
+        <v>542211</v>
       </c>
       <c r="J30" s="80">
         <f>I30-G30</f>
@@ -10396,13 +10496,13 @@
         <v/>
       </c>
       <c r="G31" s="80" t="n">
-        <v>252014</v>
+        <v>250806</v>
       </c>
       <c r="H31" s="80" t="n">
-        <v>266477</v>
+        <v>265179</v>
       </c>
       <c r="I31" s="80" t="n">
-        <v>280693</v>
+        <v>279296</v>
       </c>
       <c r="J31" s="80">
         <f>I31-G31</f>
@@ -10457,13 +10557,13 @@
         <v/>
       </c>
       <c r="G32" s="80" t="n">
-        <v>252014</v>
+        <v>250806</v>
       </c>
       <c r="H32" s="80" t="n">
-        <v>266477</v>
+        <v>265179</v>
       </c>
       <c r="I32" s="80" t="n">
-        <v>280693</v>
+        <v>279296</v>
       </c>
       <c r="J32" s="80">
         <f>I32-G32</f>
@@ -10518,13 +10618,13 @@
         <v/>
       </c>
       <c r="G33" s="80" t="n">
-        <v>237701</v>
+        <v>236519</v>
       </c>
       <c r="H33" s="80" t="n">
-        <v>251163</v>
+        <v>249892</v>
       </c>
       <c r="I33" s="80" t="n">
-        <v>264283</v>
+        <v>262914</v>
       </c>
       <c r="J33" s="80">
         <f>I33-G33</f>
@@ -10579,13 +10679,13 @@
         <v/>
       </c>
       <c r="G34" s="80" t="n">
-        <v>237701</v>
+        <v>236519</v>
       </c>
       <c r="H34" s="80" t="n">
-        <v>251163</v>
+        <v>249892</v>
       </c>
       <c r="I34" s="80" t="n">
-        <v>264283</v>
+        <v>262914</v>
       </c>
       <c r="J34" s="80">
         <f>I34-G34</f>
@@ -10640,13 +10740,13 @@
         <v/>
       </c>
       <c r="G35" s="75" t="n">
-        <v>1739161</v>
+        <v>1730761</v>
       </c>
       <c r="H35" s="75" t="n">
-        <v>1824834</v>
+        <v>1815945</v>
       </c>
       <c r="I35" s="75" t="n">
-        <v>1922805</v>
+        <v>1913209</v>
       </c>
       <c r="J35" s="75">
         <f>I35-G35</f>
@@ -10701,13 +10801,13 @@
         <v/>
       </c>
       <c r="G36" s="80" t="n">
-        <v>1032259</v>
+        <v>1027260</v>
       </c>
       <c r="H36" s="80" t="n">
-        <v>1083249</v>
+        <v>1077957</v>
       </c>
       <c r="I36" s="80" t="n">
-        <v>1141623</v>
+        <v>1135908</v>
       </c>
       <c r="J36" s="80">
         <f>I36-G36</f>
@@ -10762,13 +10862,13 @@
         <v/>
       </c>
       <c r="G37" s="80" t="n">
-        <v>405247</v>
+        <v>403532</v>
       </c>
       <c r="H37" s="80" t="n">
-        <v>425326</v>
+        <v>423513</v>
       </c>
       <c r="I37" s="80" t="n">
-        <v>448100</v>
+        <v>446146</v>
       </c>
       <c r="J37" s="80">
         <f>I37-G37</f>
@@ -10823,13 +10923,13 @@
         <v/>
       </c>
       <c r="G38" s="80" t="n">
-        <v>405247</v>
+        <v>403532</v>
       </c>
       <c r="H38" s="80" t="n">
-        <v>425326</v>
+        <v>423513</v>
       </c>
       <c r="I38" s="80" t="n">
-        <v>448100</v>
+        <v>446146</v>
       </c>
       <c r="J38" s="80">
         <f>I38-G38</f>
@@ -10884,13 +10984,13 @@
         <v/>
       </c>
       <c r="G39" s="80" t="n">
-        <v>315635</v>
+        <v>313978</v>
       </c>
       <c r="H39" s="80" t="n">
-        <v>331085</v>
+        <v>329330</v>
       </c>
       <c r="I39" s="80" t="n">
-        <v>348863</v>
+        <v>346967</v>
       </c>
       <c r="J39" s="80">
         <f>I39-G39</f>
@@ -10945,13 +11045,13 @@
         <v/>
       </c>
       <c r="G40" s="80" t="n">
-        <v>315635</v>
+        <v>313978</v>
       </c>
       <c r="H40" s="80" t="n">
-        <v>331085</v>
+        <v>329330</v>
       </c>
       <c r="I40" s="80" t="n">
-        <v>348863</v>
+        <v>346967</v>
       </c>
       <c r="J40" s="80">
         <f>I40-G40</f>
@@ -11006,13 +11106,13 @@
         <v/>
       </c>
       <c r="G41" s="80" t="n">
-        <v>311377</v>
+        <v>309749</v>
       </c>
       <c r="H41" s="80" t="n">
-        <v>326838</v>
+        <v>325113</v>
       </c>
       <c r="I41" s="80" t="n">
-        <v>344661</v>
+        <v>342795</v>
       </c>
       <c r="J41" s="80">
         <f>I41-G41</f>
@@ -11067,13 +11167,13 @@
         <v/>
       </c>
       <c r="G42" s="80" t="n">
-        <v>311377</v>
+        <v>309749</v>
       </c>
       <c r="H42" s="80" t="n">
-        <v>326838</v>
+        <v>325113</v>
       </c>
       <c r="I42" s="80" t="n">
-        <v>344661</v>
+        <v>342795</v>
       </c>
       <c r="J42" s="80">
         <f>I42-G42</f>
@@ -11128,13 +11228,13 @@
         <v/>
       </c>
       <c r="G43" s="80" t="n">
-        <v>706902</v>
+        <v>703501</v>
       </c>
       <c r="H43" s="80" t="n">
-        <v>741585</v>
+        <v>737988</v>
       </c>
       <c r="I43" s="80" t="n">
-        <v>781181</v>
+        <v>777302</v>
       </c>
       <c r="J43" s="80">
         <f>I43-G43</f>
@@ -11189,13 +11289,13 @@
         <v/>
       </c>
       <c r="G44" s="80" t="n">
-        <v>364213</v>
+        <v>362498</v>
       </c>
       <c r="H44" s="80" t="n">
-        <v>382412</v>
+        <v>380599</v>
       </c>
       <c r="I44" s="80" t="n">
-        <v>403137</v>
+        <v>401183</v>
       </c>
       <c r="J44" s="80">
         <f>I44-G44</f>
@@ -11250,13 +11350,13 @@
         <v/>
       </c>
       <c r="G45" s="80" t="n">
-        <v>364213</v>
+        <v>362498</v>
       </c>
       <c r="H45" s="80" t="n">
-        <v>382412</v>
+        <v>380599</v>
       </c>
       <c r="I45" s="80" t="n">
-        <v>403137</v>
+        <v>401183</v>
       </c>
       <c r="J45" s="80">
         <f>I45-G45</f>
@@ -11311,13 +11411,13 @@
         <v/>
       </c>
       <c r="G46" s="80" t="n">
-        <v>342689</v>
+        <v>341003</v>
       </c>
       <c r="H46" s="80" t="n">
-        <v>359173</v>
+        <v>357389</v>
       </c>
       <c r="I46" s="80" t="n">
-        <v>378044</v>
+        <v>376119</v>
       </c>
       <c r="J46" s="80">
         <f>I46-G46</f>
@@ -11372,13 +11472,13 @@
         <v/>
       </c>
       <c r="G47" s="80" t="n">
-        <v>342689</v>
+        <v>341003</v>
       </c>
       <c r="H47" s="80" t="n">
-        <v>359173</v>
+        <v>357389</v>
       </c>
       <c r="I47" s="80" t="n">
-        <v>378044</v>
+        <v>376119</v>
       </c>
       <c r="J47" s="80">
         <f>I47-G47</f>
@@ -11433,13 +11533,13 @@
         <v/>
       </c>
       <c r="G48" s="75" t="n">
-        <v>1460139</v>
+        <v>1452886</v>
       </c>
       <c r="H48" s="75" t="n">
-        <v>1535893</v>
+        <v>1528121</v>
       </c>
       <c r="I48" s="75" t="n">
-        <v>1614692</v>
+        <v>1606397</v>
       </c>
       <c r="J48" s="75">
         <f>I48-G48</f>
@@ -11494,13 +11594,13 @@
         <v/>
       </c>
       <c r="G49" s="80" t="n">
-        <v>849808</v>
+        <v>845490</v>
       </c>
       <c r="H49" s="80" t="n">
-        <v>893407</v>
+        <v>888783</v>
       </c>
       <c r="I49" s="80" t="n">
-        <v>939465</v>
+        <v>934528</v>
       </c>
       <c r="J49" s="80">
         <f>I49-G49</f>
@@ -11555,13 +11655,13 @@
         <v/>
       </c>
       <c r="G50" s="80" t="n">
-        <v>307372</v>
+        <v>305905</v>
       </c>
       <c r="H50" s="80" t="n">
-        <v>325846</v>
+        <v>324258</v>
       </c>
       <c r="I50" s="80" t="n">
-        <v>342714</v>
+        <v>341021</v>
       </c>
       <c r="J50" s="80">
         <f>I50-G50</f>
@@ -11616,13 +11716,13 @@
         <v/>
       </c>
       <c r="G51" s="80" t="n">
-        <v>307372</v>
+        <v>305905</v>
       </c>
       <c r="H51" s="80" t="n">
-        <v>325846</v>
+        <v>324258</v>
       </c>
       <c r="I51" s="80" t="n">
-        <v>342714</v>
+        <v>341021</v>
       </c>
       <c r="J51" s="80">
         <f>I51-G51</f>
@@ -11677,13 +11777,13 @@
         <v/>
       </c>
       <c r="G52" s="80" t="n">
-        <v>273182</v>
+        <v>271742</v>
       </c>
       <c r="H52" s="80" t="n">
-        <v>285722</v>
+        <v>284190</v>
       </c>
       <c r="I52" s="80" t="n">
-        <v>300314</v>
+        <v>298677</v>
       </c>
       <c r="J52" s="80">
         <f>I52-G52</f>
@@ -11738,13 +11838,13 @@
         <v/>
       </c>
       <c r="G53" s="80" t="n">
-        <v>273182</v>
+        <v>271742</v>
       </c>
       <c r="H53" s="80" t="n">
-        <v>285722</v>
+        <v>284190</v>
       </c>
       <c r="I53" s="80" t="n">
-        <v>300314</v>
+        <v>298677</v>
       </c>
       <c r="J53" s="80">
         <f>I53-G53</f>
@@ -11799,13 +11899,13 @@
         <v/>
       </c>
       <c r="G54" s="80" t="n">
-        <v>269254</v>
+        <v>267842</v>
       </c>
       <c r="H54" s="80" t="n">
-        <v>281838</v>
+        <v>280334</v>
       </c>
       <c r="I54" s="80" t="n">
-        <v>296438</v>
+        <v>294830</v>
       </c>
       <c r="J54" s="80">
         <f>I54-G54</f>
@@ -11860,13 +11960,13 @@
         <v/>
       </c>
       <c r="G55" s="80" t="n">
-        <v>269254</v>
+        <v>267842</v>
       </c>
       <c r="H55" s="80" t="n">
-        <v>281838</v>
+        <v>280334</v>
       </c>
       <c r="I55" s="80" t="n">
-        <v>296438</v>
+        <v>294830</v>
       </c>
       <c r="J55" s="80">
         <f>I55-G55</f>
@@ -11921,13 +12021,13 @@
         <v/>
       </c>
       <c r="G56" s="80" t="n">
-        <v>610331</v>
+        <v>607397</v>
       </c>
       <c r="H56" s="80" t="n">
-        <v>642486</v>
+        <v>639339</v>
       </c>
       <c r="I56" s="80" t="n">
-        <v>675227</v>
+        <v>671869</v>
       </c>
       <c r="J56" s="80">
         <f>I56-G56</f>
@@ -11982,13 +12082,13 @@
         <v/>
       </c>
       <c r="G57" s="80" t="n">
-        <v>311681</v>
+        <v>310213</v>
       </c>
       <c r="H57" s="80" t="n">
-        <v>330352</v>
+        <v>328764</v>
       </c>
       <c r="I57" s="80" t="n">
-        <v>347434</v>
+        <v>345742</v>
       </c>
       <c r="J57" s="80">
         <f>I57-G57</f>
@@ -12043,13 +12143,13 @@
         <v/>
       </c>
       <c r="G58" s="80" t="n">
-        <v>311681</v>
+        <v>310213</v>
       </c>
       <c r="H58" s="80" t="n">
-        <v>330352</v>
+        <v>328764</v>
       </c>
       <c r="I58" s="80" t="n">
-        <v>347434</v>
+        <v>345742</v>
       </c>
       <c r="J58" s="80">
         <f>I58-G58</f>
@@ -12104,13 +12204,13 @@
         <v/>
       </c>
       <c r="G59" s="80" t="n">
-        <v>298651</v>
+        <v>297183</v>
       </c>
       <c r="H59" s="80" t="n">
-        <v>312135</v>
+        <v>310575</v>
       </c>
       <c r="I59" s="80" t="n">
-        <v>327792</v>
+        <v>326128</v>
       </c>
       <c r="J59" s="80">
         <f>I59-G59</f>
@@ -12165,13 +12265,13 @@
         <v/>
       </c>
       <c r="G60" s="80" t="n">
-        <v>298651</v>
+        <v>297183</v>
       </c>
       <c r="H60" s="80" t="n">
-        <v>312135</v>
+        <v>310575</v>
       </c>
       <c r="I60" s="80" t="n">
-        <v>327792</v>
+        <v>326128</v>
       </c>
       <c r="J60" s="80">
         <f>I60-G60</f>
@@ -12226,13 +12326,13 @@
         <v/>
       </c>
       <c r="G61" s="75" t="n">
-        <v>2652983</v>
+        <v>2642448</v>
       </c>
       <c r="H61" s="75" t="n">
-        <v>2788302</v>
+        <v>2777015</v>
       </c>
       <c r="I61" s="75" t="n">
-        <v>2931111</v>
+        <v>2919047</v>
       </c>
       <c r="J61" s="75">
         <f>I61-G61</f>
@@ -12287,13 +12387,13 @@
         <v/>
       </c>
       <c r="G62" s="80" t="n">
-        <v>1616500</v>
+        <v>1610209</v>
       </c>
       <c r="H62" s="80" t="n">
-        <v>1697747</v>
+        <v>1691012</v>
       </c>
       <c r="I62" s="80" t="n">
-        <v>1784629</v>
+        <v>1777429</v>
       </c>
       <c r="J62" s="80">
         <f>I62-G62</f>
@@ -12348,13 +12448,13 @@
         <v/>
       </c>
       <c r="G63" s="80" t="n">
-        <v>588934</v>
+        <v>586796</v>
       </c>
       <c r="H63" s="80" t="n">
-        <v>622541</v>
+        <v>620234</v>
       </c>
       <c r="I63" s="80" t="n">
-        <v>654722</v>
+        <v>652259</v>
       </c>
       <c r="J63" s="80">
         <f>I63-G63</f>
@@ -12409,13 +12509,13 @@
         <v/>
       </c>
       <c r="G64" s="80" t="n">
-        <v>588934</v>
+        <v>586796</v>
       </c>
       <c r="H64" s="80" t="n">
-        <v>622541</v>
+        <v>620234</v>
       </c>
       <c r="I64" s="80" t="n">
-        <v>654722</v>
+        <v>652259</v>
       </c>
       <c r="J64" s="80">
         <f>I64-G64</f>
@@ -12470,13 +12570,13 @@
         <v/>
       </c>
       <c r="G65" s="80" t="n">
-        <v>519309</v>
+        <v>517202</v>
       </c>
       <c r="H65" s="80" t="n">
-        <v>543061</v>
+        <v>540816</v>
       </c>
       <c r="I65" s="80" t="n">
-        <v>570390</v>
+        <v>567990</v>
       </c>
       <c r="J65" s="80">
         <f>I65-G65</f>
@@ -12531,13 +12631,13 @@
         <v/>
       </c>
       <c r="G66" s="80" t="n">
-        <v>519309</v>
+        <v>517202</v>
       </c>
       <c r="H66" s="80" t="n">
-        <v>543061</v>
+        <v>540816</v>
       </c>
       <c r="I66" s="80" t="n">
-        <v>570390</v>
+        <v>567990</v>
       </c>
       <c r="J66" s="80">
         <f>I66-G66</f>
@@ -12592,13 +12692,13 @@
         <v/>
       </c>
       <c r="G67" s="80" t="n">
-        <v>508256</v>
+        <v>506211</v>
       </c>
       <c r="H67" s="80" t="n">
-        <v>532145</v>
+        <v>529963</v>
       </c>
       <c r="I67" s="80" t="n">
-        <v>559518</v>
+        <v>557181</v>
       </c>
       <c r="J67" s="80">
         <f>I67-G67</f>
@@ -12653,13 +12753,13 @@
         <v/>
       </c>
       <c r="G68" s="80" t="n">
-        <v>508256</v>
+        <v>506211</v>
       </c>
       <c r="H68" s="80" t="n">
-        <v>532145</v>
+        <v>529963</v>
       </c>
       <c r="I68" s="80" t="n">
-        <v>559518</v>
+        <v>557181</v>
       </c>
       <c r="J68" s="80">
         <f>I68-G68</f>
@@ -12714,13 +12814,13 @@
         <v/>
       </c>
       <c r="G69" s="80" t="n">
-        <v>1036484</v>
+        <v>1032239</v>
       </c>
       <c r="H69" s="80" t="n">
-        <v>1090555</v>
+        <v>1086002</v>
       </c>
       <c r="I69" s="80" t="n">
-        <v>1146482</v>
+        <v>1141618</v>
       </c>
       <c r="J69" s="80">
         <f>I69-G69</f>
@@ -12775,13 +12875,13 @@
         <v/>
       </c>
       <c r="G70" s="80" t="n">
-        <v>535115</v>
+        <v>532977</v>
       </c>
       <c r="H70" s="80" t="n">
-        <v>566256</v>
+        <v>563948</v>
       </c>
       <c r="I70" s="80" t="n">
-        <v>595750</v>
+        <v>593286</v>
       </c>
       <c r="J70" s="80">
         <f>I70-G70</f>
@@ -12836,13 +12936,13 @@
         <v/>
       </c>
       <c r="G71" s="80" t="n">
-        <v>535115</v>
+        <v>532977</v>
       </c>
       <c r="H71" s="80" t="n">
-        <v>566256</v>
+        <v>563948</v>
       </c>
       <c r="I71" s="80" t="n">
-        <v>595750</v>
+        <v>593286</v>
       </c>
       <c r="J71" s="80">
         <f>I71-G71</f>
@@ -12897,13 +12997,13 @@
         <v/>
       </c>
       <c r="G72" s="80" t="n">
-        <v>501369</v>
+        <v>499262</v>
       </c>
       <c r="H72" s="80" t="n">
-        <v>524299</v>
+        <v>522054</v>
       </c>
       <c r="I72" s="80" t="n">
-        <v>550732</v>
+        <v>548332</v>
       </c>
       <c r="J72" s="80">
         <f>I72-G72</f>
@@ -12958,13 +13058,13 @@
         <v/>
       </c>
       <c r="G73" s="80" t="n">
-        <v>501369</v>
+        <v>499262</v>
       </c>
       <c r="H73" s="80" t="n">
-        <v>524299</v>
+        <v>522054</v>
       </c>
       <c r="I73" s="80" t="n">
-        <v>550732</v>
+        <v>548332</v>
       </c>
       <c r="J73" s="80">
         <f>I73-G73</f>
@@ -13019,13 +13119,13 @@
         <v/>
       </c>
       <c r="G74" s="70" t="n">
-        <v>4785303</v>
+        <v>4764012</v>
       </c>
       <c r="H74" s="70" t="n">
-        <v>5024435</v>
+        <v>5001790</v>
       </c>
       <c r="I74" s="70" t="n">
-        <v>5290478</v>
+        <v>5266073</v>
       </c>
       <c r="J74" s="70">
         <f>I74-G74</f>
@@ -13080,13 +13180,13 @@
         <v/>
       </c>
       <c r="G75" s="75" t="n">
-        <v>1149448</v>
+        <v>1143506</v>
       </c>
       <c r="H75" s="75" t="n">
-        <v>1206986</v>
+        <v>1200677</v>
       </c>
       <c r="I75" s="75" t="n">
-        <v>1272073</v>
+        <v>1265262</v>
       </c>
       <c r="J75" s="75">
         <f>I75-G75</f>
@@ -13141,13 +13241,13 @@
         <v/>
       </c>
       <c r="G76" s="80" t="n">
-        <v>699074</v>
+        <v>695541</v>
       </c>
       <c r="H76" s="80" t="n">
-        <v>733398</v>
+        <v>729651</v>
       </c>
       <c r="I76" s="80" t="n">
-        <v>773068</v>
+        <v>769021</v>
       </c>
       <c r="J76" s="80">
         <f>I76-G76</f>
@@ -13202,13 +13302,13 @@
         <v/>
       </c>
       <c r="G77" s="80" t="n">
-        <v>254345</v>
+        <v>253140</v>
       </c>
       <c r="H77" s="80" t="n">
-        <v>269426</v>
+        <v>268131</v>
       </c>
       <c r="I77" s="80" t="n">
-        <v>283885</v>
+        <v>282489</v>
       </c>
       <c r="J77" s="80">
         <f>I77-G77</f>
@@ -13263,13 +13363,13 @@
         <v/>
       </c>
       <c r="G78" s="80" t="n">
-        <v>254345</v>
+        <v>253140</v>
       </c>
       <c r="H78" s="80" t="n">
-        <v>269426</v>
+        <v>268131</v>
       </c>
       <c r="I78" s="80" t="n">
-        <v>283885</v>
+        <v>282489</v>
       </c>
       <c r="J78" s="80">
         <f>I78-G78</f>
@@ -13324,13 +13424,13 @@
         <v/>
       </c>
       <c r="G79" s="80" t="n">
-        <v>224229</v>
+        <v>223052</v>
       </c>
       <c r="H79" s="80" t="n">
-        <v>233842</v>
+        <v>232602</v>
       </c>
       <c r="I79" s="80" t="n">
-        <v>246430</v>
+        <v>245090</v>
       </c>
       <c r="J79" s="80">
         <f>I79-G79</f>
@@ -13385,13 +13485,13 @@
         <v/>
       </c>
       <c r="G80" s="80" t="n">
-        <v>224229</v>
+        <v>223052</v>
       </c>
       <c r="H80" s="80" t="n">
-        <v>233842</v>
+        <v>232602</v>
       </c>
       <c r="I80" s="80" t="n">
-        <v>246430</v>
+        <v>245090</v>
       </c>
       <c r="J80" s="80">
         <f>I80-G80</f>
@@ -13446,13 +13546,13 @@
         <v/>
       </c>
       <c r="G81" s="80" t="n">
-        <v>220500</v>
+        <v>219350</v>
       </c>
       <c r="H81" s="80" t="n">
-        <v>230130</v>
+        <v>228917</v>
       </c>
       <c r="I81" s="80" t="n">
-        <v>242753</v>
+        <v>241442</v>
       </c>
       <c r="J81" s="80">
         <f>I81-G81</f>
@@ -13507,13 +13607,13 @@
         <v/>
       </c>
       <c r="G82" s="80" t="n">
-        <v>220500</v>
+        <v>219350</v>
       </c>
       <c r="H82" s="80" t="n">
-        <v>230130</v>
+        <v>228917</v>
       </c>
       <c r="I82" s="80" t="n">
-        <v>242753</v>
+        <v>241442</v>
       </c>
       <c r="J82" s="80">
         <f>I82-G82</f>
@@ -13568,13 +13668,13 @@
         <v/>
       </c>
       <c r="G83" s="80" t="n">
-        <v>450375</v>
+        <v>447965</v>
       </c>
       <c r="H83" s="80" t="n">
-        <v>473589</v>
+        <v>471026</v>
       </c>
       <c r="I83" s="80" t="n">
-        <v>499005</v>
+        <v>496242</v>
       </c>
       <c r="J83" s="80">
         <f>I83-G83</f>
@@ -13629,13 +13729,13 @@
         <v/>
       </c>
       <c r="G84" s="80" t="n">
-        <v>230398</v>
+        <v>229193</v>
       </c>
       <c r="H84" s="80" t="n">
-        <v>244382</v>
+        <v>243087</v>
       </c>
       <c r="I84" s="80" t="n">
-        <v>257645</v>
+        <v>256250</v>
       </c>
       <c r="J84" s="80">
         <f>I84-G84</f>
@@ -13690,13 +13790,13 @@
         <v/>
       </c>
       <c r="G85" s="80" t="n">
-        <v>230398</v>
+        <v>229193</v>
       </c>
       <c r="H85" s="80" t="n">
-        <v>244382</v>
+        <v>243087</v>
       </c>
       <c r="I85" s="80" t="n">
-        <v>257645</v>
+        <v>256250</v>
       </c>
       <c r="J85" s="80">
         <f>I85-G85</f>
@@ -13751,13 +13851,13 @@
         <v/>
       </c>
       <c r="G86" s="80" t="n">
-        <v>219977</v>
+        <v>218772</v>
       </c>
       <c r="H86" s="80" t="n">
-        <v>229206</v>
+        <v>227939</v>
       </c>
       <c r="I86" s="80" t="n">
-        <v>241359</v>
+        <v>239992</v>
       </c>
       <c r="J86" s="80">
         <f>I86-G86</f>
@@ -13812,13 +13912,13 @@
         <v/>
       </c>
       <c r="G87" s="80" t="n">
-        <v>219977</v>
+        <v>218772</v>
       </c>
       <c r="H87" s="80" t="n">
-        <v>229206</v>
+        <v>227939</v>
       </c>
       <c r="I87" s="80" t="n">
-        <v>241359</v>
+        <v>239992</v>
       </c>
       <c r="J87" s="80">
         <f>I87-G87</f>
@@ -13873,13 +13973,13 @@
         <v/>
       </c>
       <c r="G88" s="75" t="n">
-        <v>2542368</v>
+        <v>2532546</v>
       </c>
       <c r="H88" s="75" t="n">
-        <v>2670967</v>
+        <v>2660460</v>
       </c>
       <c r="I88" s="75" t="n">
-        <v>2809420</v>
+        <v>2798139</v>
       </c>
       <c r="J88" s="75">
         <f>I88-G88</f>
@@ -13934,13 +14034,13 @@
         <v/>
       </c>
       <c r="G89" s="80" t="n">
-        <v>1548364</v>
+        <v>1542515</v>
       </c>
       <c r="H89" s="80" t="n">
-        <v>1626759</v>
+        <v>1620498</v>
       </c>
       <c r="I89" s="80" t="n">
-        <v>1711126</v>
+        <v>1704402</v>
       </c>
       <c r="J89" s="80">
         <f>I89-G89</f>
@@ -13995,13 +14095,13 @@
         <v/>
       </c>
       <c r="G90" s="80" t="n">
-        <v>566209</v>
+        <v>564207</v>
       </c>
       <c r="H90" s="80" t="n">
-        <v>595000</v>
+        <v>592861</v>
       </c>
       <c r="I90" s="80" t="n">
-        <v>626091</v>
+        <v>623796</v>
       </c>
       <c r="J90" s="80">
         <f>I90-G90</f>
@@ -14056,13 +14156,13 @@
         <v/>
       </c>
       <c r="G91" s="80" t="n">
-        <v>566209</v>
+        <v>564207</v>
       </c>
       <c r="H91" s="80" t="n">
-        <v>595000</v>
+        <v>592861</v>
       </c>
       <c r="I91" s="80" t="n">
-        <v>626091</v>
+        <v>623796</v>
       </c>
       <c r="J91" s="80">
         <f>I91-G91</f>
@@ -14117,13 +14217,13 @@
         <v/>
       </c>
       <c r="G92" s="80" t="n">
-        <v>493903</v>
+        <v>491964</v>
       </c>
       <c r="H92" s="80" t="n">
-        <v>518671</v>
+        <v>516595</v>
       </c>
       <c r="I92" s="80" t="n">
-        <v>545289</v>
+        <v>543059</v>
       </c>
       <c r="J92" s="80">
         <f>I92-G92</f>
@@ -14178,13 +14278,13 @@
         <v/>
       </c>
       <c r="G93" s="80" t="n">
-        <v>493903</v>
+        <v>491964</v>
       </c>
       <c r="H93" s="80" t="n">
-        <v>518671</v>
+        <v>516595</v>
       </c>
       <c r="I93" s="80" t="n">
-        <v>545289</v>
+        <v>543059</v>
       </c>
       <c r="J93" s="80">
         <f>I93-G93</f>
@@ -14239,13 +14339,13 @@
         <v/>
       </c>
       <c r="G94" s="80" t="n">
-        <v>488251</v>
+        <v>486344</v>
       </c>
       <c r="H94" s="80" t="n">
-        <v>513087</v>
+        <v>511042</v>
       </c>
       <c r="I94" s="80" t="n">
-        <v>539746</v>
+        <v>537547</v>
       </c>
       <c r="J94" s="80">
         <f>I94-G94</f>
@@ -14300,13 +14400,13 @@
         <v/>
       </c>
       <c r="G95" s="80" t="n">
-        <v>488251</v>
+        <v>486344</v>
       </c>
       <c r="H95" s="80" t="n">
-        <v>513087</v>
+        <v>511042</v>
       </c>
       <c r="I95" s="80" t="n">
-        <v>539746</v>
+        <v>537547</v>
       </c>
       <c r="J95" s="80">
         <f>I95-G95</f>
@@ -14361,13 +14461,13 @@
         <v/>
       </c>
       <c r="G96" s="80" t="n">
-        <v>994004</v>
+        <v>990032</v>
       </c>
       <c r="H96" s="80" t="n">
-        <v>1044209</v>
+        <v>1039962</v>
       </c>
       <c r="I96" s="80" t="n">
-        <v>1098294</v>
+        <v>1093737</v>
       </c>
       <c r="J96" s="80">
         <f>I96-G96</f>
@@ -14422,13 +14522,13 @@
         <v/>
       </c>
       <c r="G97" s="80" t="n">
-        <v>512390</v>
+        <v>510388</v>
       </c>
       <c r="H97" s="80" t="n">
-        <v>538715</v>
+        <v>536575</v>
       </c>
       <c r="I97" s="80" t="n">
-        <v>567119</v>
+        <v>564824</v>
       </c>
       <c r="J97" s="80">
         <f>I97-G97</f>
@@ -14483,13 +14583,13 @@
         <v/>
       </c>
       <c r="G98" s="80" t="n">
-        <v>512390</v>
+        <v>510388</v>
       </c>
       <c r="H98" s="80" t="n">
-        <v>538715</v>
+        <v>536575</v>
       </c>
       <c r="I98" s="80" t="n">
-        <v>567119</v>
+        <v>564824</v>
       </c>
       <c r="J98" s="80">
         <f>I98-G98</f>
@@ -14544,13 +14644,13 @@
         <v/>
       </c>
       <c r="G99" s="80" t="n">
-        <v>481614</v>
+        <v>479644</v>
       </c>
       <c r="H99" s="80" t="n">
-        <v>505494</v>
+        <v>503386</v>
       </c>
       <c r="I99" s="80" t="n">
-        <v>531175</v>
+        <v>528913</v>
       </c>
       <c r="J99" s="80">
         <f>I99-G99</f>
@@ -14605,13 +14705,13 @@
         <v/>
       </c>
       <c r="G100" s="80" t="n">
-        <v>481614</v>
+        <v>479644</v>
       </c>
       <c r="H100" s="80" t="n">
-        <v>505494</v>
+        <v>503386</v>
       </c>
       <c r="I100" s="80" t="n">
-        <v>531175</v>
+        <v>528913</v>
       </c>
       <c r="J100" s="80">
         <f>I100-G100</f>
@@ -14666,13 +14766,13 @@
         <v/>
       </c>
       <c r="G101" s="75" t="n">
-        <v>1093487</v>
+        <v>1087960</v>
       </c>
       <c r="H101" s="75" t="n">
-        <v>1146481</v>
+        <v>1140653</v>
       </c>
       <c r="I101" s="75" t="n">
-        <v>1208986</v>
+        <v>1202672</v>
       </c>
       <c r="J101" s="75">
         <f>I101-G101</f>
@@ -14727,13 +14827,13 @@
         <v/>
       </c>
       <c r="G102" s="80" t="n">
-        <v>667789</v>
+        <v>664489</v>
       </c>
       <c r="H102" s="80" t="n">
-        <v>700125</v>
+        <v>696644</v>
       </c>
       <c r="I102" s="80" t="n">
-        <v>738240</v>
+        <v>734468</v>
       </c>
       <c r="J102" s="80">
         <f>I102-G102</f>
@@ -14788,13 +14888,13 @@
         <v/>
       </c>
       <c r="G103" s="80" t="n">
-        <v>242863</v>
+        <v>241736</v>
       </c>
       <c r="H103" s="80" t="n">
-        <v>254730</v>
+        <v>253543</v>
       </c>
       <c r="I103" s="80" t="n">
-        <v>268582</v>
+        <v>267297</v>
       </c>
       <c r="J103" s="80">
         <f>I103-G103</f>
@@ -14849,13 +14949,13 @@
         <v/>
       </c>
       <c r="G104" s="80" t="n">
-        <v>242863</v>
+        <v>241736</v>
       </c>
       <c r="H104" s="80" t="n">
-        <v>254730</v>
+        <v>253543</v>
       </c>
       <c r="I104" s="80" t="n">
-        <v>268582</v>
+        <v>267297</v>
       </c>
       <c r="J104" s="80">
         <f>I104-G104</f>
@@ -14910,13 +15010,13 @@
         <v/>
       </c>
       <c r="G105" s="80" t="n">
-        <v>214309</v>
+        <v>213209</v>
       </c>
       <c r="H105" s="80" t="n">
-        <v>224543</v>
+        <v>223383</v>
       </c>
       <c r="I105" s="80" t="n">
-        <v>236652</v>
+        <v>235394</v>
       </c>
       <c r="J105" s="80">
         <f>I105-G105</f>
@@ -14971,13 +15071,13 @@
         <v/>
       </c>
       <c r="G106" s="80" t="n">
-        <v>214309</v>
+        <v>213209</v>
       </c>
       <c r="H106" s="80" t="n">
-        <v>224543</v>
+        <v>223383</v>
       </c>
       <c r="I106" s="80" t="n">
-        <v>236652</v>
+        <v>235394</v>
       </c>
       <c r="J106" s="80">
         <f>I106-G106</f>
@@ -15032,13 +15132,13 @@
         <v/>
       </c>
       <c r="G107" s="80" t="n">
-        <v>210617</v>
+        <v>209544</v>
       </c>
       <c r="H107" s="80" t="n">
-        <v>220852</v>
+        <v>219719</v>
       </c>
       <c r="I107" s="80" t="n">
-        <v>233006</v>
+        <v>231776</v>
       </c>
       <c r="J107" s="80">
         <f>I107-G107</f>
@@ -15093,13 +15193,13 @@
         <v/>
       </c>
       <c r="G108" s="80" t="n">
-        <v>210617</v>
+        <v>209544</v>
       </c>
       <c r="H108" s="80" t="n">
-        <v>220852</v>
+        <v>219719</v>
       </c>
       <c r="I108" s="80" t="n">
-        <v>233006</v>
+        <v>231776</v>
       </c>
       <c r="J108" s="80">
         <f>I108-G108</f>
@@ -15154,13 +15254,13 @@
         <v/>
       </c>
       <c r="G109" s="80" t="n">
-        <v>425698</v>
+        <v>423471</v>
       </c>
       <c r="H109" s="80" t="n">
-        <v>446356</v>
+        <v>444009</v>
       </c>
       <c r="I109" s="80" t="n">
-        <v>470746</v>
+        <v>468204</v>
       </c>
       <c r="J109" s="80">
         <f>I109-G109</f>
@@ -15215,13 +15315,13 @@
         <v/>
       </c>
       <c r="G110" s="80" t="n">
-        <v>219257</v>
+        <v>218131</v>
       </c>
       <c r="H110" s="80" t="n">
-        <v>230043</v>
+        <v>228855</v>
       </c>
       <c r="I110" s="80" t="n">
-        <v>242716</v>
+        <v>241432</v>
       </c>
       <c r="J110" s="80">
         <f>I110-G110</f>
@@ -15276,13 +15376,13 @@
         <v/>
       </c>
       <c r="G111" s="80" t="n">
-        <v>219257</v>
+        <v>218131</v>
       </c>
       <c r="H111" s="80" t="n">
-        <v>230043</v>
+        <v>228855</v>
       </c>
       <c r="I111" s="80" t="n">
-        <v>242716</v>
+        <v>241432</v>
       </c>
       <c r="J111" s="80">
         <f>I111-G111</f>
@@ -15337,13 +15437,13 @@
         <v/>
       </c>
       <c r="G112" s="80" t="n">
-        <v>206440</v>
+        <v>205340</v>
       </c>
       <c r="H112" s="80" t="n">
-        <v>216314</v>
+        <v>215153</v>
       </c>
       <c r="I112" s="80" t="n">
-        <v>228030</v>
+        <v>226772</v>
       </c>
       <c r="J112" s="80">
         <f>I112-G112</f>
@@ -15398,13 +15498,13 @@
         <v/>
       </c>
       <c r="G113" s="80" t="n">
-        <v>206440</v>
+        <v>205340</v>
       </c>
       <c r="H113" s="80" t="n">
-        <v>216314</v>
+        <v>215153</v>
       </c>
       <c r="I113" s="80" t="n">
-        <v>228030</v>
+        <v>226772</v>
       </c>
       <c r="J113" s="80">
         <f>I113-G113</f>
@@ -15459,13 +15559,13 @@
         <v/>
       </c>
       <c r="G114" s="70" t="n">
-        <v>1940009</v>
+        <v>1930216</v>
       </c>
       <c r="H114" s="70" t="n">
-        <v>2037766</v>
+        <v>2027359</v>
       </c>
       <c r="I114" s="70" t="n">
-        <v>2144860</v>
+        <v>2133702</v>
       </c>
       <c r="J114" s="70">
         <f>I114-G114</f>
@@ -15520,13 +15620,13 @@
         <v/>
       </c>
       <c r="G115" s="75" t="n">
-        <v>600000</v>
+        <v>597026</v>
       </c>
       <c r="H115" s="75" t="n">
-        <v>630292</v>
+        <v>627128</v>
       </c>
       <c r="I115" s="75" t="n">
-        <v>662728</v>
+        <v>659352</v>
       </c>
       <c r="J115" s="75">
         <f>I115-G115</f>
@@ -15581,13 +15681,13 @@
         <v/>
       </c>
       <c r="G116" s="80" t="n">
-        <v>600000</v>
+        <v>597026</v>
       </c>
       <c r="H116" s="80" t="n">
-        <v>630292</v>
+        <v>627128</v>
       </c>
       <c r="I116" s="80" t="n">
-        <v>662728</v>
+        <v>659352</v>
       </c>
       <c r="J116" s="80">
         <f>I116-G116</f>
@@ -15642,13 +15742,13 @@
         <v/>
       </c>
       <c r="G117" s="80" t="n">
-        <v>212184</v>
+        <v>211164</v>
       </c>
       <c r="H117" s="80" t="n">
-        <v>223096</v>
+        <v>222013</v>
       </c>
       <c r="I117" s="80" t="n">
-        <v>234820</v>
+        <v>233665</v>
       </c>
       <c r="J117" s="80">
         <f>I117-G117</f>
@@ -15703,13 +15803,13 @@
         <v/>
       </c>
       <c r="G118" s="80" t="n">
-        <v>212184</v>
+        <v>211164</v>
       </c>
       <c r="H118" s="80" t="n">
-        <v>223096</v>
+        <v>222013</v>
       </c>
       <c r="I118" s="80" t="n">
-        <v>234820</v>
+        <v>233665</v>
       </c>
       <c r="J118" s="80">
         <f>I118-G118</f>
@@ -15764,13 +15864,13 @@
         <v/>
       </c>
       <c r="G119" s="80" t="n">
-        <v>195819</v>
+        <v>194828</v>
       </c>
       <c r="H119" s="80" t="n">
-        <v>205498</v>
+        <v>204443</v>
       </c>
       <c r="I119" s="80" t="n">
-        <v>215850</v>
+        <v>214725</v>
       </c>
       <c r="J119" s="80">
         <f>I119-G119</f>
@@ -15825,13 +15925,13 @@
         <v/>
       </c>
       <c r="G120" s="80" t="n">
-        <v>195819</v>
+        <v>194828</v>
       </c>
       <c r="H120" s="80" t="n">
-        <v>205498</v>
+        <v>204443</v>
       </c>
       <c r="I120" s="80" t="n">
-        <v>215850</v>
+        <v>214725</v>
       </c>
       <c r="J120" s="80">
         <f>I120-G120</f>
@@ -15886,13 +15986,13 @@
         <v/>
       </c>
       <c r="G121" s="80" t="n">
-        <v>191997</v>
+        <v>191034</v>
       </c>
       <c r="H121" s="80" t="n">
-        <v>201698</v>
+        <v>200671</v>
       </c>
       <c r="I121" s="80" t="n">
-        <v>212059</v>
+        <v>210962</v>
       </c>
       <c r="J121" s="80">
         <f>I121-G121</f>
@@ -15947,13 +16047,13 @@
         <v/>
       </c>
       <c r="G122" s="80" t="n">
-        <v>191997</v>
+        <v>191034</v>
       </c>
       <c r="H122" s="80" t="n">
-        <v>201698</v>
+        <v>200671</v>
       </c>
       <c r="I122" s="80" t="n">
-        <v>212059</v>
+        <v>210962</v>
       </c>
       <c r="J122" s="80">
         <f>I122-G122</f>
@@ -16008,13 +16108,13 @@
         <v/>
       </c>
       <c r="G123" s="75" t="n">
-        <v>740212</v>
+        <v>736367</v>
       </c>
       <c r="H123" s="75" t="n">
-        <v>777405</v>
+        <v>773325</v>
       </c>
       <c r="I123" s="75" t="n">
-        <v>819648</v>
+        <v>815244</v>
       </c>
       <c r="J123" s="75">
         <f>I123-G123</f>
@@ -16069,13 +16169,13 @@
         <v/>
       </c>
       <c r="G124" s="80" t="n">
-        <v>740212</v>
+        <v>736367</v>
       </c>
       <c r="H124" s="80" t="n">
-        <v>777405</v>
+        <v>773325</v>
       </c>
       <c r="I124" s="80" t="n">
-        <v>819648</v>
+        <v>815244</v>
       </c>
       <c r="J124" s="80">
         <f>I124-G124</f>
@@ -16130,13 +16230,13 @@
         <v/>
       </c>
       <c r="G125" s="80" t="n">
-        <v>262755</v>
+        <v>261444</v>
       </c>
       <c r="H125" s="80" t="n">
-        <v>279012</v>
+        <v>277603</v>
       </c>
       <c r="I125" s="80" t="n">
-        <v>294344</v>
+        <v>292825</v>
       </c>
       <c r="J125" s="80">
         <f>I125-G125</f>
@@ -16191,13 +16291,13 @@
         <v/>
       </c>
       <c r="G126" s="80" t="n">
-        <v>262755</v>
+        <v>261444</v>
       </c>
       <c r="H126" s="80" t="n">
-        <v>279012</v>
+        <v>277603</v>
       </c>
       <c r="I126" s="80" t="n">
-        <v>294344</v>
+        <v>292825</v>
       </c>
       <c r="J126" s="80">
         <f>I126-G126</f>
@@ -16252,13 +16352,13 @@
         <v/>
       </c>
       <c r="G127" s="80" t="n">
-        <v>240743</v>
+        <v>239461</v>
       </c>
       <c r="H127" s="80" t="n">
-        <v>251203</v>
+        <v>249853</v>
       </c>
       <c r="I127" s="80" t="n">
-        <v>264639</v>
+        <v>263181</v>
       </c>
       <c r="J127" s="80">
         <f>I127-G127</f>
@@ -16313,13 +16413,13 @@
         <v/>
       </c>
       <c r="G128" s="80" t="n">
-        <v>240743</v>
+        <v>239461</v>
       </c>
       <c r="H128" s="80" t="n">
-        <v>251203</v>
+        <v>249853</v>
       </c>
       <c r="I128" s="80" t="n">
-        <v>264639</v>
+        <v>263181</v>
       </c>
       <c r="J128" s="80">
         <f>I128-G128</f>
@@ -16374,13 +16474,13 @@
         <v/>
       </c>
       <c r="G129" s="80" t="n">
-        <v>236714</v>
+        <v>235462</v>
       </c>
       <c r="H129" s="80" t="n">
-        <v>247189</v>
+        <v>245870</v>
       </c>
       <c r="I129" s="80" t="n">
-        <v>260666</v>
+        <v>259238</v>
       </c>
       <c r="J129" s="80">
         <f>I129-G129</f>
@@ -16435,13 +16535,13 @@
         <v/>
       </c>
       <c r="G130" s="80" t="n">
-        <v>236714</v>
+        <v>235462</v>
       </c>
       <c r="H130" s="80" t="n">
-        <v>247189</v>
+        <v>245870</v>
       </c>
       <c r="I130" s="80" t="n">
-        <v>260666</v>
+        <v>259238</v>
       </c>
       <c r="J130" s="80">
         <f>I130-G130</f>
@@ -16496,13 +16596,13 @@
         <v/>
       </c>
       <c r="G131" s="75" t="n">
-        <v>599798</v>
+        <v>596824</v>
       </c>
       <c r="H131" s="75" t="n">
-        <v>630069</v>
+        <v>626905</v>
       </c>
       <c r="I131" s="75" t="n">
-        <v>662483</v>
+        <v>659107</v>
       </c>
       <c r="J131" s="75">
         <f>I131-G131</f>
@@ -16557,13 +16657,13 @@
         <v/>
       </c>
       <c r="G132" s="80" t="n">
-        <v>599798</v>
+        <v>596824</v>
       </c>
       <c r="H132" s="80" t="n">
-        <v>630069</v>
+        <v>626905</v>
       </c>
       <c r="I132" s="80" t="n">
-        <v>662483</v>
+        <v>659107</v>
       </c>
       <c r="J132" s="80">
         <f>I132-G132</f>
@@ -16618,13 +16718,13 @@
         <v/>
       </c>
       <c r="G133" s="80" t="n">
-        <v>211982</v>
+        <v>210962</v>
       </c>
       <c r="H133" s="80" t="n">
-        <v>222873</v>
+        <v>221790</v>
       </c>
       <c r="I133" s="80" t="n">
-        <v>234575</v>
+        <v>233420</v>
       </c>
       <c r="J133" s="80">
         <f>I133-G133</f>
@@ -16679,13 +16779,13 @@
         <v/>
       </c>
       <c r="G134" s="80" t="n">
-        <v>211982</v>
+        <v>210962</v>
       </c>
       <c r="H134" s="80" t="n">
-        <v>222873</v>
+        <v>221790</v>
       </c>
       <c r="I134" s="80" t="n">
-        <v>234575</v>
+        <v>233420</v>
       </c>
       <c r="J134" s="80">
         <f>I134-G134</f>
@@ -16740,13 +16840,13 @@
         <v/>
       </c>
       <c r="G135" s="80" t="n">
-        <v>195819</v>
+        <v>194828</v>
       </c>
       <c r="H135" s="80" t="n">
-        <v>205498</v>
+        <v>204443</v>
       </c>
       <c r="I135" s="80" t="n">
-        <v>215850</v>
+        <v>214725</v>
       </c>
       <c r="J135" s="80">
         <f>I135-G135</f>
@@ -16801,13 +16901,13 @@
         <v/>
       </c>
       <c r="G136" s="80" t="n">
-        <v>195819</v>
+        <v>194828</v>
       </c>
       <c r="H136" s="80" t="n">
-        <v>205498</v>
+        <v>204443</v>
       </c>
       <c r="I136" s="80" t="n">
-        <v>215850</v>
+        <v>214725</v>
       </c>
       <c r="J136" s="80">
         <f>I136-G136</f>
@@ -16862,13 +16962,13 @@
         <v/>
       </c>
       <c r="G137" s="80" t="n">
-        <v>191997</v>
+        <v>191034</v>
       </c>
       <c r="H137" s="80" t="n">
-        <v>201698</v>
+        <v>200671</v>
       </c>
       <c r="I137" s="80" t="n">
-        <v>212059</v>
+        <v>210962</v>
       </c>
       <c r="J137" s="80">
         <f>I137-G137</f>
@@ -16923,13 +17023,13 @@
         <v/>
       </c>
       <c r="G138" s="80" t="n">
-        <v>191997</v>
+        <v>191034</v>
       </c>
       <c r="H138" s="80" t="n">
-        <v>201698</v>
+        <v>200671</v>
       </c>
       <c r="I138" s="80" t="n">
-        <v>212059</v>
+        <v>210962</v>
       </c>
       <c r="J138" s="80">
         <f>I138-G138</f>
@@ -16967,13 +17067,13 @@
         </is>
       </c>
       <c r="B139" s="70" t="n">
-        <v>1913220</v>
+        <v>2403570</v>
       </c>
       <c r="C139" s="70" t="n">
-        <v>2018980</v>
+        <v>2537610</v>
       </c>
       <c r="D139" s="70" t="n">
-        <v>2152220</v>
+        <v>2706480</v>
       </c>
       <c r="E139" s="70">
         <f>D139-B139</f>
@@ -16984,13 +17084,13 @@
         <v/>
       </c>
       <c r="G139" s="70" t="n">
-        <v>1880670</v>
+        <v>1950462</v>
       </c>
       <c r="H139" s="70" t="n">
-        <v>1974858</v>
+        <v>2049161</v>
       </c>
       <c r="I139" s="70" t="n">
-        <v>2080707</v>
+        <v>2160548</v>
       </c>
       <c r="J139" s="70">
         <f>I139-G139</f>
@@ -17016,7 +17116,7 @@
         <f>N139-L139</f>
         <v/>
       </c>
-      <c r="P139" s="90">
+      <c r="P139" s="72">
         <f>IFERROR(N139/D139,0)</f>
         <v/>
       </c>
@@ -17028,13 +17128,13 @@
         </is>
       </c>
       <c r="B140" s="75" t="n">
-        <v>800190</v>
+        <v>1003890</v>
       </c>
       <c r="C140" s="75" t="n">
-        <v>850990</v>
+        <v>1068270</v>
       </c>
       <c r="D140" s="75" t="n">
-        <v>901790</v>
+        <v>1132650</v>
       </c>
       <c r="E140" s="75">
         <f>D140-B140</f>
@@ -17045,13 +17145,13 @@
         <v/>
       </c>
       <c r="G140" s="75" t="n">
-        <v>848965</v>
+        <v>877923</v>
       </c>
       <c r="H140" s="75" t="n">
-        <v>892260</v>
+        <v>923355</v>
       </c>
       <c r="I140" s="75" t="n">
-        <v>938654</v>
+        <v>971873</v>
       </c>
       <c r="J140" s="75">
         <f>I140-G140</f>
@@ -17077,7 +17177,7 @@
         <f>N140-L140</f>
         <v/>
       </c>
-      <c r="P140" s="88">
+      <c r="P140" s="77">
         <f>IFERROR(N140/D140,0)</f>
         <v/>
       </c>
@@ -17089,13 +17189,13 @@
         </is>
       </c>
       <c r="B141" s="80" t="n">
-        <v>430650</v>
+        <v>634350</v>
       </c>
       <c r="C141" s="80" t="n">
-        <v>457990</v>
+        <v>675270</v>
       </c>
       <c r="D141" s="80" t="n">
-        <v>485330</v>
+        <v>716190</v>
       </c>
       <c r="E141" s="80">
         <f>D141-B141</f>
@@ -17106,13 +17206,13 @@
         <v/>
       </c>
       <c r="G141" s="80" t="n">
-        <v>398468</v>
+        <v>496763</v>
       </c>
       <c r="H141" s="80" t="n">
-        <v>418923</v>
+        <v>522675</v>
       </c>
       <c r="I141" s="80" t="n">
-        <v>440821</v>
+        <v>550306</v>
       </c>
       <c r="J141" s="80">
         <f>I141-G141</f>
@@ -17167,13 +17267,13 @@
         <v/>
       </c>
       <c r="G142" s="80" t="n">
-        <v>205962</v>
+        <v>175362</v>
       </c>
       <c r="H142" s="80" t="n">
-        <v>216620</v>
+        <v>184566</v>
       </c>
       <c r="I142" s="80" t="n">
-        <v>228054</v>
+        <v>194418</v>
       </c>
       <c r="J142" s="80">
         <f>I142-G142</f>
@@ -17228,13 +17328,13 @@
         <v/>
       </c>
       <c r="G143" s="80" t="n">
-        <v>205962</v>
+        <v>175362</v>
       </c>
       <c r="H143" s="80" t="n">
-        <v>216620</v>
+        <v>184566</v>
       </c>
       <c r="I143" s="80" t="n">
-        <v>228054</v>
+        <v>194418</v>
       </c>
       <c r="J143" s="80">
         <f>I143-G143</f>
@@ -17268,7 +17368,7 @@
     <row r="144" hidden="1" outlineLevel="3">
       <c r="A144" s="83" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="B144" s="80" t="n">
@@ -17289,13 +17389,13 @@
         <v/>
       </c>
       <c r="G144" s="80" t="n">
-        <v>192506</v>
+        <v>162562</v>
       </c>
       <c r="H144" s="80" t="n">
-        <v>202303</v>
+        <v>170897</v>
       </c>
       <c r="I144" s="80" t="n">
-        <v>212768</v>
+        <v>179774</v>
       </c>
       <c r="J144" s="80">
         <f>I144-G144</f>
@@ -17350,13 +17450,13 @@
         <v/>
       </c>
       <c r="G145" s="80" t="n">
-        <v>192506</v>
+        <v>162562</v>
       </c>
       <c r="H145" s="80" t="n">
-        <v>202303</v>
+        <v>170897</v>
       </c>
       <c r="I145" s="80" t="n">
-        <v>212768</v>
+        <v>179774</v>
       </c>
       <c r="J145" s="80">
         <f>I145-G145</f>
@@ -17387,20 +17487,20 @@
         <v/>
       </c>
     </row>
-    <row r="146" hidden="1" outlineLevel="2">
-      <c r="A146" s="78" t="inlineStr">
-        <is>
-          <t>BTS_GES</t>
+    <row r="146" hidden="1" outlineLevel="3">
+      <c r="A146" s="83" t="inlineStr">
+        <is>
+          <t>B3</t>
         </is>
       </c>
       <c r="B146" s="80" t="n">
-        <v>369540</v>
+        <v>203700</v>
       </c>
       <c r="C146" s="80" t="n">
-        <v>393000</v>
+        <v>217280</v>
       </c>
       <c r="D146" s="80" t="n">
-        <v>416460</v>
+        <v>230860</v>
       </c>
       <c r="E146" s="80">
         <f>D146-B146</f>
@@ -17411,13 +17511,13 @@
         <v/>
       </c>
       <c r="G146" s="80" t="n">
-        <v>450498</v>
+        <v>158839</v>
       </c>
       <c r="H146" s="80" t="n">
-        <v>473337</v>
+        <v>167213</v>
       </c>
       <c r="I146" s="80" t="n">
-        <v>497833</v>
+        <v>176114</v>
       </c>
       <c r="J146" s="80">
         <f>I146-G146</f>
@@ -17443,25 +17543,25 @@
         <f>N146-L146</f>
         <v/>
       </c>
-      <c r="P146" s="86">
+      <c r="P146" s="82">
         <f>IFERROR(N146/D146,0)</f>
         <v/>
       </c>
     </row>
-    <row r="147" hidden="1" outlineLevel="3">
-      <c r="A147" s="83" t="inlineStr">
-        <is>
-          <t>BTS1</t>
+    <row r="147" hidden="1" outlineLevel="4">
+      <c r="A147" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
         </is>
       </c>
       <c r="B147" s="80" t="n">
-        <v>189120</v>
+        <v>203700</v>
       </c>
       <c r="C147" s="80" t="n">
-        <v>200940</v>
+        <v>217280</v>
       </c>
       <c r="D147" s="80" t="n">
-        <v>212760</v>
+        <v>230860</v>
       </c>
       <c r="E147" s="80">
         <f>D147-B147</f>
@@ -17472,13 +17572,13 @@
         <v/>
       </c>
       <c r="G147" s="80" t="n">
-        <v>231977</v>
+        <v>158839</v>
       </c>
       <c r="H147" s="80" t="n">
-        <v>243827</v>
+        <v>167213</v>
       </c>
       <c r="I147" s="80" t="n">
-        <v>256559</v>
+        <v>176114</v>
       </c>
       <c r="J147" s="80">
         <f>I147-G147</f>
@@ -17504,25 +17604,25 @@
         <f>N147-L147</f>
         <v/>
       </c>
-      <c r="P147" s="86">
+      <c r="P147" s="82">
         <f>IFERROR(N147/D147,0)</f>
         <v/>
       </c>
     </row>
-    <row r="148" hidden="1" outlineLevel="4">
-      <c r="A148" s="84" t="inlineStr">
-        <is>
-          <t>Alternance</t>
+    <row r="148" hidden="1" outlineLevel="2">
+      <c r="A148" s="78" t="inlineStr">
+        <is>
+          <t>BTS_GES</t>
         </is>
       </c>
       <c r="B148" s="80" t="n">
-        <v>189120</v>
+        <v>369540</v>
       </c>
       <c r="C148" s="80" t="n">
-        <v>200940</v>
+        <v>393000</v>
       </c>
       <c r="D148" s="80" t="n">
-        <v>212760</v>
+        <v>416460</v>
       </c>
       <c r="E148" s="80">
         <f>D148-B148</f>
@@ -17533,13 +17633,13 @@
         <v/>
       </c>
       <c r="G148" s="80" t="n">
-        <v>231977</v>
+        <v>381160</v>
       </c>
       <c r="H148" s="80" t="n">
-        <v>243827</v>
+        <v>400680</v>
       </c>
       <c r="I148" s="80" t="n">
-        <v>256559</v>
+        <v>421567</v>
       </c>
       <c r="J148" s="80">
         <f>I148-G148</f>
@@ -17573,17 +17673,17 @@
     <row r="149" hidden="1" outlineLevel="3">
       <c r="A149" s="83" t="inlineStr">
         <is>
-          <t>BTS2</t>
+          <t>BTS1</t>
         </is>
       </c>
       <c r="B149" s="80" t="n">
-        <v>180420</v>
+        <v>189120</v>
       </c>
       <c r="C149" s="80" t="n">
-        <v>192060</v>
+        <v>200940</v>
       </c>
       <c r="D149" s="80" t="n">
-        <v>203700</v>
+        <v>212760</v>
       </c>
       <c r="E149" s="80">
         <f>D149-B149</f>
@@ -17594,13 +17694,13 @@
         <v/>
       </c>
       <c r="G149" s="80" t="n">
-        <v>218521</v>
+        <v>196980</v>
       </c>
       <c r="H149" s="80" t="n">
-        <v>229510</v>
+        <v>207175</v>
       </c>
       <c r="I149" s="80" t="n">
-        <v>241273</v>
+        <v>218106</v>
       </c>
       <c r="J149" s="80">
         <f>I149-G149</f>
@@ -17638,13 +17738,13 @@
         </is>
       </c>
       <c r="B150" s="80" t="n">
-        <v>180420</v>
+        <v>189120</v>
       </c>
       <c r="C150" s="80" t="n">
-        <v>192060</v>
+        <v>200940</v>
       </c>
       <c r="D150" s="80" t="n">
-        <v>203700</v>
+        <v>212760</v>
       </c>
       <c r="E150" s="80">
         <f>D150-B150</f>
@@ -17655,13 +17755,13 @@
         <v/>
       </c>
       <c r="G150" s="80" t="n">
-        <v>218521</v>
+        <v>196980</v>
       </c>
       <c r="H150" s="80" t="n">
-        <v>229510</v>
+        <v>207175</v>
       </c>
       <c r="I150" s="80" t="n">
-        <v>241273</v>
+        <v>218106</v>
       </c>
       <c r="J150" s="80">
         <f>I150-G150</f>
@@ -17692,81 +17792,81 @@
         <v/>
       </c>
     </row>
-    <row r="151" outlineLevel="1">
-      <c r="A151" s="73" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="B151" s="75" t="n">
-        <v>1113030</v>
-      </c>
-      <c r="C151" s="75" t="n">
-        <v>1167990</v>
-      </c>
-      <c r="D151" s="75" t="n">
-        <v>1250430</v>
-      </c>
-      <c r="E151" s="75">
+    <row r="151" hidden="1" outlineLevel="3">
+      <c r="A151" s="83" t="inlineStr">
+        <is>
+          <t>BTS2</t>
+        </is>
+      </c>
+      <c r="B151" s="80" t="n">
+        <v>180420</v>
+      </c>
+      <c r="C151" s="80" t="n">
+        <v>192060</v>
+      </c>
+      <c r="D151" s="80" t="n">
+        <v>203700</v>
+      </c>
+      <c r="E151" s="80">
         <f>D151-B151</f>
         <v/>
       </c>
-      <c r="F151" s="101">
+      <c r="F151" s="103">
         <f>IFERROR(D151/B151-1,0)</f>
         <v/>
       </c>
-      <c r="G151" s="75" t="n">
-        <v>1031704</v>
-      </c>
-      <c r="H151" s="75" t="n">
-        <v>1082598</v>
-      </c>
-      <c r="I151" s="75" t="n">
-        <v>1142053</v>
-      </c>
-      <c r="J151" s="75">
+      <c r="G151" s="80" t="n">
+        <v>184180</v>
+      </c>
+      <c r="H151" s="80" t="n">
+        <v>193505</v>
+      </c>
+      <c r="I151" s="80" t="n">
+        <v>203462</v>
+      </c>
+      <c r="J151" s="80">
         <f>I151-G151</f>
         <v/>
       </c>
-      <c r="K151" s="101">
+      <c r="K151" s="103">
         <f>IFERROR(I151/G151-1,0)</f>
         <v/>
       </c>
-      <c r="L151" s="75">
+      <c r="L151" s="80">
         <f>B151-G151</f>
         <v/>
       </c>
-      <c r="M151" s="75">
+      <c r="M151" s="80">
         <f>C151-H151</f>
         <v/>
       </c>
-      <c r="N151" s="102">
+      <c r="N151" s="81">
         <f>D151-I151</f>
         <v/>
       </c>
-      <c r="O151" s="75">
+      <c r="O151" s="80">
         <f>N151-L151</f>
         <v/>
       </c>
-      <c r="P151" s="77">
+      <c r="P151" s="86">
         <f>IFERROR(N151/D151,0)</f>
         <v/>
       </c>
     </row>
-    <row r="152" hidden="1" outlineLevel="2">
-      <c r="A152" s="78" t="inlineStr">
-        <is>
-          <t>BAC_RH</t>
+    <row r="152" hidden="1" outlineLevel="4">
+      <c r="A152" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
         </is>
       </c>
       <c r="B152" s="80" t="n">
-        <v>599040</v>
+        <v>180420</v>
       </c>
       <c r="C152" s="80" t="n">
-        <v>628620</v>
+        <v>192060</v>
       </c>
       <c r="D152" s="80" t="n">
-        <v>672990</v>
+        <v>203700</v>
       </c>
       <c r="E152" s="80">
         <f>D152-B152</f>
@@ -17777,13 +17877,13 @@
         <v/>
       </c>
       <c r="G152" s="80" t="n">
-        <v>488651</v>
+        <v>184180</v>
       </c>
       <c r="H152" s="80" t="n">
-        <v>512851</v>
+        <v>193505</v>
       </c>
       <c r="I152" s="80" t="n">
-        <v>541220</v>
+        <v>203462</v>
       </c>
       <c r="J152" s="80">
         <f>I152-G152</f>
@@ -17809,86 +17909,86 @@
         <f>N152-L152</f>
         <v/>
       </c>
-      <c r="P152" s="82">
+      <c r="P152" s="86">
         <f>IFERROR(N152/D152,0)</f>
         <v/>
       </c>
     </row>
-    <row r="153" hidden="1" outlineLevel="3">
-      <c r="A153" s="83" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B153" s="80" t="n">
-        <v>305040</v>
-      </c>
-      <c r="C153" s="80" t="n">
-        <v>319920</v>
-      </c>
-      <c r="D153" s="80" t="n">
-        <v>342240</v>
-      </c>
-      <c r="E153" s="80">
+    <row r="153" outlineLevel="1">
+      <c r="A153" s="73" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="B153" s="75" t="n">
+        <v>1399680</v>
+      </c>
+      <c r="C153" s="75" t="n">
+        <v>1469340</v>
+      </c>
+      <c r="D153" s="75" t="n">
+        <v>1573830</v>
+      </c>
+      <c r="E153" s="75">
         <f>D153-B153</f>
         <v/>
       </c>
-      <c r="F153" s="103">
+      <c r="F153" s="101">
         <f>IFERROR(D153/B153-1,0)</f>
         <v/>
       </c>
-      <c r="G153" s="80" t="n">
-        <v>254080</v>
-      </c>
-      <c r="H153" s="80" t="n">
-        <v>266935</v>
-      </c>
-      <c r="I153" s="80" t="n">
-        <v>281922</v>
-      </c>
-      <c r="J153" s="80">
+      <c r="G153" s="75" t="n">
+        <v>1072540</v>
+      </c>
+      <c r="H153" s="75" t="n">
+        <v>1125806</v>
+      </c>
+      <c r="I153" s="75" t="n">
+        <v>1188675</v>
+      </c>
+      <c r="J153" s="75">
         <f>I153-G153</f>
         <v/>
       </c>
-      <c r="K153" s="103">
+      <c r="K153" s="101">
         <f>IFERROR(I153/G153-1,0)</f>
         <v/>
       </c>
-      <c r="L153" s="80">
+      <c r="L153" s="75">
         <f>B153-G153</f>
         <v/>
       </c>
-      <c r="M153" s="80">
+      <c r="M153" s="75">
         <f>C153-H153</f>
         <v/>
       </c>
-      <c r="N153" s="81">
+      <c r="N153" s="102">
         <f>D153-I153</f>
         <v/>
       </c>
-      <c r="O153" s="80">
+      <c r="O153" s="75">
         <f>N153-L153</f>
         <v/>
       </c>
-      <c r="P153" s="82">
+      <c r="P153" s="77">
         <f>IFERROR(N153/D153,0)</f>
         <v/>
       </c>
     </row>
-    <row r="154" hidden="1" outlineLevel="4">
-      <c r="A154" s="84" t="inlineStr">
-        <is>
-          <t>Alternance</t>
+    <row r="154" hidden="1" outlineLevel="2">
+      <c r="A154" s="78" t="inlineStr">
+        <is>
+          <t>BAC_RH</t>
         </is>
       </c>
       <c r="B154" s="80" t="n">
-        <v>305040</v>
+        <v>885690</v>
       </c>
       <c r="C154" s="80" t="n">
-        <v>319920</v>
+        <v>929970</v>
       </c>
       <c r="D154" s="80" t="n">
-        <v>342240</v>
+        <v>996390</v>
       </c>
       <c r="E154" s="80">
         <f>D154-B154</f>
@@ -17899,13 +17999,13 @@
         <v/>
       </c>
       <c r="G154" s="80" t="n">
-        <v>254080</v>
+        <v>611133</v>
       </c>
       <c r="H154" s="80" t="n">
-        <v>266935</v>
+        <v>641548</v>
       </c>
       <c r="I154" s="80" t="n">
-        <v>281922</v>
+        <v>677612</v>
       </c>
       <c r="J154" s="80">
         <f>I154-G154</f>
@@ -17939,17 +18039,17 @@
     <row r="155" hidden="1" outlineLevel="3">
       <c r="A155" s="83" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B155" s="80" t="n">
-        <v>294000</v>
+        <v>305040</v>
       </c>
       <c r="C155" s="80" t="n">
-        <v>308700</v>
+        <v>319920</v>
       </c>
       <c r="D155" s="80" t="n">
-        <v>330750</v>
+        <v>342240</v>
       </c>
       <c r="E155" s="80">
         <f>D155-B155</f>
@@ -17960,13 +18060,13 @@
         <v/>
       </c>
       <c r="G155" s="80" t="n">
-        <v>234571</v>
+        <v>217531</v>
       </c>
       <c r="H155" s="80" t="n">
-        <v>245916</v>
+        <v>228676</v>
       </c>
       <c r="I155" s="80" t="n">
-        <v>259299</v>
+        <v>241758</v>
       </c>
       <c r="J155" s="80">
         <f>I155-G155</f>
@@ -18004,13 +18104,13 @@
         </is>
       </c>
       <c r="B156" s="80" t="n">
-        <v>294000</v>
+        <v>305040</v>
       </c>
       <c r="C156" s="80" t="n">
-        <v>308700</v>
+        <v>319920</v>
       </c>
       <c r="D156" s="80" t="n">
-        <v>330750</v>
+        <v>342240</v>
       </c>
       <c r="E156" s="80">
         <f>D156-B156</f>
@@ -18021,13 +18121,13 @@
         <v/>
       </c>
       <c r="G156" s="80" t="n">
-        <v>234571</v>
+        <v>217531</v>
       </c>
       <c r="H156" s="80" t="n">
-        <v>245916</v>
+        <v>228676</v>
       </c>
       <c r="I156" s="80" t="n">
-        <v>259299</v>
+        <v>241758</v>
       </c>
       <c r="J156" s="80">
         <f>I156-G156</f>
@@ -18058,20 +18158,20 @@
         <v/>
       </c>
     </row>
-    <row r="157" hidden="1" outlineLevel="2">
-      <c r="A157" s="78" t="inlineStr">
-        <is>
-          <t>BTS_GES</t>
+    <row r="157" hidden="1" outlineLevel="3">
+      <c r="A157" s="83" t="inlineStr">
+        <is>
+          <t>B2</t>
         </is>
       </c>
       <c r="B157" s="80" t="n">
-        <v>513990</v>
+        <v>294000</v>
       </c>
       <c r="C157" s="80" t="n">
-        <v>539370</v>
+        <v>308700</v>
       </c>
       <c r="D157" s="80" t="n">
-        <v>577440</v>
+        <v>330750</v>
       </c>
       <c r="E157" s="80">
         <f>D157-B157</f>
@@ -18082,13 +18182,13 @@
         <v/>
       </c>
       <c r="G157" s="80" t="n">
-        <v>543054</v>
+        <v>198668</v>
       </c>
       <c r="H157" s="80" t="n">
-        <v>569747</v>
+        <v>208302</v>
       </c>
       <c r="I157" s="80" t="n">
-        <v>600832</v>
+        <v>219769</v>
       </c>
       <c r="J157" s="80">
         <f>I157-G157</f>
@@ -18114,25 +18214,25 @@
         <f>N157-L157</f>
         <v/>
       </c>
-      <c r="P157" s="86">
+      <c r="P157" s="82">
         <f>IFERROR(N157/D157,0)</f>
         <v/>
       </c>
     </row>
-    <row r="158" hidden="1" outlineLevel="3">
-      <c r="A158" s="83" t="inlineStr">
-        <is>
-          <t>BTS1</t>
+    <row r="158" hidden="1" outlineLevel="4">
+      <c r="A158" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
         </is>
       </c>
       <c r="B158" s="80" t="n">
-        <v>261990</v>
+        <v>294000</v>
       </c>
       <c r="C158" s="80" t="n">
-        <v>274770</v>
+        <v>308700</v>
       </c>
       <c r="D158" s="80" t="n">
-        <v>293940</v>
+        <v>330750</v>
       </c>
       <c r="E158" s="80">
         <f>D158-B158</f>
@@ -18143,13 +18243,13 @@
         <v/>
       </c>
       <c r="G158" s="80" t="n">
-        <v>281282</v>
+        <v>198668</v>
       </c>
       <c r="H158" s="80" t="n">
-        <v>295383</v>
+        <v>208302</v>
       </c>
       <c r="I158" s="80" t="n">
-        <v>311728</v>
+        <v>219769</v>
       </c>
       <c r="J158" s="80">
         <f>I158-G158</f>
@@ -18175,25 +18275,25 @@
         <f>N158-L158</f>
         <v/>
       </c>
-      <c r="P158" s="86">
+      <c r="P158" s="82">
         <f>IFERROR(N158/D158,0)</f>
         <v/>
       </c>
     </row>
-    <row r="159" hidden="1" outlineLevel="4">
-      <c r="A159" s="84" t="inlineStr">
-        <is>
-          <t>Alternance</t>
+    <row r="159" hidden="1" outlineLevel="3">
+      <c r="A159" s="83" t="inlineStr">
+        <is>
+          <t>B3</t>
         </is>
       </c>
       <c r="B159" s="80" t="n">
-        <v>261990</v>
+        <v>286650</v>
       </c>
       <c r="C159" s="80" t="n">
-        <v>274770</v>
+        <v>301350</v>
       </c>
       <c r="D159" s="80" t="n">
-        <v>293940</v>
+        <v>323400</v>
       </c>
       <c r="E159" s="80">
         <f>D159-B159</f>
@@ -18204,13 +18304,13 @@
         <v/>
       </c>
       <c r="G159" s="80" t="n">
-        <v>281282</v>
+        <v>194934</v>
       </c>
       <c r="H159" s="80" t="n">
-        <v>295383</v>
+        <v>204571</v>
       </c>
       <c r="I159" s="80" t="n">
-        <v>311728</v>
+        <v>216086</v>
       </c>
       <c r="J159" s="80">
         <f>I159-G159</f>
@@ -18236,25 +18336,25 @@
         <f>N159-L159</f>
         <v/>
       </c>
-      <c r="P159" s="86">
+      <c r="P159" s="82">
         <f>IFERROR(N159/D159,0)</f>
         <v/>
       </c>
     </row>
-    <row r="160" hidden="1" outlineLevel="3">
-      <c r="A160" s="83" t="inlineStr">
-        <is>
-          <t>BTS2</t>
+    <row r="160" hidden="1" outlineLevel="4">
+      <c r="A160" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
         </is>
       </c>
       <c r="B160" s="80" t="n">
-        <v>252000</v>
+        <v>286650</v>
       </c>
       <c r="C160" s="80" t="n">
-        <v>264600</v>
+        <v>301350</v>
       </c>
       <c r="D160" s="80" t="n">
-        <v>283500</v>
+        <v>323400</v>
       </c>
       <c r="E160" s="80">
         <f>D160-B160</f>
@@ -18265,13 +18365,13 @@
         <v/>
       </c>
       <c r="G160" s="80" t="n">
-        <v>261772</v>
+        <v>194934</v>
       </c>
       <c r="H160" s="80" t="n">
-        <v>274364</v>
+        <v>204571</v>
       </c>
       <c r="I160" s="80" t="n">
-        <v>289105</v>
+        <v>216086</v>
       </c>
       <c r="J160" s="80">
         <f>I160-G160</f>
@@ -18297,25 +18397,25 @@
         <f>N160-L160</f>
         <v/>
       </c>
-      <c r="P160" s="86">
+      <c r="P160" s="82">
         <f>IFERROR(N160/D160,0)</f>
         <v/>
       </c>
     </row>
-    <row r="161" hidden="1" outlineLevel="4">
-      <c r="A161" s="84" t="inlineStr">
-        <is>
-          <t>Alternance</t>
+    <row r="161" hidden="1" outlineLevel="2">
+      <c r="A161" s="78" t="inlineStr">
+        <is>
+          <t>BTS_GES</t>
         </is>
       </c>
       <c r="B161" s="80" t="n">
-        <v>252000</v>
+        <v>513990</v>
       </c>
       <c r="C161" s="80" t="n">
-        <v>264600</v>
+        <v>539370</v>
       </c>
       <c r="D161" s="80" t="n">
-        <v>283500</v>
+        <v>577440</v>
       </c>
       <c r="E161" s="80">
         <f>D161-B161</f>
@@ -18326,13 +18426,13 @@
         <v/>
       </c>
       <c r="G161" s="80" t="n">
-        <v>261772</v>
+        <v>461407</v>
       </c>
       <c r="H161" s="80" t="n">
-        <v>274364</v>
+        <v>484257</v>
       </c>
       <c r="I161" s="80" t="n">
-        <v>289105</v>
+        <v>511063</v>
       </c>
       <c r="J161" s="80">
         <f>I161-G161</f>
@@ -18358,147 +18458,147 @@
         <f>N161-L161</f>
         <v/>
       </c>
-      <c r="P161" s="86">
+      <c r="P161" s="82">
         <f>IFERROR(N161/D161,0)</f>
         <v/>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="68" t="inlineStr">
-        <is>
-          <t>Tunon</t>
-        </is>
-      </c>
-      <c r="B162" s="70" t="n">
-        <v>1743090</v>
-      </c>
-      <c r="C162" s="70" t="n">
-        <v>1834590</v>
-      </c>
-      <c r="D162" s="70" t="n">
-        <v>1949700</v>
-      </c>
-      <c r="E162" s="70">
+    <row r="162" hidden="1" outlineLevel="3">
+      <c r="A162" s="83" t="inlineStr">
+        <is>
+          <t>BTS1</t>
+        </is>
+      </c>
+      <c r="B162" s="80" t="n">
+        <v>261990</v>
+      </c>
+      <c r="C162" s="80" t="n">
+        <v>274770</v>
+      </c>
+      <c r="D162" s="80" t="n">
+        <v>293940</v>
+      </c>
+      <c r="E162" s="80">
         <f>D162-B162</f>
         <v/>
       </c>
-      <c r="F162" s="98">
+      <c r="F162" s="103">
         <f>IFERROR(D162/B162-1,0)</f>
         <v/>
       </c>
-      <c r="G162" s="70" t="n">
-        <v>1701189</v>
-      </c>
-      <c r="H162" s="70" t="n">
-        <v>1784825</v>
-      </c>
-      <c r="I162" s="70" t="n">
-        <v>1878371</v>
-      </c>
-      <c r="J162" s="70">
+      <c r="G162" s="80" t="n">
+        <v>240135</v>
+      </c>
+      <c r="H162" s="80" t="n">
+        <v>252315</v>
+      </c>
+      <c r="I162" s="80" t="n">
+        <v>266526</v>
+      </c>
+      <c r="J162" s="80">
         <f>I162-G162</f>
         <v/>
       </c>
-      <c r="K162" s="98">
+      <c r="K162" s="103">
         <f>IFERROR(I162/G162-1,0)</f>
         <v/>
       </c>
-      <c r="L162" s="70">
+      <c r="L162" s="80">
         <f>B162-G162</f>
         <v/>
       </c>
-      <c r="M162" s="70">
+      <c r="M162" s="80">
         <f>C162-H162</f>
         <v/>
       </c>
-      <c r="N162" s="99">
+      <c r="N162" s="81">
         <f>D162-I162</f>
         <v/>
       </c>
-      <c r="O162" s="70">
+      <c r="O162" s="80">
         <f>N162-L162</f>
         <v/>
       </c>
-      <c r="P162" s="90">
+      <c r="P162" s="82">
         <f>IFERROR(N162/D162,0)</f>
         <v/>
       </c>
     </row>
-    <row r="163" outlineLevel="1">
-      <c r="A163" s="73" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="B163" s="75" t="n">
-        <v>774990</v>
-      </c>
-      <c r="C163" s="75" t="n">
-        <v>819270</v>
-      </c>
-      <c r="D163" s="75" t="n">
-        <v>863550</v>
-      </c>
-      <c r="E163" s="75">
+    <row r="163" hidden="1" outlineLevel="4">
+      <c r="A163" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
+        </is>
+      </c>
+      <c r="B163" s="80" t="n">
+        <v>261990</v>
+      </c>
+      <c r="C163" s="80" t="n">
+        <v>274770</v>
+      </c>
+      <c r="D163" s="80" t="n">
+        <v>293940</v>
+      </c>
+      <c r="E163" s="80">
         <f>D163-B163</f>
         <v/>
       </c>
-      <c r="F163" s="101">
+      <c r="F163" s="103">
         <f>IFERROR(D163/B163-1,0)</f>
         <v/>
       </c>
-      <c r="G163" s="75" t="n">
-        <v>699956</v>
-      </c>
-      <c r="H163" s="75" t="n">
-        <v>734974</v>
-      </c>
-      <c r="I163" s="75" t="n">
-        <v>772544</v>
-      </c>
-      <c r="J163" s="75">
+      <c r="G163" s="80" t="n">
+        <v>240135</v>
+      </c>
+      <c r="H163" s="80" t="n">
+        <v>252315</v>
+      </c>
+      <c r="I163" s="80" t="n">
+        <v>266526</v>
+      </c>
+      <c r="J163" s="80">
         <f>I163-G163</f>
         <v/>
       </c>
-      <c r="K163" s="101">
+      <c r="K163" s="103">
         <f>IFERROR(I163/G163-1,0)</f>
         <v/>
       </c>
-      <c r="L163" s="75">
+      <c r="L163" s="80">
         <f>B163-G163</f>
         <v/>
       </c>
-      <c r="M163" s="75">
+      <c r="M163" s="80">
         <f>C163-H163</f>
         <v/>
       </c>
-      <c r="N163" s="102">
+      <c r="N163" s="81">
         <f>D163-I163</f>
         <v/>
       </c>
-      <c r="O163" s="75">
+      <c r="O163" s="80">
         <f>N163-L163</f>
         <v/>
       </c>
-      <c r="P163" s="77">
+      <c r="P163" s="82">
         <f>IFERROR(N163/D163,0)</f>
         <v/>
       </c>
     </row>
-    <row r="164" hidden="1" outlineLevel="2">
-      <c r="A164" s="78" t="inlineStr">
-        <is>
-          <t>BAC_TOU</t>
+    <row r="164" hidden="1" outlineLevel="3">
+      <c r="A164" s="83" t="inlineStr">
+        <is>
+          <t>BTS2</t>
         </is>
       </c>
       <c r="B164" s="80" t="n">
-        <v>774990</v>
+        <v>252000</v>
       </c>
       <c r="C164" s="80" t="n">
-        <v>819270</v>
+        <v>264600</v>
       </c>
       <c r="D164" s="80" t="n">
-        <v>863550</v>
+        <v>283500</v>
       </c>
       <c r="E164" s="80">
         <f>D164-B164</f>
@@ -18509,13 +18609,13 @@
         <v/>
       </c>
       <c r="G164" s="80" t="n">
-        <v>699956</v>
+        <v>221272</v>
       </c>
       <c r="H164" s="80" t="n">
-        <v>734974</v>
+        <v>231942</v>
       </c>
       <c r="I164" s="80" t="n">
-        <v>772544</v>
+        <v>244537</v>
       </c>
       <c r="J164" s="80">
         <f>I164-G164</f>
@@ -18546,20 +18646,20 @@
         <v/>
       </c>
     </row>
-    <row r="165" hidden="1" outlineLevel="3">
-      <c r="A165" s="83" t="inlineStr">
-        <is>
-          <t>B1</t>
+    <row r="165" hidden="1" outlineLevel="4">
+      <c r="A165" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
         </is>
       </c>
       <c r="B165" s="80" t="n">
-        <v>267840</v>
+        <v>252000</v>
       </c>
       <c r="C165" s="80" t="n">
-        <v>282720</v>
+        <v>264600</v>
       </c>
       <c r="D165" s="80" t="n">
-        <v>297600</v>
+        <v>283500</v>
       </c>
       <c r="E165" s="80">
         <f>D165-B165</f>
@@ -18570,13 +18670,13 @@
         <v/>
       </c>
       <c r="G165" s="80" t="n">
-        <v>248138</v>
+        <v>221272</v>
       </c>
       <c r="H165" s="80" t="n">
-        <v>260820</v>
+        <v>231942</v>
       </c>
       <c r="I165" s="80" t="n">
-        <v>274474</v>
+        <v>244537</v>
       </c>
       <c r="J165" s="80">
         <f>I165-G165</f>
@@ -18607,142 +18707,142 @@
         <v/>
       </c>
     </row>
-    <row r="166" hidden="1" outlineLevel="4">
-      <c r="A166" s="84" t="inlineStr">
-        <is>
-          <t>Alternance</t>
-        </is>
-      </c>
-      <c r="B166" s="80" t="n">
-        <v>267840</v>
-      </c>
-      <c r="C166" s="80" t="n">
-        <v>282720</v>
-      </c>
-      <c r="D166" s="80" t="n">
-        <v>297600</v>
-      </c>
-      <c r="E166" s="80">
+    <row r="166">
+      <c r="A166" s="68" t="inlineStr">
+        <is>
+          <t>Tunon</t>
+        </is>
+      </c>
+      <c r="B166" s="70" t="n">
+        <v>1743090</v>
+      </c>
+      <c r="C166" s="70" t="n">
+        <v>1834590</v>
+      </c>
+      <c r="D166" s="70" t="n">
+        <v>1949700</v>
+      </c>
+      <c r="E166" s="70">
         <f>D166-B166</f>
         <v/>
       </c>
-      <c r="F166" s="103">
+      <c r="F166" s="98">
         <f>IFERROR(D166/B166-1,0)</f>
         <v/>
       </c>
-      <c r="G166" s="80" t="n">
-        <v>248138</v>
-      </c>
-      <c r="H166" s="80" t="n">
-        <v>260820</v>
-      </c>
-      <c r="I166" s="80" t="n">
-        <v>274474</v>
-      </c>
-      <c r="J166" s="80">
+      <c r="G166" s="70" t="n">
+        <v>1694603</v>
+      </c>
+      <c r="H166" s="70" t="n">
+        <v>1777848</v>
+      </c>
+      <c r="I166" s="70" t="n">
+        <v>1870864</v>
+      </c>
+      <c r="J166" s="70">
         <f>I166-G166</f>
         <v/>
       </c>
-      <c r="K166" s="103">
+      <c r="K166" s="98">
         <f>IFERROR(I166/G166-1,0)</f>
         <v/>
       </c>
-      <c r="L166" s="80">
+      <c r="L166" s="70">
         <f>B166-G166</f>
         <v/>
       </c>
-      <c r="M166" s="80">
+      <c r="M166" s="70">
         <f>C166-H166</f>
         <v/>
       </c>
-      <c r="N166" s="81">
+      <c r="N166" s="99">
         <f>D166-I166</f>
         <v/>
       </c>
-      <c r="O166" s="80">
+      <c r="O166" s="70">
         <f>N166-L166</f>
         <v/>
       </c>
-      <c r="P166" s="82">
+      <c r="P166" s="90">
         <f>IFERROR(N166/D166,0)</f>
         <v/>
       </c>
     </row>
-    <row r="167" hidden="1" outlineLevel="3">
-      <c r="A167" s="83" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B167" s="80" t="n">
-        <v>257250</v>
-      </c>
-      <c r="C167" s="80" t="n">
-        <v>271950</v>
-      </c>
-      <c r="D167" s="80" t="n">
-        <v>286650</v>
-      </c>
-      <c r="E167" s="80">
+    <row r="167" outlineLevel="1">
+      <c r="A167" s="73" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="B167" s="75" t="n">
+        <v>774990</v>
+      </c>
+      <c r="C167" s="75" t="n">
+        <v>819270</v>
+      </c>
+      <c r="D167" s="75" t="n">
+        <v>863550</v>
+      </c>
+      <c r="E167" s="75">
         <f>D167-B167</f>
         <v/>
       </c>
-      <c r="F167" s="103">
+      <c r="F167" s="101">
         <f>IFERROR(D167/B167-1,0)</f>
         <v/>
       </c>
-      <c r="G167" s="80" t="n">
-        <v>228126</v>
-      </c>
-      <c r="H167" s="80" t="n">
-        <v>239279</v>
-      </c>
-      <c r="I167" s="80" t="n">
-        <v>251231</v>
-      </c>
-      <c r="J167" s="80">
+      <c r="G167" s="75" t="n">
+        <v>697028</v>
+      </c>
+      <c r="H167" s="75" t="n">
+        <v>731858</v>
+      </c>
+      <c r="I167" s="75" t="n">
+        <v>769219</v>
+      </c>
+      <c r="J167" s="75">
         <f>I167-G167</f>
         <v/>
       </c>
-      <c r="K167" s="103">
+      <c r="K167" s="101">
         <f>IFERROR(I167/G167-1,0)</f>
         <v/>
       </c>
-      <c r="L167" s="80">
+      <c r="L167" s="75">
         <f>B167-G167</f>
         <v/>
       </c>
-      <c r="M167" s="80">
+      <c r="M167" s="75">
         <f>C167-H167</f>
         <v/>
       </c>
-      <c r="N167" s="81">
+      <c r="N167" s="102">
         <f>D167-I167</f>
         <v/>
       </c>
-      <c r="O167" s="80">
+      <c r="O167" s="75">
         <f>N167-L167</f>
         <v/>
       </c>
-      <c r="P167" s="82">
+      <c r="P167" s="77">
         <f>IFERROR(N167/D167,0)</f>
         <v/>
       </c>
     </row>
-    <row r="168" hidden="1" outlineLevel="4">
-      <c r="A168" s="84" t="inlineStr">
-        <is>
-          <t>Alternance</t>
+    <row r="168" hidden="1" outlineLevel="2">
+      <c r="A168" s="78" t="inlineStr">
+        <is>
+          <t>BAC_TOU</t>
         </is>
       </c>
       <c r="B168" s="80" t="n">
-        <v>257250</v>
+        <v>774990</v>
       </c>
       <c r="C168" s="80" t="n">
-        <v>271950</v>
+        <v>819270</v>
       </c>
       <c r="D168" s="80" t="n">
-        <v>286650</v>
+        <v>863550</v>
       </c>
       <c r="E168" s="80">
         <f>D168-B168</f>
@@ -18753,13 +18853,13 @@
         <v/>
       </c>
       <c r="G168" s="80" t="n">
-        <v>228126</v>
+        <v>697028</v>
       </c>
       <c r="H168" s="80" t="n">
-        <v>239279</v>
+        <v>731858</v>
       </c>
       <c r="I168" s="80" t="n">
-        <v>251231</v>
+        <v>769219</v>
       </c>
       <c r="J168" s="80">
         <f>I168-G168</f>
@@ -18793,17 +18893,17 @@
     <row r="169" hidden="1" outlineLevel="3">
       <c r="A169" s="83" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B169" s="80" t="n">
-        <v>249900</v>
+        <v>267840</v>
       </c>
       <c r="C169" s="80" t="n">
-        <v>264600</v>
+        <v>282720</v>
       </c>
       <c r="D169" s="80" t="n">
-        <v>279300</v>
+        <v>297600</v>
       </c>
       <c r="E169" s="80">
         <f>D169-B169</f>
@@ -18814,13 +18914,13 @@
         <v/>
       </c>
       <c r="G169" s="80" t="n">
-        <v>223692</v>
+        <v>247134</v>
       </c>
       <c r="H169" s="80" t="n">
-        <v>234874</v>
+        <v>259754</v>
       </c>
       <c r="I169" s="80" t="n">
-        <v>246839</v>
+        <v>273337</v>
       </c>
       <c r="J169" s="80">
         <f>I169-G169</f>
@@ -18858,13 +18958,13 @@
         </is>
       </c>
       <c r="B170" s="80" t="n">
-        <v>249900</v>
+        <v>267840</v>
       </c>
       <c r="C170" s="80" t="n">
-        <v>264600</v>
+        <v>282720</v>
       </c>
       <c r="D170" s="80" t="n">
-        <v>279300</v>
+        <v>297600</v>
       </c>
       <c r="E170" s="80">
         <f>D170-B170</f>
@@ -18875,13 +18975,13 @@
         <v/>
       </c>
       <c r="G170" s="80" t="n">
-        <v>223692</v>
+        <v>247134</v>
       </c>
       <c r="H170" s="80" t="n">
-        <v>234874</v>
+        <v>259754</v>
       </c>
       <c r="I170" s="80" t="n">
-        <v>246839</v>
+        <v>273337</v>
       </c>
       <c r="J170" s="80">
         <f>I170-G170</f>
@@ -18912,81 +19012,81 @@
         <v/>
       </c>
     </row>
-    <row r="171" outlineLevel="1">
-      <c r="A171" s="73" t="inlineStr">
-        <is>
-          <t>Paris</t>
-        </is>
-      </c>
-      <c r="B171" s="75" t="n">
-        <v>968100</v>
-      </c>
-      <c r="C171" s="75" t="n">
-        <v>1015320</v>
-      </c>
-      <c r="D171" s="75" t="n">
-        <v>1086150</v>
-      </c>
-      <c r="E171" s="75">
+    <row r="171" hidden="1" outlineLevel="3">
+      <c r="A171" s="83" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B171" s="80" t="n">
+        <v>257250</v>
+      </c>
+      <c r="C171" s="80" t="n">
+        <v>271950</v>
+      </c>
+      <c r="D171" s="80" t="n">
+        <v>286650</v>
+      </c>
+      <c r="E171" s="80">
         <f>D171-B171</f>
         <v/>
       </c>
-      <c r="F171" s="101">
+      <c r="F171" s="103">
         <f>IFERROR(D171/B171-1,0)</f>
         <v/>
       </c>
-      <c r="G171" s="75" t="n">
-        <v>1001233</v>
-      </c>
-      <c r="H171" s="75" t="n">
-        <v>1049851</v>
-      </c>
-      <c r="I171" s="75" t="n">
-        <v>1105827</v>
-      </c>
-      <c r="J171" s="75">
+      <c r="G171" s="80" t="n">
+        <v>227150</v>
+      </c>
+      <c r="H171" s="80" t="n">
+        <v>238241</v>
+      </c>
+      <c r="I171" s="80" t="n">
+        <v>250123</v>
+      </c>
+      <c r="J171" s="80">
         <f>I171-G171</f>
         <v/>
       </c>
-      <c r="K171" s="101">
+      <c r="K171" s="103">
         <f>IFERROR(I171/G171-1,0)</f>
         <v/>
       </c>
-      <c r="L171" s="75">
+      <c r="L171" s="80">
         <f>B171-G171</f>
         <v/>
       </c>
-      <c r="M171" s="75">
+      <c r="M171" s="80">
         <f>C171-H171</f>
         <v/>
       </c>
-      <c r="N171" s="102">
+      <c r="N171" s="81">
         <f>D171-I171</f>
         <v/>
       </c>
-      <c r="O171" s="75">
+      <c r="O171" s="80">
         <f>N171-L171</f>
         <v/>
       </c>
-      <c r="P171" s="88">
+      <c r="P171" s="82">
         <f>IFERROR(N171/D171,0)</f>
         <v/>
       </c>
     </row>
-    <row r="172" hidden="1" outlineLevel="2">
-      <c r="A172" s="78" t="inlineStr">
-        <is>
-          <t>BAC_TOU</t>
+    <row r="172" hidden="1" outlineLevel="4">
+      <c r="A172" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
         </is>
       </c>
       <c r="B172" s="80" t="n">
-        <v>968100</v>
+        <v>257250</v>
       </c>
       <c r="C172" s="80" t="n">
-        <v>1015320</v>
+        <v>271950</v>
       </c>
       <c r="D172" s="80" t="n">
-        <v>1086150</v>
+        <v>286650</v>
       </c>
       <c r="E172" s="80">
         <f>D172-B172</f>
@@ -18997,13 +19097,13 @@
         <v/>
       </c>
       <c r="G172" s="80" t="n">
-        <v>1001233</v>
+        <v>227150</v>
       </c>
       <c r="H172" s="80" t="n">
-        <v>1049851</v>
+        <v>238241</v>
       </c>
       <c r="I172" s="80" t="n">
-        <v>1105827</v>
+        <v>250123</v>
       </c>
       <c r="J172" s="80">
         <f>I172-G172</f>
@@ -19029,7 +19129,7 @@
         <f>N172-L172</f>
         <v/>
       </c>
-      <c r="P172" s="86">
+      <c r="P172" s="82">
         <f>IFERROR(N172/D172,0)</f>
         <v/>
       </c>
@@ -19037,17 +19137,17 @@
     <row r="173" hidden="1" outlineLevel="3">
       <c r="A173" s="83" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="B173" s="80" t="n">
-        <v>333060</v>
+        <v>249900</v>
       </c>
       <c r="C173" s="80" t="n">
-        <v>348920</v>
+        <v>264600</v>
       </c>
       <c r="D173" s="80" t="n">
-        <v>372710</v>
+        <v>279300</v>
       </c>
       <c r="E173" s="80">
         <f>D173-B173</f>
@@ -19058,13 +19158,13 @@
         <v/>
       </c>
       <c r="G173" s="80" t="n">
-        <v>356009</v>
+        <v>222744</v>
       </c>
       <c r="H173" s="80" t="n">
-        <v>373876</v>
+        <v>233864</v>
       </c>
       <c r="I173" s="80" t="n">
-        <v>394284</v>
+        <v>245759</v>
       </c>
       <c r="J173" s="80">
         <f>I173-G173</f>
@@ -19090,7 +19190,7 @@
         <f>N173-L173</f>
         <v/>
       </c>
-      <c r="P173" s="86">
+      <c r="P173" s="82">
         <f>IFERROR(N173/D173,0)</f>
         <v/>
       </c>
@@ -19102,13 +19202,13 @@
         </is>
       </c>
       <c r="B174" s="80" t="n">
-        <v>333060</v>
+        <v>249900</v>
       </c>
       <c r="C174" s="80" t="n">
-        <v>348920</v>
+        <v>264600</v>
       </c>
       <c r="D174" s="80" t="n">
-        <v>372710</v>
+        <v>279300</v>
       </c>
       <c r="E174" s="80">
         <f>D174-B174</f>
@@ -19119,13 +19219,13 @@
         <v/>
       </c>
       <c r="G174" s="80" t="n">
-        <v>356009</v>
+        <v>222744</v>
       </c>
       <c r="H174" s="80" t="n">
-        <v>373876</v>
+        <v>233864</v>
       </c>
       <c r="I174" s="80" t="n">
-        <v>394284</v>
+        <v>245759</v>
       </c>
       <c r="J174" s="80">
         <f>I174-G174</f>
@@ -19151,86 +19251,86 @@
         <f>N174-L174</f>
         <v/>
       </c>
-      <c r="P174" s="86">
+      <c r="P174" s="82">
         <f>IFERROR(N174/D174,0)</f>
         <v/>
       </c>
     </row>
-    <row r="175" hidden="1" outlineLevel="3">
-      <c r="A175" s="83" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B175" s="80" t="n">
-        <v>321440</v>
-      </c>
-      <c r="C175" s="80" t="n">
-        <v>337120</v>
-      </c>
-      <c r="D175" s="80" t="n">
-        <v>360640</v>
-      </c>
-      <c r="E175" s="80">
+    <row r="175" outlineLevel="1">
+      <c r="A175" s="73" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="B175" s="75" t="n">
+        <v>968100</v>
+      </c>
+      <c r="C175" s="75" t="n">
+        <v>1015320</v>
+      </c>
+      <c r="D175" s="75" t="n">
+        <v>1086150</v>
+      </c>
+      <c r="E175" s="75">
         <f>D175-B175</f>
         <v/>
       </c>
-      <c r="F175" s="103">
+      <c r="F175" s="101">
         <f>IFERROR(D175/B175-1,0)</f>
         <v/>
       </c>
-      <c r="G175" s="80" t="n">
-        <v>325414</v>
-      </c>
-      <c r="H175" s="80" t="n">
-        <v>340787</v>
-      </c>
-      <c r="I175" s="80" t="n">
-        <v>358529</v>
-      </c>
-      <c r="J175" s="80">
+      <c r="G175" s="75" t="n">
+        <v>997575</v>
+      </c>
+      <c r="H175" s="75" t="n">
+        <v>1045990</v>
+      </c>
+      <c r="I175" s="75" t="n">
+        <v>1101645</v>
+      </c>
+      <c r="J175" s="75">
         <f>I175-G175</f>
         <v/>
       </c>
-      <c r="K175" s="103">
+      <c r="K175" s="101">
         <f>IFERROR(I175/G175-1,0)</f>
         <v/>
       </c>
-      <c r="L175" s="80">
+      <c r="L175" s="75">
         <f>B175-G175</f>
         <v/>
       </c>
-      <c r="M175" s="80">
+      <c r="M175" s="75">
         <f>C175-H175</f>
         <v/>
       </c>
-      <c r="N175" s="81">
+      <c r="N175" s="102">
         <f>D175-I175</f>
         <v/>
       </c>
-      <c r="O175" s="80">
+      <c r="O175" s="75">
         <f>N175-L175</f>
         <v/>
       </c>
-      <c r="P175" s="86">
+      <c r="P175" s="88">
         <f>IFERROR(N175/D175,0)</f>
         <v/>
       </c>
     </row>
-    <row r="176" hidden="1" outlineLevel="4">
-      <c r="A176" s="84" t="inlineStr">
-        <is>
-          <t>Alternance</t>
+    <row r="176" hidden="1" outlineLevel="2">
+      <c r="A176" s="78" t="inlineStr">
+        <is>
+          <t>BAC_TOU</t>
         </is>
       </c>
       <c r="B176" s="80" t="n">
-        <v>321440</v>
+        <v>968100</v>
       </c>
       <c r="C176" s="80" t="n">
-        <v>337120</v>
+        <v>1015320</v>
       </c>
       <c r="D176" s="80" t="n">
-        <v>360640</v>
+        <v>1086150</v>
       </c>
       <c r="E176" s="80">
         <f>D176-B176</f>
@@ -19241,13 +19341,13 @@
         <v/>
       </c>
       <c r="G176" s="80" t="n">
-        <v>325414</v>
+        <v>997575</v>
       </c>
       <c r="H176" s="80" t="n">
-        <v>340787</v>
+        <v>1045990</v>
       </c>
       <c r="I176" s="80" t="n">
-        <v>358529</v>
+        <v>1101645</v>
       </c>
       <c r="J176" s="80">
         <f>I176-G176</f>
@@ -19281,17 +19381,17 @@
     <row r="177" hidden="1" outlineLevel="3">
       <c r="A177" s="83" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B177" s="80" t="n">
-        <v>313600</v>
+        <v>333060</v>
       </c>
       <c r="C177" s="80" t="n">
-        <v>329280</v>
+        <v>348920</v>
       </c>
       <c r="D177" s="80" t="n">
-        <v>352800</v>
+        <v>372710</v>
       </c>
       <c r="E177" s="80">
         <f>D177-B177</f>
@@ -19302,13 +19402,13 @@
         <v/>
       </c>
       <c r="G177" s="80" t="n">
-        <v>319810</v>
+        <v>354760</v>
       </c>
       <c r="H177" s="80" t="n">
-        <v>335188</v>
+        <v>372559</v>
       </c>
       <c r="I177" s="80" t="n">
-        <v>353014</v>
+        <v>392860</v>
       </c>
       <c r="J177" s="80">
         <f>I177-G177</f>
@@ -19346,13 +19446,13 @@
         </is>
       </c>
       <c r="B178" s="80" t="n">
-        <v>313600</v>
+        <v>333060</v>
       </c>
       <c r="C178" s="80" t="n">
-        <v>329280</v>
+        <v>348920</v>
       </c>
       <c r="D178" s="80" t="n">
-        <v>352800</v>
+        <v>372710</v>
       </c>
       <c r="E178" s="80">
         <f>D178-B178</f>
@@ -19363,13 +19463,13 @@
         <v/>
       </c>
       <c r="G178" s="80" t="n">
-        <v>319810</v>
+        <v>354760</v>
       </c>
       <c r="H178" s="80" t="n">
-        <v>335188</v>
+        <v>372559</v>
       </c>
       <c r="I178" s="80" t="n">
-        <v>353014</v>
+        <v>392860</v>
       </c>
       <c r="J178" s="80">
         <f>I178-G178</f>
@@ -19397,6 +19497,250 @@
       </c>
       <c r="P178" s="86">
         <f>IFERROR(N178/D178,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179" hidden="1" outlineLevel="3">
+      <c r="A179" s="83" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B179" s="80" t="n">
+        <v>321440</v>
+      </c>
+      <c r="C179" s="80" t="n">
+        <v>337120</v>
+      </c>
+      <c r="D179" s="80" t="n">
+        <v>360640</v>
+      </c>
+      <c r="E179" s="80">
+        <f>D179-B179</f>
+        <v/>
+      </c>
+      <c r="F179" s="103">
+        <f>IFERROR(D179/B179-1,0)</f>
+        <v/>
+      </c>
+      <c r="G179" s="80" t="n">
+        <v>324194</v>
+      </c>
+      <c r="H179" s="80" t="n">
+        <v>339500</v>
+      </c>
+      <c r="I179" s="80" t="n">
+        <v>357135</v>
+      </c>
+      <c r="J179" s="80">
+        <f>I179-G179</f>
+        <v/>
+      </c>
+      <c r="K179" s="103">
+        <f>IFERROR(I179/G179-1,0)</f>
+        <v/>
+      </c>
+      <c r="L179" s="80">
+        <f>B179-G179</f>
+        <v/>
+      </c>
+      <c r="M179" s="80">
+        <f>C179-H179</f>
+        <v/>
+      </c>
+      <c r="N179" s="81">
+        <f>D179-I179</f>
+        <v/>
+      </c>
+      <c r="O179" s="80">
+        <f>N179-L179</f>
+        <v/>
+      </c>
+      <c r="P179" s="86">
+        <f>IFERROR(N179/D179,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180" hidden="1" outlineLevel="4">
+      <c r="A180" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
+        </is>
+      </c>
+      <c r="B180" s="80" t="n">
+        <v>321440</v>
+      </c>
+      <c r="C180" s="80" t="n">
+        <v>337120</v>
+      </c>
+      <c r="D180" s="80" t="n">
+        <v>360640</v>
+      </c>
+      <c r="E180" s="80">
+        <f>D180-B180</f>
+        <v/>
+      </c>
+      <c r="F180" s="103">
+        <f>IFERROR(D180/B180-1,0)</f>
+        <v/>
+      </c>
+      <c r="G180" s="80" t="n">
+        <v>324194</v>
+      </c>
+      <c r="H180" s="80" t="n">
+        <v>339500</v>
+      </c>
+      <c r="I180" s="80" t="n">
+        <v>357135</v>
+      </c>
+      <c r="J180" s="80">
+        <f>I180-G180</f>
+        <v/>
+      </c>
+      <c r="K180" s="103">
+        <f>IFERROR(I180/G180-1,0)</f>
+        <v/>
+      </c>
+      <c r="L180" s="80">
+        <f>B180-G180</f>
+        <v/>
+      </c>
+      <c r="M180" s="80">
+        <f>C180-H180</f>
+        <v/>
+      </c>
+      <c r="N180" s="81">
+        <f>D180-I180</f>
+        <v/>
+      </c>
+      <c r="O180" s="80">
+        <f>N180-L180</f>
+        <v/>
+      </c>
+      <c r="P180" s="86">
+        <f>IFERROR(N180/D180,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181" hidden="1" outlineLevel="3">
+      <c r="A181" s="83" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B181" s="80" t="n">
+        <v>313600</v>
+      </c>
+      <c r="C181" s="80" t="n">
+        <v>329280</v>
+      </c>
+      <c r="D181" s="80" t="n">
+        <v>352800</v>
+      </c>
+      <c r="E181" s="80">
+        <f>D181-B181</f>
+        <v/>
+      </c>
+      <c r="F181" s="103">
+        <f>IFERROR(D181/B181-1,0)</f>
+        <v/>
+      </c>
+      <c r="G181" s="80" t="n">
+        <v>318621</v>
+      </c>
+      <c r="H181" s="80" t="n">
+        <v>333931</v>
+      </c>
+      <c r="I181" s="80" t="n">
+        <v>351650</v>
+      </c>
+      <c r="J181" s="80">
+        <f>I181-G181</f>
+        <v/>
+      </c>
+      <c r="K181" s="103">
+        <f>IFERROR(I181/G181-1,0)</f>
+        <v/>
+      </c>
+      <c r="L181" s="80">
+        <f>B181-G181</f>
+        <v/>
+      </c>
+      <c r="M181" s="80">
+        <f>C181-H181</f>
+        <v/>
+      </c>
+      <c r="N181" s="81">
+        <f>D181-I181</f>
+        <v/>
+      </c>
+      <c r="O181" s="80">
+        <f>N181-L181</f>
+        <v/>
+      </c>
+      <c r="P181" s="86">
+        <f>IFERROR(N181/D181,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182" hidden="1" outlineLevel="4">
+      <c r="A182" s="84" t="inlineStr">
+        <is>
+          <t>Alternance</t>
+        </is>
+      </c>
+      <c r="B182" s="80" t="n">
+        <v>313600</v>
+      </c>
+      <c r="C182" s="80" t="n">
+        <v>329280</v>
+      </c>
+      <c r="D182" s="80" t="n">
+        <v>352800</v>
+      </c>
+      <c r="E182" s="80">
+        <f>D182-B182</f>
+        <v/>
+      </c>
+      <c r="F182" s="103">
+        <f>IFERROR(D182/B182-1,0)</f>
+        <v/>
+      </c>
+      <c r="G182" s="80" t="n">
+        <v>318621</v>
+      </c>
+      <c r="H182" s="80" t="n">
+        <v>333931</v>
+      </c>
+      <c r="I182" s="80" t="n">
+        <v>351650</v>
+      </c>
+      <c r="J182" s="80">
+        <f>I182-G182</f>
+        <v/>
+      </c>
+      <c r="K182" s="103">
+        <f>IFERROR(I182/G182-1,0)</f>
+        <v/>
+      </c>
+      <c r="L182" s="80">
+        <f>B182-G182</f>
+        <v/>
+      </c>
+      <c r="M182" s="80">
+        <f>C182-H182</f>
+        <v/>
+      </c>
+      <c r="N182" s="81">
+        <f>D182-I182</f>
+        <v/>
+      </c>
+      <c r="O182" s="80">
+        <f>N182-L182</f>
+        <v/>
+      </c>
+      <c r="P182" s="86">
+        <f>IFERROR(N182/D182,0)</f>
         <v/>
       </c>
     </row>
